--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128536275</v>
       </c>
       <c r="B2" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,6 +795,1718 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128970268</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>665540</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6564865</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128970277</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>665424</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6565079</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128970265</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92824</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>665424</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6565096</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128970274</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>665452</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6565050</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128970270</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>665540</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6564894</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128970269</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>665528</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6564890</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128970284</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>665545</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6564914</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128970275</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>665443</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6565057</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128970267</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>665571</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6564879</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128970271</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>665506</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6564967</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128970281</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>665505</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6565027</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128970264</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>665464</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6565020</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128970273</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>665465</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6565043</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128970272</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>665504</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6564970</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128970278</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>665427</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6565093</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128970282</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>665516</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6565017</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970265</v>
+        <v>128970274</v>
       </c>
       <c r="B5" t="n">
-        <v>92824</v>
+        <v>92836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665424</v>
+        <v>665452</v>
       </c>
       <c r="R5" t="n">
-        <v>6565096</v>
+        <v>6565050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970274</v>
+        <v>128970265</v>
       </c>
       <c r="B6" t="n">
-        <v>92836</v>
+        <v>92824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665452</v>
+        <v>665424</v>
       </c>
       <c r="R6" t="n">
-        <v>6565050</v>
+        <v>6565096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128536275</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970274</v>
+        <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92836</v>
+        <v>92829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665452</v>
+        <v>665424</v>
       </c>
       <c r="R5" t="n">
-        <v>6565050</v>
+        <v>6565096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970265</v>
+        <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92824</v>
+        <v>92841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665424</v>
+        <v>665452</v>
       </c>
       <c r="R6" t="n">
-        <v>6565096</v>
+        <v>6565050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128970264</v>
       </c>
       <c r="B14" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>128970273</v>
       </c>
       <c r="B15" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128536275</v>
       </c>
       <c r="B2" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3209,6 +3209,6644 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129150596</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>665174</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6564743</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129150574</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>665437</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6564617</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129150586</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>665436</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6564778</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129150585</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>665424</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6564786</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129150579</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>665438</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6564656</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129150565</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>665143</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6564565</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129150582</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>665370</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6564621</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129150584</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>665409</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6564786</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129150576</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>665452</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6564659</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129150599</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>665294</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6564670</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129150567</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>665228</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6564499</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129150578</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>665443</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6564659</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129150620</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>665358</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6564768</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129150604</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>665464</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6564686</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129150602</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>665388</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6564663</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129150616</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>665382</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6564609</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129150569</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>665388</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6564531</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129150617</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>665376</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6564598</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129150612</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>665587</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6564768</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129150606</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>665503</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6564692</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129150590</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>665331</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6564765</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129150571</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>665408</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6564551</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129150568</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>665276</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6564529</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129150621</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>665321</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6564753</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129150577</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>665446</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6564659</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129150627</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92279</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>665419</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6564672</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129150611</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>665607</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6564770</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129150601</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>665364</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6564665</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129150591</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>665318</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6564762</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129150580</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>665374</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6564595</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129150570</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>665399</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6564537</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129150557</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>665183</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6564505</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129150626</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92279</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>665260</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6564773</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129150628</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92279</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>665455</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6564681</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129150618</v>
+      </c>
+      <c r="B60" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>665400</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6564742</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129150566</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>665194</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6564498</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129150619</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>665365</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6564786</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129150583</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>665372</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6564721</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129150594</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>665232</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6564745</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129150598</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>665283</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6564685</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129150605</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>665484</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6564691</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129150593</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>665256</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6564756</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129150625</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92279</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>665422</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6564565</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129150613</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>665566</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6564813</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129150587</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>665424</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6564762</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129150595</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>665210</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6564762</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129150556</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>665406</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6564548</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129150609</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>665505</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6564674</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129150610</v>
+      </c>
+      <c r="B74" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>665640</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6564667</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129150622</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>665194</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6564740</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129150581</v>
+      </c>
+      <c r="B76" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>665366</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6564608</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129150597</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>665233</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6564718</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129150589</v>
+      </c>
+      <c r="B78" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>665371</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6564789</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129150572</v>
+      </c>
+      <c r="B79" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>665424</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6564571</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129150607</v>
+      </c>
+      <c r="B80" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>665514</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6564684</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129150629</v>
+      </c>
+      <c r="B81" t="n">
+        <v>92279</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>665507</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6564685</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129150600</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>665346</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6564670</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129150603</v>
+      </c>
+      <c r="B83" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>665453</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6564677</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129150575</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>665457</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6564660</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129150588</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92849</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>665414</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6564728</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129150615</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>665164</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6564505</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129150623</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>665233</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6564720</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92837</v>
+        <v>92842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128970264</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>128970273</v>
       </c>
       <c r="B15" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150596</v>
+        <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665174</v>
+        <v>665437</v>
       </c>
       <c r="R26" t="n">
-        <v>6564743</v>
+        <v>6564617</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150574</v>
+        <v>129150586</v>
       </c>
       <c r="B27" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665437</v>
+        <v>665436</v>
       </c>
       <c r="R27" t="n">
-        <v>6564617</v>
+        <v>6564778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150586</v>
+        <v>129150585</v>
       </c>
       <c r="B28" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665436</v>
+        <v>665424</v>
       </c>
       <c r="R28" t="n">
-        <v>6564778</v>
+        <v>6564786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150585</v>
+        <v>129150596</v>
       </c>
       <c r="B29" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665424</v>
+        <v>665174</v>
       </c>
       <c r="R29" t="n">
-        <v>6564786</v>
+        <v>6564743</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129150579</v>
+        <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665438</v>
+        <v>665143</v>
       </c>
       <c r="R30" t="n">
-        <v>6564656</v>
+        <v>6564565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129150565</v>
+        <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665143</v>
+        <v>665438</v>
       </c>
       <c r="R31" t="n">
-        <v>6564565</v>
+        <v>6564656</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129150582</v>
+        <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665370</v>
+        <v>665409</v>
       </c>
       <c r="R32" t="n">
-        <v>6564621</v>
+        <v>6564786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129150584</v>
+        <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665409</v>
+        <v>665370</v>
       </c>
       <c r="R33" t="n">
-        <v>6564786</v>
+        <v>6564621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150599</v>
+        <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665294</v>
+        <v>665464</v>
       </c>
       <c r="R35" t="n">
-        <v>6564670</v>
+        <v>6564686</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150567</v>
+        <v>129150599</v>
       </c>
       <c r="B36" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665228</v>
+        <v>665294</v>
       </c>
       <c r="R36" t="n">
-        <v>6564499</v>
+        <v>6564670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4391,7 +4391,7 @@
         <v>129150578</v>
       </c>
       <c r="B37" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4495,32 +4495,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150620</v>
+        <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>92854</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665358</v>
+        <v>665228</v>
       </c>
       <c r="R38" t="n">
-        <v>6564768</v>
+        <v>6564499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150604</v>
+        <v>129150620</v>
       </c>
       <c r="B39" t="n">
-        <v>92849</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665464</v>
+        <v>665358</v>
       </c>
       <c r="R39" t="n">
-        <v>6564686</v>
+        <v>6564768</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150602</v>
+        <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665388</v>
+        <v>665408</v>
       </c>
       <c r="R40" t="n">
-        <v>6564663</v>
+        <v>6564551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150616</v>
+        <v>129150590</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92854</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665382</v>
+        <v>665331</v>
       </c>
       <c r="R41" t="n">
-        <v>6564609</v>
+        <v>6564765</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4923,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150569</v>
+        <v>129150602</v>
       </c>
       <c r="B42" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>665388</v>
       </c>
       <c r="R42" t="n">
-        <v>6564531</v>
+        <v>6564663</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,32 +5030,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150617</v>
+        <v>129150606</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>92854</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665376</v>
+        <v>665503</v>
       </c>
       <c r="R43" t="n">
-        <v>6564598</v>
+        <v>6564692</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5140,7 +5140,7 @@
         <v>129150612</v>
       </c>
       <c r="B44" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150606</v>
+        <v>129150569</v>
       </c>
       <c r="B45" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R45" t="n">
-        <v>6564692</v>
+        <v>6564531</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150590</v>
+        <v>129150617</v>
       </c>
       <c r="B46" t="n">
-        <v>92849</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665331</v>
+        <v>665376</v>
       </c>
       <c r="R46" t="n">
-        <v>6564765</v>
+        <v>6564598</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150571</v>
+        <v>129150616</v>
       </c>
       <c r="B47" t="n">
-        <v>92849</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665408</v>
+        <v>665382</v>
       </c>
       <c r="R47" t="n">
-        <v>6564551</v>
+        <v>6564609</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150577</v>
+        <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92849</v>
+        <v>92284</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665446</v>
+        <v>665419</v>
       </c>
       <c r="R50" t="n">
-        <v>6564659</v>
+        <v>6564672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,32 +5886,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150627</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
-        <v>92279</v>
+        <v>92854</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665419</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564672</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B52" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R52" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6103,7 +6103,7 @@
         <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>129150591</v>
       </c>
       <c r="B54" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>129150557</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6635,10 +6635,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150626</v>
+        <v>129150628</v>
       </c>
       <c r="B58" t="n">
-        <v>92279</v>
+        <v>92284</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665260</v>
+        <v>665455</v>
       </c>
       <c r="R58" t="n">
-        <v>6564773</v>
+        <v>6564681</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,10 +6742,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150628</v>
+        <v>129150626</v>
       </c>
       <c r="B59" t="n">
-        <v>92279</v>
+        <v>92284</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665455</v>
+        <v>665260</v>
       </c>
       <c r="R59" t="n">
-        <v>6564681</v>
+        <v>6564773</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6956,10 +6956,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R61" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,32 +7063,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150619</v>
+        <v>129150566</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>92854</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665365</v>
+        <v>665194</v>
       </c>
       <c r="R62" t="n">
-        <v>6564786</v>
+        <v>6564498</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150583</v>
+        <v>129150619</v>
       </c>
       <c r="B63" t="n">
-        <v>92849</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665372</v>
+        <v>665365</v>
       </c>
       <c r="R63" t="n">
-        <v>6564721</v>
+        <v>6564786</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7280,7 +7280,7 @@
         <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7491,10 +7491,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150605</v>
+        <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665484</v>
+        <v>665256</v>
       </c>
       <c r="R66" t="n">
-        <v>6564691</v>
+        <v>6564756</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7598,10 +7598,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129150593</v>
+        <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>665256</v>
+        <v>665484</v>
       </c>
       <c r="R67" t="n">
-        <v>6564756</v>
+        <v>6564691</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7705,32 +7705,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150625</v>
+        <v>129150613</v>
       </c>
       <c r="B68" t="n">
-        <v>92279</v>
+        <v>92854</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665422</v>
+        <v>665566</v>
       </c>
       <c r="R68" t="n">
-        <v>6564565</v>
+        <v>6564813</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7812,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150613</v>
+        <v>129150625</v>
       </c>
       <c r="B69" t="n">
-        <v>92849</v>
+        <v>92284</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665566</v>
+        <v>665422</v>
       </c>
       <c r="R69" t="n">
-        <v>6564813</v>
+        <v>6564565</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129150595</v>
+        <v>129150556</v>
       </c>
       <c r="B71" t="n">
-        <v>92849</v>
+        <v>57883</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8037,34 +8037,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665210</v>
+        <v>665406</v>
       </c>
       <c r="R71" t="n">
-        <v>6564762</v>
+        <v>6564548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8096,7 +8100,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8106,7 +8110,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8133,10 +8137,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150556</v>
+        <v>129150595</v>
       </c>
       <c r="B72" t="n">
-        <v>57883</v>
+        <v>92854</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8144,38 +8148,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665406</v>
+        <v>665210</v>
       </c>
       <c r="R72" t="n">
-        <v>6564548</v>
+        <v>6564762</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8244,10 +8244,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150609</v>
+        <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665505</v>
+        <v>665640</v>
       </c>
       <c r="R73" t="n">
-        <v>6564674</v>
+        <v>6564667</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R74" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150581</v>
+        <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92849</v>
+        <v>92284</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665366</v>
+        <v>665507</v>
       </c>
       <c r="R76" t="n">
-        <v>6564608</v>
+        <v>6564685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150597</v>
+        <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665233</v>
+        <v>665424</v>
       </c>
       <c r="R77" t="n">
-        <v>6564718</v>
+        <v>6564571</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150589</v>
+        <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665371</v>
+        <v>665514</v>
       </c>
       <c r="R78" t="n">
-        <v>6564789</v>
+        <v>6564684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150572</v>
+        <v>129150581</v>
       </c>
       <c r="B79" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665424</v>
+        <v>665366</v>
       </c>
       <c r="R79" t="n">
-        <v>6564571</v>
+        <v>6564608</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150607</v>
+        <v>129150600</v>
       </c>
       <c r="B80" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665514</v>
+        <v>665346</v>
       </c>
       <c r="R80" t="n">
-        <v>6564684</v>
+        <v>6564670</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,32 +9100,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150629</v>
+        <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92279</v>
+        <v>92854</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665507</v>
+        <v>665371</v>
       </c>
       <c r="R81" t="n">
-        <v>6564685</v>
+        <v>6564789</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,10 +9207,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150600</v>
+        <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665346</v>
+        <v>665233</v>
       </c>
       <c r="R82" t="n">
-        <v>6564670</v>
+        <v>6564718</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9314,10 +9314,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150603</v>
+        <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665453</v>
+        <v>665457</v>
       </c>
       <c r="R83" t="n">
-        <v>6564677</v>
+        <v>6564660</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150575</v>
+        <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665457</v>
+        <v>665453</v>
       </c>
       <c r="R84" t="n">
-        <v>6564660</v>
+        <v>6564677</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9531,7 +9531,7 @@
         <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129150615</v>
+        <v>129150623</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>665164</v>
+        <v>665233</v>
       </c>
       <c r="R86" t="n">
-        <v>6564505</v>
+        <v>6564720</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9742,7 +9742,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129150623</v>
+        <v>129150615</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>665233</v>
+        <v>665164</v>
       </c>
       <c r="R87" t="n">
-        <v>6564720</v>
+        <v>6564505</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128536275</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92842</v>
+        <v>92845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128970264</v>
+        <v>128970273</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>92857</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665464</v>
+        <v>665465</v>
       </c>
       <c r="R14" t="n">
-        <v>6565020</v>
+        <v>6565043</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128970273</v>
+        <v>128970264</v>
       </c>
       <c r="B15" t="n">
-        <v>92854</v>
+        <v>91546</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665465</v>
+        <v>665464</v>
       </c>
       <c r="R15" t="n">
-        <v>6565043</v>
+        <v>6565020</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150574</v>
+        <v>129150585</v>
       </c>
       <c r="B26" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665437</v>
+        <v>665424</v>
       </c>
       <c r="R26" t="n">
-        <v>6564617</v>
+        <v>6564786</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150586</v>
+        <v>129150596</v>
       </c>
       <c r="B27" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665436</v>
+        <v>665174</v>
       </c>
       <c r="R27" t="n">
-        <v>6564778</v>
+        <v>6564743</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150585</v>
+        <v>129150574</v>
       </c>
       <c r="B28" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665424</v>
+        <v>665437</v>
       </c>
       <c r="R28" t="n">
-        <v>6564786</v>
+        <v>6564617</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150596</v>
+        <v>129150586</v>
       </c>
       <c r="B29" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665174</v>
+        <v>665436</v>
       </c>
       <c r="R29" t="n">
-        <v>6564743</v>
+        <v>6564778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129150584</v>
+        <v>129150582</v>
       </c>
       <c r="B32" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665409</v>
+        <v>665370</v>
       </c>
       <c r="R32" t="n">
-        <v>6564786</v>
+        <v>6564621</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129150582</v>
+        <v>129150584</v>
       </c>
       <c r="B33" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665370</v>
+        <v>665409</v>
       </c>
       <c r="R33" t="n">
-        <v>6564621</v>
+        <v>6564786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150599</v>
+        <v>129150578</v>
       </c>
       <c r="B36" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665294</v>
+        <v>665443</v>
       </c>
       <c r="R36" t="n">
-        <v>6564670</v>
+        <v>6564659</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B37" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R37" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4498,7 +4498,7 @@
         <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150571</v>
+        <v>129150617</v>
       </c>
       <c r="B40" t="n">
-        <v>92854</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665408</v>
+        <v>665376</v>
       </c>
       <c r="R40" t="n">
-        <v>6564551</v>
+        <v>6564598</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150590</v>
+        <v>129150616</v>
       </c>
       <c r="B41" t="n">
-        <v>92854</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665331</v>
+        <v>665382</v>
       </c>
       <c r="R41" t="n">
-        <v>6564765</v>
+        <v>6564609</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4926,7 +4926,7 @@
         <v>129150602</v>
       </c>
       <c r="B42" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>129150606</v>
       </c>
       <c r="B43" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150612</v>
+        <v>129150571</v>
       </c>
       <c r="B44" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665587</v>
+        <v>665408</v>
       </c>
       <c r="R44" t="n">
-        <v>6564768</v>
+        <v>6564551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150569</v>
+        <v>129150612</v>
       </c>
       <c r="B45" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665388</v>
+        <v>665587</v>
       </c>
       <c r="R45" t="n">
-        <v>6564531</v>
+        <v>6564768</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150617</v>
+        <v>129150569</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665376</v>
+        <v>665388</v>
       </c>
       <c r="R46" t="n">
-        <v>6564598</v>
+        <v>6564531</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150616</v>
+        <v>129150590</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665382</v>
+        <v>665331</v>
       </c>
       <c r="R47" t="n">
-        <v>6564609</v>
+        <v>6564765</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150627</v>
+        <v>129150611</v>
       </c>
       <c r="B50" t="n">
-        <v>92284</v>
+        <v>92857</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665419</v>
+        <v>665607</v>
       </c>
       <c r="R50" t="n">
-        <v>6564672</v>
+        <v>6564770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B51" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150577</v>
+        <v>129150627</v>
       </c>
       <c r="B52" t="n">
-        <v>92854</v>
+        <v>92287</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665446</v>
+        <v>665419</v>
       </c>
       <c r="R52" t="n">
-        <v>6564659</v>
+        <v>6564672</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6103,7 +6103,7 @@
         <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>129150591</v>
       </c>
       <c r="B54" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>129150557</v>
       </c>
       <c r="B57" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6635,32 +6635,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150628</v>
+        <v>129150618</v>
       </c>
       <c r="B58" t="n">
-        <v>92284</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1958</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665455</v>
+        <v>665400</v>
       </c>
       <c r="R58" t="n">
-        <v>6564681</v>
+        <v>6564742</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,10 +6742,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150626</v>
+        <v>129150628</v>
       </c>
       <c r="B59" t="n">
-        <v>92284</v>
+        <v>92287</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665260</v>
+        <v>665455</v>
       </c>
       <c r="R59" t="n">
-        <v>6564773</v>
+        <v>6564681</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150618</v>
+        <v>129150626</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>92287</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>1958</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665400</v>
+        <v>665260</v>
       </c>
       <c r="R60" t="n">
-        <v>6564742</v>
+        <v>6564773</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6959,7 +6959,7 @@
         <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>129150566</v>
       </c>
       <c r="B62" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7277,10 +7277,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129150594</v>
+        <v>129150598</v>
       </c>
       <c r="B64" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>665232</v>
+        <v>665283</v>
       </c>
       <c r="R64" t="n">
-        <v>6564745</v>
+        <v>6564685</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7384,10 +7384,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129150598</v>
+        <v>129150593</v>
       </c>
       <c r="B65" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>665283</v>
+        <v>665256</v>
       </c>
       <c r="R65" t="n">
-        <v>6564685</v>
+        <v>6564756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,10 +7491,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150593</v>
+        <v>129150594</v>
       </c>
       <c r="B66" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665256</v>
+        <v>665232</v>
       </c>
       <c r="R66" t="n">
-        <v>6564756</v>
+        <v>6564745</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7705,32 +7705,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150613</v>
+        <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92854</v>
+        <v>92287</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665566</v>
+        <v>665422</v>
       </c>
       <c r="R68" t="n">
-        <v>6564813</v>
+        <v>6564565</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7812,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150625</v>
+        <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92284</v>
+        <v>92857</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665422</v>
+        <v>665566</v>
       </c>
       <c r="R69" t="n">
-        <v>6564565</v>
+        <v>6564813</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>129150595</v>
       </c>
       <c r="B72" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92284</v>
+        <v>92287</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>129150581</v>
       </c>
       <c r="B79" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>129150600</v>
       </c>
       <c r="B80" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970265</v>
+        <v>128970274</v>
       </c>
       <c r="B5" t="n">
-        <v>92845</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665424</v>
+        <v>665452</v>
       </c>
       <c r="R5" t="n">
-        <v>6565096</v>
+        <v>6565050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970274</v>
+        <v>128970265</v>
       </c>
       <c r="B6" t="n">
-        <v>92857</v>
+        <v>92845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665452</v>
+        <v>665424</v>
       </c>
       <c r="R6" t="n">
-        <v>6565050</v>
+        <v>6565096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3211,7 +3211,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150585</v>
+        <v>129150574</v>
       </c>
       <c r="B26" t="n">
         <v>92857</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665424</v>
+        <v>665437</v>
       </c>
       <c r="R26" t="n">
-        <v>6564786</v>
+        <v>6564617</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,7 +3318,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150596</v>
+        <v>129150586</v>
       </c>
       <c r="B27" t="n">
         <v>92857</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665174</v>
+        <v>665436</v>
       </c>
       <c r="R27" t="n">
-        <v>6564743</v>
+        <v>6564778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150574</v>
+        <v>129150585</v>
       </c>
       <c r="B28" t="n">
         <v>92857</v>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665437</v>
+        <v>665424</v>
       </c>
       <c r="R28" t="n">
-        <v>6564617</v>
+        <v>6564786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150586</v>
+        <v>129150596</v>
       </c>
       <c r="B29" t="n">
         <v>92857</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665436</v>
+        <v>665174</v>
       </c>
       <c r="R29" t="n">
-        <v>6564778</v>
+        <v>6564743</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4174,7 +4174,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150604</v>
+        <v>129150599</v>
       </c>
       <c r="B35" t="n">
         <v>92857</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665464</v>
+        <v>665294</v>
       </c>
       <c r="R35" t="n">
-        <v>6564686</v>
+        <v>6564670</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150599</v>
+        <v>129150567</v>
       </c>
       <c r="B37" t="n">
         <v>92857</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665294</v>
+        <v>665228</v>
       </c>
       <c r="R37" t="n">
-        <v>6564670</v>
+        <v>6564499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,32 +4495,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150567</v>
+        <v>129150620</v>
       </c>
       <c r="B38" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665228</v>
+        <v>665358</v>
       </c>
       <c r="R38" t="n">
-        <v>6564499</v>
+        <v>6564768</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150620</v>
+        <v>129150604</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665358</v>
+        <v>665464</v>
       </c>
       <c r="R39" t="n">
-        <v>6564768</v>
+        <v>6564686</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150602</v>
+        <v>129150571</v>
       </c>
       <c r="B42" t="n">
         <v>92857</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665388</v>
+        <v>665408</v>
       </c>
       <c r="R42" t="n">
-        <v>6564663</v>
+        <v>6564551</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150606</v>
+        <v>129150569</v>
       </c>
       <c r="B43" t="n">
         <v>92857</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R43" t="n">
-        <v>6564692</v>
+        <v>6564531</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150571</v>
+        <v>129150590</v>
       </c>
       <c r="B44" t="n">
         <v>92857</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665408</v>
+        <v>665331</v>
       </c>
       <c r="R44" t="n">
-        <v>6564551</v>
+        <v>6564765</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5244,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150612</v>
+        <v>129150602</v>
       </c>
       <c r="B45" t="n">
         <v>92857</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665587</v>
+        <v>665388</v>
       </c>
       <c r="R45" t="n">
-        <v>6564768</v>
+        <v>6564663</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,7 +5351,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150569</v>
+        <v>129150606</v>
       </c>
       <c r="B46" t="n">
         <v>92857</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665388</v>
+        <v>665503</v>
       </c>
       <c r="R46" t="n">
-        <v>6564531</v>
+        <v>6564692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,7 +5458,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150590</v>
+        <v>129150612</v>
       </c>
       <c r="B47" t="n">
         <v>92857</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665331</v>
+        <v>665587</v>
       </c>
       <c r="R47" t="n">
-        <v>6564765</v>
+        <v>6564768</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150627</v>
+        <v>129150601</v>
       </c>
       <c r="B52" t="n">
-        <v>92287</v>
+        <v>92857</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665419</v>
+        <v>665364</v>
       </c>
       <c r="R52" t="n">
-        <v>6564672</v>
+        <v>6564665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150601</v>
+        <v>129150627</v>
       </c>
       <c r="B53" t="n">
-        <v>92857</v>
+        <v>92287</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665364</v>
+        <v>665419</v>
       </c>
       <c r="R53" t="n">
-        <v>6564665</v>
+        <v>6564672</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6207,7 +6207,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150591</v>
+        <v>129150570</v>
       </c>
       <c r="B54" t="n">
         <v>92857</v>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665318</v>
+        <v>665399</v>
       </c>
       <c r="R54" t="n">
-        <v>6564762</v>
+        <v>6564537</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,7 +6314,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150580</v>
+        <v>129150591</v>
       </c>
       <c r="B55" t="n">
         <v>92857</v>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665374</v>
+        <v>665318</v>
       </c>
       <c r="R55" t="n">
-        <v>6564595</v>
+        <v>6564762</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6421,7 +6421,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129150570</v>
+        <v>129150580</v>
       </c>
       <c r="B56" t="n">
         <v>92857</v>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665399</v>
+        <v>665374</v>
       </c>
       <c r="R56" t="n">
-        <v>6564537</v>
+        <v>6564595</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6635,32 +6635,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150618</v>
+        <v>129150628</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>92287</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>1958</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665400</v>
+        <v>665455</v>
       </c>
       <c r="R58" t="n">
-        <v>6564742</v>
+        <v>6564681</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,7 +6742,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150628</v>
+        <v>129150626</v>
       </c>
       <c r="B59" t="n">
         <v>92287</v>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665455</v>
+        <v>665260</v>
       </c>
       <c r="R59" t="n">
-        <v>6564681</v>
+        <v>6564773</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150626</v>
+        <v>129150618</v>
       </c>
       <c r="B60" t="n">
-        <v>92287</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1958</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665260</v>
+        <v>665400</v>
       </c>
       <c r="R60" t="n">
-        <v>6564773</v>
+        <v>6564742</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7277,7 +7277,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129150598</v>
+        <v>129150594</v>
       </c>
       <c r="B64" t="n">
         <v>92857</v>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>665283</v>
+        <v>665232</v>
       </c>
       <c r="R64" t="n">
-        <v>6564685</v>
+        <v>6564745</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7384,7 +7384,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129150593</v>
+        <v>129150598</v>
       </c>
       <c r="B65" t="n">
         <v>92857</v>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>665256</v>
+        <v>665283</v>
       </c>
       <c r="R65" t="n">
-        <v>6564756</v>
+        <v>6564685</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,7 +7491,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150594</v>
+        <v>129150593</v>
       </c>
       <c r="B66" t="n">
         <v>92857</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665232</v>
+        <v>665256</v>
       </c>
       <c r="R66" t="n">
-        <v>6564745</v>
+        <v>6564756</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7705,32 +7705,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150625</v>
+        <v>129150613</v>
       </c>
       <c r="B68" t="n">
-        <v>92287</v>
+        <v>92857</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665422</v>
+        <v>665566</v>
       </c>
       <c r="R68" t="n">
-        <v>6564565</v>
+        <v>6564813</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7812,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150613</v>
+        <v>129150625</v>
       </c>
       <c r="B69" t="n">
-        <v>92857</v>
+        <v>92287</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665566</v>
+        <v>665422</v>
       </c>
       <c r="R69" t="n">
-        <v>6564813</v>
+        <v>6564565</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8026,10 +8026,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129150556</v>
+        <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>57883</v>
+        <v>92857</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8037,38 +8037,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665406</v>
+        <v>665210</v>
       </c>
       <c r="R71" t="n">
-        <v>6564548</v>
+        <v>6564762</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8100,7 +8096,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8110,7 +8106,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8137,10 +8133,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150595</v>
+        <v>129150556</v>
       </c>
       <c r="B72" t="n">
-        <v>92857</v>
+        <v>57883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8148,34 +8144,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665210</v>
+        <v>665406</v>
       </c>
       <c r="R72" t="n">
-        <v>6564762</v>
+        <v>6564548</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8244,32 +8244,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150610</v>
+        <v>129150622</v>
       </c>
       <c r="B73" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665640</v>
+        <v>665194</v>
       </c>
       <c r="R73" t="n">
-        <v>6564667</v>
+        <v>6564740</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,7 +8351,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150609</v>
+        <v>129150610</v>
       </c>
       <c r="B74" t="n">
         <v>92857</v>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665505</v>
+        <v>665640</v>
       </c>
       <c r="R74" t="n">
-        <v>6564674</v>
+        <v>6564667</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8458,32 +8458,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150622</v>
+        <v>129150609</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665194</v>
+        <v>665505</v>
       </c>
       <c r="R75" t="n">
-        <v>6564740</v>
+        <v>6564674</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150629</v>
+        <v>129150572</v>
       </c>
       <c r="B76" t="n">
-        <v>92287</v>
+        <v>92857</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665507</v>
+        <v>665424</v>
       </c>
       <c r="R76" t="n">
-        <v>6564685</v>
+        <v>6564571</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150572</v>
+        <v>129150607</v>
       </c>
       <c r="B77" t="n">
         <v>92857</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665424</v>
+        <v>665514</v>
       </c>
       <c r="R77" t="n">
-        <v>6564571</v>
+        <v>6564684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150607</v>
+        <v>129150581</v>
       </c>
       <c r="B78" t="n">
         <v>92857</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665514</v>
+        <v>665366</v>
       </c>
       <c r="R78" t="n">
-        <v>6564684</v>
+        <v>6564608</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150581</v>
+        <v>129150600</v>
       </c>
       <c r="B79" t="n">
         <v>92857</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665366</v>
+        <v>665346</v>
       </c>
       <c r="R79" t="n">
-        <v>6564608</v>
+        <v>6564670</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,7 +8993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150600</v>
+        <v>129150589</v>
       </c>
       <c r="B80" t="n">
         <v>92857</v>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665346</v>
+        <v>665371</v>
       </c>
       <c r="R80" t="n">
-        <v>6564670</v>
+        <v>6564789</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150589</v>
+        <v>129150597</v>
       </c>
       <c r="B81" t="n">
         <v>92857</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665371</v>
+        <v>665233</v>
       </c>
       <c r="R81" t="n">
-        <v>6564789</v>
+        <v>6564718</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150597</v>
+        <v>129150629</v>
       </c>
       <c r="B82" t="n">
-        <v>92857</v>
+        <v>92287</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665233</v>
+        <v>665507</v>
       </c>
       <c r="R82" t="n">
-        <v>6564718</v>
+        <v>6564685</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -3853,7 +3853,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129150582</v>
+        <v>129150584</v>
       </c>
       <c r="B32" t="n">
         <v>92857</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665370</v>
+        <v>665409</v>
       </c>
       <c r="R32" t="n">
-        <v>6564621</v>
+        <v>6564786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,7 +3960,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129150584</v>
+        <v>129150582</v>
       </c>
       <c r="B33" t="n">
         <v>92857</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665409</v>
+        <v>665370</v>
       </c>
       <c r="R33" t="n">
-        <v>6564786</v>
+        <v>6564621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4174,7 +4174,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150599</v>
+        <v>129150604</v>
       </c>
       <c r="B35" t="n">
         <v>92857</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665294</v>
+        <v>665464</v>
       </c>
       <c r="R35" t="n">
-        <v>6564670</v>
+        <v>6564686</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B36" t="n">
         <v>92857</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R36" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150567</v>
+        <v>129150578</v>
       </c>
       <c r="B37" t="n">
         <v>92857</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665228</v>
+        <v>665443</v>
       </c>
       <c r="R37" t="n">
-        <v>6564499</v>
+        <v>6564659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,32 +4495,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150620</v>
+        <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665358</v>
+        <v>665228</v>
       </c>
       <c r="R38" t="n">
-        <v>6564768</v>
+        <v>6564499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150604</v>
+        <v>129150620</v>
       </c>
       <c r="B39" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665464</v>
+        <v>665358</v>
       </c>
       <c r="R39" t="n">
-        <v>6564686</v>
+        <v>6564768</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5565,32 +5565,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129150568</v>
+        <v>129150621</v>
       </c>
       <c r="B48" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665276</v>
+        <v>665321</v>
       </c>
       <c r="R48" t="n">
-        <v>6564529</v>
+        <v>6564753</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,32 +5672,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129150621</v>
+        <v>129150568</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665321</v>
+        <v>665276</v>
       </c>
       <c r="R49" t="n">
-        <v>6564753</v>
+        <v>6564529</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150611</v>
+        <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92857</v>
+        <v>92287</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665607</v>
+        <v>665419</v>
       </c>
       <c r="R50" t="n">
-        <v>6564770</v>
+        <v>6564672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
         <v>92857</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150601</v>
+        <v>129150577</v>
       </c>
       <c r="B52" t="n">
         <v>92857</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665364</v>
+        <v>665446</v>
       </c>
       <c r="R52" t="n">
-        <v>6564665</v>
+        <v>6564659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150627</v>
+        <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92287</v>
+        <v>92857</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665419</v>
+        <v>665364</v>
       </c>
       <c r="R53" t="n">
-        <v>6564672</v>
+        <v>6564665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6528,32 +6528,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150557</v>
+        <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>91546</v>
+        <v>92287</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>1958</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665183</v>
+        <v>665455</v>
       </c>
       <c r="R57" t="n">
-        <v>6564505</v>
+        <v>6564681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,7 +6635,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150628</v>
+        <v>129150626</v>
       </c>
       <c r="B58" t="n">
         <v>92287</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665455</v>
+        <v>665260</v>
       </c>
       <c r="R58" t="n">
-        <v>6564681</v>
+        <v>6564773</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150626</v>
+        <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>92287</v>
+        <v>91546</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1958</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665260</v>
+        <v>665183</v>
       </c>
       <c r="R59" t="n">
-        <v>6564773</v>
+        <v>6564505</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6956,32 +6956,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150583</v>
+        <v>129150619</v>
       </c>
       <c r="B61" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665372</v>
+        <v>665365</v>
       </c>
       <c r="R61" t="n">
-        <v>6564721</v>
+        <v>6564786</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,7 +7063,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B62" t="n">
         <v>92857</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R62" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150619</v>
+        <v>129150566</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665365</v>
+        <v>665194</v>
       </c>
       <c r="R63" t="n">
-        <v>6564786</v>
+        <v>6564498</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8244,32 +8244,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150622</v>
+        <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665194</v>
+        <v>665640</v>
       </c>
       <c r="R73" t="n">
-        <v>6564740</v>
+        <v>6564667</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,7 +8351,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B74" t="n">
         <v>92857</v>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R74" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8458,32 +8458,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150609</v>
+        <v>129150622</v>
       </c>
       <c r="B75" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665505</v>
+        <v>665194</v>
       </c>
       <c r="R75" t="n">
-        <v>6564674</v>
+        <v>6564740</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970274</v>
+        <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665452</v>
+        <v>665424</v>
       </c>
       <c r="R5" t="n">
-        <v>6565050</v>
+        <v>6565096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970265</v>
+        <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92845</v>
+        <v>92857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665424</v>
+        <v>665452</v>
       </c>
       <c r="R6" t="n">
-        <v>6565096</v>
+        <v>6565050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,7 +1226,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128970270</v>
+        <v>128970269</v>
       </c>
       <c r="B7" t="n">
         <v>92857</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665540</v>
+        <v>665528</v>
       </c>
       <c r="R7" t="n">
-        <v>6564894</v>
+        <v>6564890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,7 +1333,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128970269</v>
+        <v>128970270</v>
       </c>
       <c r="B8" t="n">
         <v>92857</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665528</v>
+        <v>665540</v>
       </c>
       <c r="R8" t="n">
-        <v>6564890</v>
+        <v>6564894</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128970273</v>
+        <v>128970264</v>
       </c>
       <c r="B14" t="n">
-        <v>92857</v>
+        <v>91546</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665465</v>
+        <v>665464</v>
       </c>
       <c r="R14" t="n">
-        <v>6565043</v>
+        <v>6565020</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128970264</v>
+        <v>128970273</v>
       </c>
       <c r="B15" t="n">
-        <v>91546</v>
+        <v>92857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665464</v>
+        <v>665465</v>
       </c>
       <c r="R15" t="n">
-        <v>6565020</v>
+        <v>6565043</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,7 +2189,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128970272</v>
+        <v>128970278</v>
       </c>
       <c r="B16" t="n">
         <v>92857</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665504</v>
+        <v>665427</v>
       </c>
       <c r="R16" t="n">
-        <v>6564970</v>
+        <v>6565093</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128970278</v>
+        <v>128970272</v>
       </c>
       <c r="B17" t="n">
         <v>92857</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665427</v>
+        <v>665504</v>
       </c>
       <c r="R17" t="n">
-        <v>6565093</v>
+        <v>6564970</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3211,7 +3211,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150574</v>
+        <v>129150586</v>
       </c>
       <c r="B26" t="n">
         <v>92857</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665437</v>
+        <v>665436</v>
       </c>
       <c r="R26" t="n">
-        <v>6564617</v>
+        <v>6564778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,7 +3318,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150586</v>
+        <v>129150574</v>
       </c>
       <c r="B27" t="n">
         <v>92857</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665436</v>
+        <v>665437</v>
       </c>
       <c r="R27" t="n">
-        <v>6564778</v>
+        <v>6564617</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150617</v>
+        <v>129150569</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665376</v>
+        <v>665388</v>
       </c>
       <c r="R40" t="n">
-        <v>6564598</v>
+        <v>6564531</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150616</v>
+        <v>129150590</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665382</v>
+        <v>665331</v>
       </c>
       <c r="R41" t="n">
-        <v>6564609</v>
+        <v>6564765</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150569</v>
+        <v>129150602</v>
       </c>
       <c r="B43" t="n">
         <v>92857</v>
@@ -5068,7 +5068,7 @@
         <v>665388</v>
       </c>
       <c r="R43" t="n">
-        <v>6564531</v>
+        <v>6564663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150590</v>
+        <v>129150606</v>
       </c>
       <c r="B44" t="n">
         <v>92857</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665331</v>
+        <v>665503</v>
       </c>
       <c r="R44" t="n">
-        <v>6564765</v>
+        <v>6564692</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5244,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150602</v>
+        <v>129150612</v>
       </c>
       <c r="B45" t="n">
         <v>92857</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665388</v>
+        <v>665587</v>
       </c>
       <c r="R45" t="n">
-        <v>6564663</v>
+        <v>6564768</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150606</v>
+        <v>129150617</v>
       </c>
       <c r="B46" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665503</v>
+        <v>665376</v>
       </c>
       <c r="R46" t="n">
-        <v>6564692</v>
+        <v>6564598</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150612</v>
+        <v>129150616</v>
       </c>
       <c r="B47" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665587</v>
+        <v>665382</v>
       </c>
       <c r="R47" t="n">
-        <v>6564768</v>
+        <v>6564609</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5565,32 +5565,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129150621</v>
+        <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665321</v>
+        <v>665276</v>
       </c>
       <c r="R48" t="n">
-        <v>6564753</v>
+        <v>6564529</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,32 +5672,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129150568</v>
+        <v>129150621</v>
       </c>
       <c r="B49" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665276</v>
+        <v>665321</v>
       </c>
       <c r="R49" t="n">
-        <v>6564529</v>
+        <v>6564753</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150627</v>
+        <v>129150601</v>
       </c>
       <c r="B50" t="n">
-        <v>92287</v>
+        <v>92857</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665419</v>
+        <v>665364</v>
       </c>
       <c r="R50" t="n">
-        <v>6564672</v>
+        <v>6564665</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,32 +5886,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150627</v>
       </c>
       <c r="B51" t="n">
-        <v>92857</v>
+        <v>92287</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665419</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564672</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B52" t="n">
         <v>92857</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R52" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,7 +6100,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150601</v>
+        <v>129150577</v>
       </c>
       <c r="B53" t="n">
         <v>92857</v>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665364</v>
+        <v>665446</v>
       </c>
       <c r="R53" t="n">
-        <v>6564665</v>
+        <v>6564659</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6207,7 +6207,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150570</v>
+        <v>129150591</v>
       </c>
       <c r="B54" t="n">
         <v>92857</v>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665399</v>
+        <v>665318</v>
       </c>
       <c r="R54" t="n">
-        <v>6564537</v>
+        <v>6564762</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,7 +6314,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150591</v>
+        <v>129150580</v>
       </c>
       <c r="B55" t="n">
         <v>92857</v>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665318</v>
+        <v>665374</v>
       </c>
       <c r="R55" t="n">
-        <v>6564762</v>
+        <v>6564595</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6421,7 +6421,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129150580</v>
+        <v>129150570</v>
       </c>
       <c r="B56" t="n">
         <v>92857</v>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665374</v>
+        <v>665399</v>
       </c>
       <c r="R56" t="n">
-        <v>6564595</v>
+        <v>6564537</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6956,32 +6956,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150619</v>
+        <v>129150566</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>92857</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665365</v>
+        <v>665194</v>
       </c>
       <c r="R61" t="n">
-        <v>6564786</v>
+        <v>6564498</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,32 +7063,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150583</v>
+        <v>129150619</v>
       </c>
       <c r="B62" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665372</v>
+        <v>665365</v>
       </c>
       <c r="R62" t="n">
-        <v>6564721</v>
+        <v>6564786</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,7 +7170,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B63" t="n">
         <v>92857</v>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R63" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7277,7 +7277,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129150594</v>
+        <v>129150598</v>
       </c>
       <c r="B64" t="n">
         <v>92857</v>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>665232</v>
+        <v>665283</v>
       </c>
       <c r="R64" t="n">
-        <v>6564745</v>
+        <v>6564685</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7384,7 +7384,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129150598</v>
+        <v>129150593</v>
       </c>
       <c r="B65" t="n">
         <v>92857</v>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>665283</v>
+        <v>665256</v>
       </c>
       <c r="R65" t="n">
-        <v>6564685</v>
+        <v>6564756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,7 +7491,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150593</v>
+        <v>129150605</v>
       </c>
       <c r="B66" t="n">
         <v>92857</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665256</v>
+        <v>665484</v>
       </c>
       <c r="R66" t="n">
-        <v>6564756</v>
+        <v>6564691</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7598,7 +7598,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129150605</v>
+        <v>129150594</v>
       </c>
       <c r="B67" t="n">
         <v>92857</v>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>665484</v>
+        <v>665232</v>
       </c>
       <c r="R67" t="n">
-        <v>6564691</v>
+        <v>6564745</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7705,32 +7705,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150613</v>
+        <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92857</v>
+        <v>92287</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665566</v>
+        <v>665422</v>
       </c>
       <c r="R68" t="n">
-        <v>6564813</v>
+        <v>6564565</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7812,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150625</v>
+        <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92287</v>
+        <v>92857</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665422</v>
+        <v>665566</v>
       </c>
       <c r="R69" t="n">
-        <v>6564565</v>
+        <v>6564813</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150572</v>
+        <v>129150607</v>
       </c>
       <c r="B76" t="n">
         <v>92857</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665424</v>
+        <v>665514</v>
       </c>
       <c r="R76" t="n">
-        <v>6564571</v>
+        <v>6564684</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150607</v>
+        <v>129150600</v>
       </c>
       <c r="B77" t="n">
         <v>92857</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665514</v>
+        <v>665346</v>
       </c>
       <c r="R77" t="n">
-        <v>6564684</v>
+        <v>6564670</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150581</v>
+        <v>129150597</v>
       </c>
       <c r="B78" t="n">
         <v>92857</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665366</v>
+        <v>665233</v>
       </c>
       <c r="R78" t="n">
-        <v>6564608</v>
+        <v>6564718</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,32 +8886,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150600</v>
+        <v>129150629</v>
       </c>
       <c r="B79" t="n">
-        <v>92857</v>
+        <v>92287</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665346</v>
+        <v>665507</v>
       </c>
       <c r="R79" t="n">
-        <v>6564670</v>
+        <v>6564685</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,7 +8993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150589</v>
+        <v>129150572</v>
       </c>
       <c r="B80" t="n">
         <v>92857</v>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665371</v>
+        <v>665424</v>
       </c>
       <c r="R80" t="n">
-        <v>6564789</v>
+        <v>6564571</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150597</v>
+        <v>129150581</v>
       </c>
       <c r="B81" t="n">
         <v>92857</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665233</v>
+        <v>665366</v>
       </c>
       <c r="R81" t="n">
-        <v>6564718</v>
+        <v>6564608</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150629</v>
+        <v>129150589</v>
       </c>
       <c r="B82" t="n">
-        <v>92287</v>
+        <v>92857</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665507</v>
+        <v>665371</v>
       </c>
       <c r="R82" t="n">
-        <v>6564685</v>
+        <v>6564789</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92845</v>
+        <v>92852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128970269</v>
+        <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665528</v>
+        <v>665540</v>
       </c>
       <c r="R7" t="n">
-        <v>6564890</v>
+        <v>6564894</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128970270</v>
+        <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665540</v>
+        <v>665528</v>
       </c>
       <c r="R8" t="n">
-        <v>6564894</v>
+        <v>6564890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128970264</v>
       </c>
       <c r="B14" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>128970273</v>
       </c>
       <c r="B15" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128970278</v>
+        <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665427</v>
+        <v>665504</v>
       </c>
       <c r="R16" t="n">
-        <v>6565093</v>
+        <v>6564970</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128970272</v>
+        <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665504</v>
+        <v>665427</v>
       </c>
       <c r="R17" t="n">
-        <v>6564970</v>
+        <v>6565093</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>129052185</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>129107649</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150586</v>
+        <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665436</v>
+        <v>665437</v>
       </c>
       <c r="R26" t="n">
-        <v>6564778</v>
+        <v>6564617</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150574</v>
+        <v>129150586</v>
       </c>
       <c r="B27" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665437</v>
+        <v>665436</v>
       </c>
       <c r="R27" t="n">
-        <v>6564617</v>
+        <v>6564778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,7 +3428,7 @@
         <v>129150585</v>
       </c>
       <c r="B28" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>129150596</v>
       </c>
       <c r="B29" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>129150599</v>
       </c>
       <c r="B36" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>129150578</v>
       </c>
       <c r="B37" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4709,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150569</v>
+        <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665388</v>
+        <v>665408</v>
       </c>
       <c r="R40" t="n">
-        <v>6564531</v>
+        <v>6564551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150590</v>
+        <v>129150569</v>
       </c>
       <c r="B41" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665331</v>
+        <v>665388</v>
       </c>
       <c r="R41" t="n">
-        <v>6564765</v>
+        <v>6564531</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4923,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150571</v>
+        <v>129150590</v>
       </c>
       <c r="B42" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665408</v>
+        <v>665331</v>
       </c>
       <c r="R42" t="n">
-        <v>6564551</v>
+        <v>6564765</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5033,7 +5033,7 @@
         <v>129150602</v>
       </c>
       <c r="B43" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>129150606</v>
       </c>
       <c r="B44" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>129150612</v>
       </c>
       <c r="B45" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150601</v>
+        <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92857</v>
+        <v>92294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665364</v>
+        <v>665419</v>
       </c>
       <c r="R50" t="n">
-        <v>6564665</v>
+        <v>6564672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,32 +5886,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150627</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
-        <v>92287</v>
+        <v>92864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665419</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564672</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B52" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R52" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,10 +6100,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150577</v>
+        <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665446</v>
+        <v>665364</v>
       </c>
       <c r="R53" t="n">
-        <v>6564659</v>
+        <v>6564665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6210,7 +6210,7 @@
         <v>129150591</v>
       </c>
       <c r="B54" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>92287</v>
+        <v>92294</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>92287</v>
+        <v>92294</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R61" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,32 +7063,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150619</v>
+        <v>129150566</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>92864</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665365</v>
+        <v>665194</v>
       </c>
       <c r="R62" t="n">
-        <v>6564786</v>
+        <v>6564498</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150583</v>
+        <v>129150619</v>
       </c>
       <c r="B63" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665372</v>
+        <v>665365</v>
       </c>
       <c r="R63" t="n">
-        <v>6564721</v>
+        <v>6564786</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7277,10 +7277,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129150598</v>
+        <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>665283</v>
+        <v>665232</v>
       </c>
       <c r="R64" t="n">
-        <v>6564685</v>
+        <v>6564745</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7384,10 +7384,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129150593</v>
+        <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>665256</v>
+        <v>665283</v>
       </c>
       <c r="R65" t="n">
-        <v>6564756</v>
+        <v>6564685</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,10 +7491,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150605</v>
+        <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665484</v>
+        <v>665256</v>
       </c>
       <c r="R66" t="n">
-        <v>6564691</v>
+        <v>6564756</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7598,10 +7598,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129150594</v>
+        <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>665232</v>
+        <v>665484</v>
       </c>
       <c r="R67" t="n">
-        <v>6564745</v>
+        <v>6564691</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7708,7 +7708,7 @@
         <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92287</v>
+        <v>92294</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>129150556</v>
       </c>
       <c r="B72" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8244,32 +8244,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150610</v>
+        <v>129150622</v>
       </c>
       <c r="B73" t="n">
-        <v>92857</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665640</v>
+        <v>665194</v>
       </c>
       <c r="R73" t="n">
-        <v>6564667</v>
+        <v>6564740</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150609</v>
+        <v>129150610</v>
       </c>
       <c r="B74" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665505</v>
+        <v>665640</v>
       </c>
       <c r="R74" t="n">
-        <v>6564674</v>
+        <v>6564667</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8458,32 +8458,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150622</v>
+        <v>129150609</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>92864</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665194</v>
+        <v>665505</v>
       </c>
       <c r="R75" t="n">
-        <v>6564740</v>
+        <v>6564674</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150607</v>
+        <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92857</v>
+        <v>92294</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665514</v>
+        <v>665507</v>
       </c>
       <c r="R76" t="n">
-        <v>6564684</v>
+        <v>6564685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150600</v>
+        <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665346</v>
+        <v>665424</v>
       </c>
       <c r="R77" t="n">
-        <v>6564670</v>
+        <v>6564571</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150597</v>
+        <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665233</v>
+        <v>665514</v>
       </c>
       <c r="R78" t="n">
-        <v>6564718</v>
+        <v>6564684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,32 +8886,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150629</v>
+        <v>129150581</v>
       </c>
       <c r="B79" t="n">
-        <v>92287</v>
+        <v>92864</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665507</v>
+        <v>665366</v>
       </c>
       <c r="R79" t="n">
-        <v>6564685</v>
+        <v>6564608</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150572</v>
+        <v>129150600</v>
       </c>
       <c r="B80" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665424</v>
+        <v>665346</v>
       </c>
       <c r="R80" t="n">
-        <v>6564571</v>
+        <v>6564670</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,10 +9100,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150581</v>
+        <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665366</v>
+        <v>665371</v>
       </c>
       <c r="R81" t="n">
-        <v>6564608</v>
+        <v>6564789</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,10 +9207,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150589</v>
+        <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665371</v>
+        <v>665233</v>
       </c>
       <c r="R82" t="n">
-        <v>6564789</v>
+        <v>6564718</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9317,7 +9317,7 @@
         <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129150623</v>
+        <v>129150615</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>665233</v>
+        <v>665164</v>
       </c>
       <c r="R86" t="n">
-        <v>6564720</v>
+        <v>6564505</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9742,7 +9742,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129150615</v>
+        <v>129150623</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>665164</v>
+        <v>665233</v>
       </c>
       <c r="R87" t="n">
-        <v>6564505</v>
+        <v>6564720</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150629</v>
+        <v>129150572</v>
       </c>
       <c r="B76" t="n">
-        <v>92294</v>
+        <v>92864</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665507</v>
+        <v>665424</v>
       </c>
       <c r="R76" t="n">
-        <v>6564685</v>
+        <v>6564571</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,32 +8672,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150572</v>
+        <v>129150629</v>
       </c>
       <c r="B77" t="n">
-        <v>92864</v>
+        <v>92294</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665424</v>
+        <v>665507</v>
       </c>
       <c r="R77" t="n">
-        <v>6564571</v>
+        <v>6564685</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970265</v>
+        <v>128970274</v>
       </c>
       <c r="B5" t="n">
-        <v>92852</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665424</v>
+        <v>665452</v>
       </c>
       <c r="R5" t="n">
-        <v>6565096</v>
+        <v>6565050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970274</v>
+        <v>128970265</v>
       </c>
       <c r="B6" t="n">
-        <v>92864</v>
+        <v>92859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665452</v>
+        <v>665424</v>
       </c>
       <c r="R6" t="n">
-        <v>6565050</v>
+        <v>6565096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128970264</v>
+        <v>128970273</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>92871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665464</v>
+        <v>665465</v>
       </c>
       <c r="R14" t="n">
-        <v>6565020</v>
+        <v>6565043</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128970273</v>
+        <v>128970264</v>
       </c>
       <c r="B15" t="n">
-        <v>92864</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665465</v>
+        <v>665464</v>
       </c>
       <c r="R15" t="n">
-        <v>6565043</v>
+        <v>6565020</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129150586</v>
       </c>
       <c r="B27" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>129150585</v>
       </c>
       <c r="B28" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>129150596</v>
       </c>
       <c r="B29" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150604</v>
+        <v>129150620</v>
       </c>
       <c r="B35" t="n">
-        <v>92864</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665464</v>
+        <v>665358</v>
       </c>
       <c r="R35" t="n">
-        <v>6564686</v>
+        <v>6564768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150599</v>
+        <v>129150604</v>
       </c>
       <c r="B36" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665294</v>
+        <v>665464</v>
       </c>
       <c r="R36" t="n">
-        <v>6564670</v>
+        <v>6564686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B37" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R37" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150567</v>
+        <v>129150578</v>
       </c>
       <c r="B38" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665228</v>
+        <v>665443</v>
       </c>
       <c r="R38" t="n">
-        <v>6564499</v>
+        <v>6564659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150620</v>
+        <v>129150567</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92871</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665358</v>
+        <v>665228</v>
       </c>
       <c r="R39" t="n">
-        <v>6564768</v>
+        <v>6564499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4712,7 +4712,7 @@
         <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>129150569</v>
       </c>
       <c r="B41" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>129150590</v>
       </c>
       <c r="B42" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>129150602</v>
       </c>
       <c r="B43" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>129150606</v>
       </c>
       <c r="B44" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>129150612</v>
       </c>
       <c r="B45" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150627</v>
+        <v>129150611</v>
       </c>
       <c r="B50" t="n">
-        <v>92294</v>
+        <v>92871</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665419</v>
+        <v>665607</v>
       </c>
       <c r="R50" t="n">
-        <v>6564672</v>
+        <v>6564770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B51" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150577</v>
+        <v>129150601</v>
       </c>
       <c r="B52" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665446</v>
+        <v>665364</v>
       </c>
       <c r="R52" t="n">
-        <v>6564659</v>
+        <v>6564665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150601</v>
+        <v>129150627</v>
       </c>
       <c r="B53" t="n">
-        <v>92864</v>
+        <v>92301</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665364</v>
+        <v>665419</v>
       </c>
       <c r="R53" t="n">
-        <v>6564665</v>
+        <v>6564672</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6210,7 +6210,7 @@
         <v>129150591</v>
       </c>
       <c r="B54" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6528,32 +6528,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150628</v>
+        <v>129150557</v>
       </c>
       <c r="B57" t="n">
-        <v>92294</v>
+        <v>91560</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1958</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665455</v>
+        <v>665183</v>
       </c>
       <c r="R57" t="n">
-        <v>6564681</v>
+        <v>6564505</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,10 +6635,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150626</v>
+        <v>129150628</v>
       </c>
       <c r="B58" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665260</v>
+        <v>665455</v>
       </c>
       <c r="R58" t="n">
-        <v>6564773</v>
+        <v>6564681</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150557</v>
+        <v>129150626</v>
       </c>
       <c r="B59" t="n">
-        <v>91553</v>
+        <v>92301</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>1958</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665183</v>
+        <v>665260</v>
       </c>
       <c r="R59" t="n">
-        <v>6564505</v>
+        <v>6564773</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6959,7 +6959,7 @@
         <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>129150566</v>
       </c>
       <c r="B62" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8244,32 +8244,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150622</v>
+        <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>92871</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665194</v>
+        <v>665640</v>
       </c>
       <c r="R73" t="n">
-        <v>6564740</v>
+        <v>6564667</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R74" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8458,32 +8458,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150609</v>
+        <v>129150622</v>
       </c>
       <c r="B75" t="n">
-        <v>92864</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665505</v>
+        <v>665194</v>
       </c>
       <c r="R75" t="n">
-        <v>6564674</v>
+        <v>6564740</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150572</v>
+        <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92864</v>
+        <v>92301</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665424</v>
+        <v>665507</v>
       </c>
       <c r="R76" t="n">
-        <v>6564571</v>
+        <v>6564685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,32 +8672,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150629</v>
+        <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92294</v>
+        <v>92871</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665507</v>
+        <v>665424</v>
       </c>
       <c r="R77" t="n">
-        <v>6564685</v>
+        <v>6564571</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8782,7 +8782,7 @@
         <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>129150581</v>
       </c>
       <c r="B79" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>129150600</v>
       </c>
       <c r="B80" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129150615</v>
+        <v>129150623</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>665164</v>
+        <v>665233</v>
       </c>
       <c r="R86" t="n">
-        <v>6564505</v>
+        <v>6564720</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9742,7 +9742,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129150623</v>
+        <v>129150615</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>665233</v>
+        <v>665164</v>
       </c>
       <c r="R87" t="n">
-        <v>6564720</v>
+        <v>6564505</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970274</v>
+        <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665452</v>
+        <v>665424</v>
       </c>
       <c r="R5" t="n">
-        <v>6565050</v>
+        <v>6565096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970265</v>
+        <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92859</v>
+        <v>92873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665424</v>
+        <v>665452</v>
       </c>
       <c r="R6" t="n">
-        <v>6565096</v>
+        <v>6565050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128970273</v>
+        <v>128970264</v>
       </c>
       <c r="B14" t="n">
-        <v>92871</v>
+        <v>91562</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665465</v>
+        <v>665464</v>
       </c>
       <c r="R14" t="n">
-        <v>6565043</v>
+        <v>6565020</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128970264</v>
+        <v>128970273</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>92873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665464</v>
+        <v>665465</v>
       </c>
       <c r="R15" t="n">
-        <v>6565020</v>
+        <v>6565043</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>129052185</v>
       </c>
       <c r="B19" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>129107649</v>
       </c>
       <c r="B25" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129150586</v>
       </c>
       <c r="B27" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>129150585</v>
       </c>
       <c r="B28" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>129150596</v>
       </c>
       <c r="B29" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150620</v>
+        <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665358</v>
+        <v>665464</v>
       </c>
       <c r="R35" t="n">
-        <v>6564768</v>
+        <v>6564686</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150604</v>
+        <v>129150599</v>
       </c>
       <c r="B36" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665464</v>
+        <v>665294</v>
       </c>
       <c r="R36" t="n">
-        <v>6564686</v>
+        <v>6564670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150599</v>
+        <v>129150578</v>
       </c>
       <c r="B37" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665294</v>
+        <v>665443</v>
       </c>
       <c r="R37" t="n">
-        <v>6564670</v>
+        <v>6564659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150578</v>
+        <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665443</v>
+        <v>665228</v>
       </c>
       <c r="R38" t="n">
-        <v>6564659</v>
+        <v>6564499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150567</v>
+        <v>129150620</v>
       </c>
       <c r="B39" t="n">
-        <v>92871</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665228</v>
+        <v>665358</v>
       </c>
       <c r="R39" t="n">
-        <v>6564499</v>
+        <v>6564768</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4712,7 +4712,7 @@
         <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>129150569</v>
       </c>
       <c r="B41" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>129150590</v>
       </c>
       <c r="B42" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>129150602</v>
       </c>
       <c r="B43" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>129150606</v>
       </c>
       <c r="B44" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>129150612</v>
       </c>
       <c r="B45" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150611</v>
+        <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92871</v>
+        <v>92303</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665607</v>
+        <v>665419</v>
       </c>
       <c r="R50" t="n">
-        <v>6564770</v>
+        <v>6564672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150601</v>
+        <v>129150577</v>
       </c>
       <c r="B52" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665364</v>
+        <v>665446</v>
       </c>
       <c r="R52" t="n">
-        <v>6564665</v>
+        <v>6564659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150627</v>
+        <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92301</v>
+        <v>92873</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665419</v>
+        <v>665364</v>
       </c>
       <c r="R53" t="n">
-        <v>6564672</v>
+        <v>6564665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6210,7 +6210,7 @@
         <v>129150591</v>
       </c>
       <c r="B54" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6528,32 +6528,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150557</v>
+        <v>129150618</v>
       </c>
       <c r="B57" t="n">
-        <v>91560</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665183</v>
+        <v>665400</v>
       </c>
       <c r="R57" t="n">
-        <v>6564505</v>
+        <v>6564742</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6638,7 +6638,7 @@
         <v>129150628</v>
       </c>
       <c r="B58" t="n">
-        <v>92301</v>
+        <v>92303</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>129150626</v>
       </c>
       <c r="B59" t="n">
-        <v>92301</v>
+        <v>92303</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6849,32 +6849,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150618</v>
+        <v>129150557</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>91562</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665400</v>
+        <v>665183</v>
       </c>
       <c r="R60" t="n">
-        <v>6564742</v>
+        <v>6564505</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6959,7 +6959,7 @@
         <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>129150566</v>
       </c>
       <c r="B62" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92301</v>
+        <v>92303</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>129150556</v>
       </c>
       <c r="B72" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150629</v>
+        <v>129150572</v>
       </c>
       <c r="B76" t="n">
-        <v>92301</v>
+        <v>92873</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665507</v>
+        <v>665424</v>
       </c>
       <c r="R76" t="n">
-        <v>6564685</v>
+        <v>6564571</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150572</v>
+        <v>129150607</v>
       </c>
       <c r="B77" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665424</v>
+        <v>665514</v>
       </c>
       <c r="R77" t="n">
-        <v>6564571</v>
+        <v>6564684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150607</v>
+        <v>129150581</v>
       </c>
       <c r="B78" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665514</v>
+        <v>665366</v>
       </c>
       <c r="R78" t="n">
-        <v>6564684</v>
+        <v>6564608</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150581</v>
+        <v>129150600</v>
       </c>
       <c r="B79" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665366</v>
+        <v>665346</v>
       </c>
       <c r="R79" t="n">
-        <v>6564608</v>
+        <v>6564670</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150600</v>
+        <v>129150589</v>
       </c>
       <c r="B80" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665346</v>
+        <v>665371</v>
       </c>
       <c r="R80" t="n">
-        <v>6564670</v>
+        <v>6564789</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,10 +9100,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150589</v>
+        <v>129150597</v>
       </c>
       <c r="B81" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665371</v>
+        <v>665233</v>
       </c>
       <c r="R81" t="n">
-        <v>6564789</v>
+        <v>6564718</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150597</v>
+        <v>129150629</v>
       </c>
       <c r="B82" t="n">
-        <v>92871</v>
+        <v>92303</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665233</v>
+        <v>665507</v>
       </c>
       <c r="R82" t="n">
-        <v>6564718</v>
+        <v>6564685</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9317,7 +9317,7 @@
         <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150604</v>
+        <v>129150620</v>
       </c>
       <c r="B35" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665464</v>
+        <v>665358</v>
       </c>
       <c r="R35" t="n">
-        <v>6564686</v>
+        <v>6564768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150599</v>
+        <v>129150604</v>
       </c>
       <c r="B36" t="n">
         <v>92873</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665294</v>
+        <v>665464</v>
       </c>
       <c r="R36" t="n">
-        <v>6564670</v>
+        <v>6564686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B37" t="n">
         <v>92873</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R37" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150567</v>
+        <v>129150578</v>
       </c>
       <c r="B38" t="n">
         <v>92873</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665228</v>
+        <v>665443</v>
       </c>
       <c r="R38" t="n">
-        <v>6564499</v>
+        <v>6564659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150620</v>
+        <v>129150567</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665358</v>
+        <v>665228</v>
       </c>
       <c r="R39" t="n">
-        <v>6564768</v>
+        <v>6564499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150571</v>
+        <v>129150616</v>
       </c>
       <c r="B40" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665408</v>
+        <v>665382</v>
       </c>
       <c r="R40" t="n">
-        <v>6564551</v>
+        <v>6564609</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,7 +4816,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150569</v>
+        <v>129150571</v>
       </c>
       <c r="B41" t="n">
         <v>92873</v>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665388</v>
+        <v>665408</v>
       </c>
       <c r="R41" t="n">
-        <v>6564531</v>
+        <v>6564551</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150590</v>
+        <v>129150569</v>
       </c>
       <c r="B42" t="n">
         <v>92873</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665331</v>
+        <v>665388</v>
       </c>
       <c r="R42" t="n">
-        <v>6564765</v>
+        <v>6564531</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150602</v>
+        <v>129150590</v>
       </c>
       <c r="B43" t="n">
         <v>92873</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665388</v>
+        <v>665331</v>
       </c>
       <c r="R43" t="n">
-        <v>6564663</v>
+        <v>6564765</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150606</v>
+        <v>129150602</v>
       </c>
       <c r="B44" t="n">
         <v>92873</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R44" t="n">
-        <v>6564692</v>
+        <v>6564663</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5244,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150612</v>
+        <v>129150606</v>
       </c>
       <c r="B45" t="n">
         <v>92873</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665587</v>
+        <v>665503</v>
       </c>
       <c r="R45" t="n">
-        <v>6564768</v>
+        <v>6564692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150617</v>
+        <v>129150612</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665376</v>
+        <v>665587</v>
       </c>
       <c r="R46" t="n">
-        <v>6564598</v>
+        <v>6564768</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,7 +5458,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150616</v>
+        <v>129150617</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665382</v>
+        <v>665376</v>
       </c>
       <c r="R47" t="n">
-        <v>6564609</v>
+        <v>6564598</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150572</v>
+        <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92873</v>
+        <v>92303</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665424</v>
+        <v>665507</v>
       </c>
       <c r="R76" t="n">
-        <v>6564571</v>
+        <v>6564685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150607</v>
+        <v>129150572</v>
       </c>
       <c r="B77" t="n">
         <v>92873</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665514</v>
+        <v>665424</v>
       </c>
       <c r="R77" t="n">
-        <v>6564684</v>
+        <v>6564571</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150581</v>
+        <v>129150607</v>
       </c>
       <c r="B78" t="n">
         <v>92873</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665366</v>
+        <v>665514</v>
       </c>
       <c r="R78" t="n">
-        <v>6564608</v>
+        <v>6564684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150600</v>
+        <v>129150581</v>
       </c>
       <c r="B79" t="n">
         <v>92873</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665346</v>
+        <v>665366</v>
       </c>
       <c r="R79" t="n">
-        <v>6564670</v>
+        <v>6564608</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,7 +8993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150589</v>
+        <v>129150600</v>
       </c>
       <c r="B80" t="n">
         <v>92873</v>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665371</v>
+        <v>665346</v>
       </c>
       <c r="R80" t="n">
-        <v>6564789</v>
+        <v>6564670</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150597</v>
+        <v>129150589</v>
       </c>
       <c r="B81" t="n">
         <v>92873</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665233</v>
+        <v>665371</v>
       </c>
       <c r="R81" t="n">
-        <v>6564718</v>
+        <v>6564789</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150629</v>
+        <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92303</v>
+        <v>92873</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665507</v>
+        <v>665233</v>
       </c>
       <c r="R82" t="n">
-        <v>6564685</v>
+        <v>6564718</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150571</v>
+        <v>129150617</v>
       </c>
       <c r="B41" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665408</v>
+        <v>665376</v>
       </c>
       <c r="R41" t="n">
-        <v>6564551</v>
+        <v>6564598</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150569</v>
+        <v>129150571</v>
       </c>
       <c r="B42" t="n">
         <v>92873</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665388</v>
+        <v>665408</v>
       </c>
       <c r="R42" t="n">
-        <v>6564531</v>
+        <v>6564551</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150590</v>
+        <v>129150569</v>
       </c>
       <c r="B43" t="n">
         <v>92873</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665331</v>
+        <v>665388</v>
       </c>
       <c r="R43" t="n">
-        <v>6564765</v>
+        <v>6564531</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150602</v>
+        <v>129150590</v>
       </c>
       <c r="B44" t="n">
         <v>92873</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665388</v>
+        <v>665331</v>
       </c>
       <c r="R44" t="n">
-        <v>6564663</v>
+        <v>6564765</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5244,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150606</v>
+        <v>129150602</v>
       </c>
       <c r="B45" t="n">
         <v>92873</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R45" t="n">
-        <v>6564692</v>
+        <v>6564663</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,7 +5351,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150612</v>
+        <v>129150606</v>
       </c>
       <c r="B46" t="n">
         <v>92873</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665587</v>
+        <v>665503</v>
       </c>
       <c r="R46" t="n">
-        <v>6564768</v>
+        <v>6564692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150617</v>
+        <v>129150612</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665376</v>
+        <v>665587</v>
       </c>
       <c r="R47" t="n">
-        <v>6564598</v>
+        <v>6564768</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150627</v>
+        <v>129150611</v>
       </c>
       <c r="B50" t="n">
-        <v>92303</v>
+        <v>92873</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665419</v>
+        <v>665607</v>
       </c>
       <c r="R50" t="n">
-        <v>6564672</v>
+        <v>6564770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B51" t="n">
         <v>92873</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150577</v>
+        <v>129150601</v>
       </c>
       <c r="B52" t="n">
         <v>92873</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665446</v>
+        <v>665364</v>
       </c>
       <c r="R52" t="n">
-        <v>6564659</v>
+        <v>6564665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150601</v>
+        <v>129150627</v>
       </c>
       <c r="B53" t="n">
-        <v>92873</v>
+        <v>92303</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665364</v>
+        <v>665419</v>
       </c>
       <c r="R53" t="n">
-        <v>6564665</v>
+        <v>6564672</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150629</v>
+        <v>129150572</v>
       </c>
       <c r="B76" t="n">
-        <v>92303</v>
+        <v>92873</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665507</v>
+        <v>665424</v>
       </c>
       <c r="R76" t="n">
-        <v>6564685</v>
+        <v>6564571</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150572</v>
+        <v>129150607</v>
       </c>
       <c r="B77" t="n">
         <v>92873</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665424</v>
+        <v>665514</v>
       </c>
       <c r="R77" t="n">
-        <v>6564571</v>
+        <v>6564684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150607</v>
+        <v>129150581</v>
       </c>
       <c r="B78" t="n">
         <v>92873</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665514</v>
+        <v>665366</v>
       </c>
       <c r="R78" t="n">
-        <v>6564684</v>
+        <v>6564608</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150581</v>
+        <v>129150600</v>
       </c>
       <c r="B79" t="n">
         <v>92873</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665366</v>
+        <v>665346</v>
       </c>
       <c r="R79" t="n">
-        <v>6564608</v>
+        <v>6564670</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,7 +8993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150600</v>
+        <v>129150589</v>
       </c>
       <c r="B80" t="n">
         <v>92873</v>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665346</v>
+        <v>665371</v>
       </c>
       <c r="R80" t="n">
-        <v>6564670</v>
+        <v>6564789</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150589</v>
+        <v>129150597</v>
       </c>
       <c r="B81" t="n">
         <v>92873</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665371</v>
+        <v>665233</v>
       </c>
       <c r="R81" t="n">
-        <v>6564789</v>
+        <v>6564718</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150597</v>
+        <v>129150629</v>
       </c>
       <c r="B82" t="n">
-        <v>92873</v>
+        <v>92303</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665233</v>
+        <v>665507</v>
       </c>
       <c r="R82" t="n">
-        <v>6564718</v>
+        <v>6564685</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92861</v>
+        <v>92847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128970264</v>
+        <v>128970273</v>
       </c>
       <c r="B14" t="n">
-        <v>91562</v>
+        <v>92859</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665464</v>
+        <v>665465</v>
       </c>
       <c r="R14" t="n">
-        <v>6565020</v>
+        <v>6565043</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128970273</v>
+        <v>128970264</v>
       </c>
       <c r="B15" t="n">
-        <v>92873</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665465</v>
+        <v>665464</v>
       </c>
       <c r="R15" t="n">
-        <v>6565043</v>
+        <v>6565020</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150586</v>
+        <v>129150585</v>
       </c>
       <c r="B27" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665436</v>
+        <v>665424</v>
       </c>
       <c r="R27" t="n">
-        <v>6564778</v>
+        <v>6564786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150585</v>
+        <v>129150596</v>
       </c>
       <c r="B28" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665424</v>
+        <v>665174</v>
       </c>
       <c r="R28" t="n">
-        <v>6564786</v>
+        <v>6564743</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150596</v>
+        <v>129150586</v>
       </c>
       <c r="B29" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665174</v>
+        <v>665436</v>
       </c>
       <c r="R29" t="n">
-        <v>6564743</v>
+        <v>6564778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150620</v>
+        <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>92859</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665358</v>
+        <v>665464</v>
       </c>
       <c r="R35" t="n">
-        <v>6564768</v>
+        <v>6564686</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150604</v>
+        <v>129150599</v>
       </c>
       <c r="B36" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665464</v>
+        <v>665294</v>
       </c>
       <c r="R36" t="n">
-        <v>6564686</v>
+        <v>6564670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150599</v>
+        <v>129150578</v>
       </c>
       <c r="B37" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665294</v>
+        <v>665443</v>
       </c>
       <c r="R37" t="n">
-        <v>6564670</v>
+        <v>6564659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150578</v>
+        <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665443</v>
+        <v>665228</v>
       </c>
       <c r="R38" t="n">
-        <v>6564659</v>
+        <v>6564499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150567</v>
+        <v>129150620</v>
       </c>
       <c r="B39" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665228</v>
+        <v>665358</v>
       </c>
       <c r="R39" t="n">
-        <v>6564499</v>
+        <v>6564768</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150616</v>
+        <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>92859</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665382</v>
+        <v>665408</v>
       </c>
       <c r="R40" t="n">
-        <v>6564609</v>
+        <v>6564551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150617</v>
+        <v>129150590</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92859</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665376</v>
+        <v>665331</v>
       </c>
       <c r="R41" t="n">
-        <v>6564598</v>
+        <v>6564765</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4923,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150571</v>
+        <v>129150606</v>
       </c>
       <c r="B42" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665408</v>
+        <v>665503</v>
       </c>
       <c r="R42" t="n">
-        <v>6564551</v>
+        <v>6564692</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5033,7 +5033,7 @@
         <v>129150569</v>
       </c>
       <c r="B43" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150590</v>
+        <v>129150602</v>
       </c>
       <c r="B44" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665331</v>
+        <v>665388</v>
       </c>
       <c r="R44" t="n">
-        <v>6564765</v>
+        <v>6564663</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150602</v>
+        <v>129150612</v>
       </c>
       <c r="B45" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665388</v>
+        <v>665587</v>
       </c>
       <c r="R45" t="n">
-        <v>6564663</v>
+        <v>6564768</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150606</v>
+        <v>129150617</v>
       </c>
       <c r="B46" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665503</v>
+        <v>665376</v>
       </c>
       <c r="R46" t="n">
-        <v>6564692</v>
+        <v>6564598</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150612</v>
+        <v>129150616</v>
       </c>
       <c r="B47" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665587</v>
+        <v>665382</v>
       </c>
       <c r="R47" t="n">
-        <v>6564768</v>
+        <v>6564609</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150611</v>
+        <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92873</v>
+        <v>92317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665607</v>
+        <v>665419</v>
       </c>
       <c r="R50" t="n">
-        <v>6564770</v>
+        <v>6564672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5889,7 +5889,7 @@
         <v>129150577</v>
       </c>
       <c r="B51" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150601</v>
+        <v>129150611</v>
       </c>
       <c r="B52" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665364</v>
+        <v>665607</v>
       </c>
       <c r="R52" t="n">
-        <v>6564665</v>
+        <v>6564770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150627</v>
+        <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92303</v>
+        <v>92859</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665419</v>
+        <v>665364</v>
       </c>
       <c r="R53" t="n">
-        <v>6564672</v>
+        <v>6564665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150591</v>
+        <v>129150580</v>
       </c>
       <c r="B54" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665318</v>
+        <v>665374</v>
       </c>
       <c r="R54" t="n">
-        <v>6564762</v>
+        <v>6564595</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,10 +6314,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150580</v>
+        <v>129150591</v>
       </c>
       <c r="B55" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665374</v>
+        <v>665318</v>
       </c>
       <c r="R55" t="n">
-        <v>6564595</v>
+        <v>6564762</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6424,7 +6424,7 @@
         <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6528,32 +6528,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150618</v>
+        <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>92317</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>1958</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665400</v>
+        <v>665455</v>
       </c>
       <c r="R57" t="n">
-        <v>6564742</v>
+        <v>6564681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,10 +6635,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150628</v>
+        <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>92303</v>
+        <v>92317</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665455</v>
+        <v>665260</v>
       </c>
       <c r="R58" t="n">
-        <v>6564681</v>
+        <v>6564773</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150626</v>
+        <v>129150618</v>
       </c>
       <c r="B59" t="n">
-        <v>92303</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1958</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665260</v>
+        <v>665400</v>
       </c>
       <c r="R59" t="n">
-        <v>6564773</v>
+        <v>6564742</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6852,7 +6852,7 @@
         <v>129150557</v>
       </c>
       <c r="B60" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150583</v>
+        <v>129150566</v>
       </c>
       <c r="B61" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665372</v>
+        <v>665194</v>
       </c>
       <c r="R61" t="n">
-        <v>6564721</v>
+        <v>6564498</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,10 +7063,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B62" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R62" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7280,7 +7280,7 @@
         <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7705,32 +7705,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150625</v>
+        <v>129150613</v>
       </c>
       <c r="B68" t="n">
-        <v>92303</v>
+        <v>92859</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665422</v>
+        <v>665566</v>
       </c>
       <c r="R68" t="n">
-        <v>6564565</v>
+        <v>6564813</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7812,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150613</v>
+        <v>129150625</v>
       </c>
       <c r="B69" t="n">
-        <v>92873</v>
+        <v>92317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665566</v>
+        <v>665422</v>
       </c>
       <c r="R69" t="n">
-        <v>6564813</v>
+        <v>6564565</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150572</v>
+        <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92873</v>
+        <v>92317</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665424</v>
+        <v>665507</v>
       </c>
       <c r="R76" t="n">
-        <v>6564571</v>
+        <v>6564685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8675,7 +8675,7 @@
         <v>129150607</v>
       </c>
       <c r="B77" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8779,10 +8779,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150581</v>
+        <v>129150572</v>
       </c>
       <c r="B78" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665366</v>
+        <v>665424</v>
       </c>
       <c r="R78" t="n">
-        <v>6564608</v>
+        <v>6564571</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150600</v>
+        <v>129150581</v>
       </c>
       <c r="B79" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665346</v>
+        <v>665366</v>
       </c>
       <c r="R79" t="n">
-        <v>6564670</v>
+        <v>6564608</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150589</v>
+        <v>129150600</v>
       </c>
       <c r="B80" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665371</v>
+        <v>665346</v>
       </c>
       <c r="R80" t="n">
-        <v>6564789</v>
+        <v>6564670</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,10 +9100,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150597</v>
+        <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665233</v>
+        <v>665371</v>
       </c>
       <c r="R81" t="n">
-        <v>6564718</v>
+        <v>6564789</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150629</v>
+        <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92303</v>
+        <v>92859</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665507</v>
+        <v>665233</v>
       </c>
       <c r="R82" t="n">
-        <v>6564685</v>
+        <v>6564718</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9317,7 +9317,7 @@
         <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128970273</v>
       </c>
       <c r="B14" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>128970264</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150574</v>
+        <v>129150596</v>
       </c>
       <c r="B26" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665437</v>
+        <v>665174</v>
       </c>
       <c r="R26" t="n">
-        <v>6564617</v>
+        <v>6564743</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,7 +3321,7 @@
         <v>129150585</v>
       </c>
       <c r="B27" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150596</v>
+        <v>129150586</v>
       </c>
       <c r="B28" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665174</v>
+        <v>665436</v>
       </c>
       <c r="R28" t="n">
-        <v>6564743</v>
+        <v>6564778</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150586</v>
+        <v>129150574</v>
       </c>
       <c r="B29" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665436</v>
+        <v>665437</v>
       </c>
       <c r="R29" t="n">
-        <v>6564778</v>
+        <v>6564617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129150584</v>
+        <v>129150582</v>
       </c>
       <c r="B32" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665409</v>
+        <v>665370</v>
       </c>
       <c r="R32" t="n">
-        <v>6564786</v>
+        <v>6564621</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129150582</v>
+        <v>129150584</v>
       </c>
       <c r="B33" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665370</v>
+        <v>665409</v>
       </c>
       <c r="R33" t="n">
-        <v>6564621</v>
+        <v>6564786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150604</v>
+        <v>129150620</v>
       </c>
       <c r="B35" t="n">
-        <v>92859</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665464</v>
+        <v>665358</v>
       </c>
       <c r="R35" t="n">
-        <v>6564686</v>
+        <v>6564768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150599</v>
+        <v>129150604</v>
       </c>
       <c r="B36" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665294</v>
+        <v>665464</v>
       </c>
       <c r="R36" t="n">
-        <v>6564670</v>
+        <v>6564686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150578</v>
+        <v>129150567</v>
       </c>
       <c r="B37" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665443</v>
+        <v>665228</v>
       </c>
       <c r="R37" t="n">
-        <v>6564659</v>
+        <v>6564499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150567</v>
+        <v>129150578</v>
       </c>
       <c r="B38" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665228</v>
+        <v>665443</v>
       </c>
       <c r="R38" t="n">
-        <v>6564499</v>
+        <v>6564659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150620</v>
+        <v>129150599</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92860</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665358</v>
+        <v>665294</v>
       </c>
       <c r="R39" t="n">
-        <v>6564768</v>
+        <v>6564670</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150571</v>
+        <v>129150617</v>
       </c>
       <c r="B40" t="n">
-        <v>92859</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665408</v>
+        <v>665376</v>
       </c>
       <c r="R40" t="n">
-        <v>6564551</v>
+        <v>6564598</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150590</v>
+        <v>129150616</v>
       </c>
       <c r="B41" t="n">
-        <v>92859</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665331</v>
+        <v>665382</v>
       </c>
       <c r="R41" t="n">
-        <v>6564765</v>
+        <v>6564609</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4926,7 +4926,7 @@
         <v>129150606</v>
       </c>
       <c r="B42" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5030,10 +5030,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150569</v>
+        <v>129150602</v>
       </c>
       <c r="B43" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>665388</v>
       </c>
       <c r="R43" t="n">
-        <v>6564531</v>
+        <v>6564663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150602</v>
+        <v>129150590</v>
       </c>
       <c r="B44" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665388</v>
+        <v>665331</v>
       </c>
       <c r="R44" t="n">
-        <v>6564663</v>
+        <v>6564765</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150612</v>
+        <v>129150569</v>
       </c>
       <c r="B45" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665587</v>
+        <v>665388</v>
       </c>
       <c r="R45" t="n">
-        <v>6564768</v>
+        <v>6564531</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150617</v>
+        <v>129150612</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>92860</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665376</v>
+        <v>665587</v>
       </c>
       <c r="R46" t="n">
-        <v>6564598</v>
+        <v>6564768</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150616</v>
+        <v>129150571</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>92860</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665382</v>
+        <v>665408</v>
       </c>
       <c r="R47" t="n">
-        <v>6564609</v>
+        <v>6564551</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150627</v>
+        <v>129150577</v>
       </c>
       <c r="B50" t="n">
-        <v>92317</v>
+        <v>92860</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665419</v>
+        <v>665446</v>
       </c>
       <c r="R50" t="n">
-        <v>6564672</v>
+        <v>6564659</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150611</v>
+        <v>129150601</v>
       </c>
       <c r="B52" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665607</v>
+        <v>665364</v>
       </c>
       <c r="R52" t="n">
-        <v>6564770</v>
+        <v>6564665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150601</v>
+        <v>129150627</v>
       </c>
       <c r="B53" t="n">
-        <v>92859</v>
+        <v>92318</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665364</v>
+        <v>665419</v>
       </c>
       <c r="R53" t="n">
-        <v>6564665</v>
+        <v>6564672</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150580</v>
+        <v>129150570</v>
       </c>
       <c r="B54" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665374</v>
+        <v>665399</v>
       </c>
       <c r="R54" t="n">
-        <v>6564595</v>
+        <v>6564537</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,10 +6314,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150591</v>
+        <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665318</v>
+        <v>665374</v>
       </c>
       <c r="R55" t="n">
-        <v>6564762</v>
+        <v>6564595</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6421,10 +6421,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129150570</v>
+        <v>129150591</v>
       </c>
       <c r="B56" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665399</v>
+        <v>665318</v>
       </c>
       <c r="R56" t="n">
-        <v>6564537</v>
+        <v>6564762</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6528,10 +6528,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150628</v>
+        <v>129150626</v>
       </c>
       <c r="B57" t="n">
-        <v>92317</v>
+        <v>92318</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665455</v>
+        <v>665260</v>
       </c>
       <c r="R57" t="n">
-        <v>6564681</v>
+        <v>6564773</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,32 +6635,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150626</v>
+        <v>129150618</v>
       </c>
       <c r="B58" t="n">
-        <v>92317</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1958</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665260</v>
+        <v>665400</v>
       </c>
       <c r="R58" t="n">
-        <v>6564773</v>
+        <v>6564742</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150618</v>
+        <v>129150628</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>92318</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>1958</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665400</v>
+        <v>665455</v>
       </c>
       <c r="R59" t="n">
-        <v>6564742</v>
+        <v>6564681</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6852,7 +6852,7 @@
         <v>129150557</v>
       </c>
       <c r="B60" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>129150566</v>
       </c>
       <c r="B61" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>129150583</v>
       </c>
       <c r="B62" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7277,10 +7277,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129150594</v>
+        <v>129150593</v>
       </c>
       <c r="B64" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>665232</v>
+        <v>665256</v>
       </c>
       <c r="R64" t="n">
-        <v>6564745</v>
+        <v>6564756</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7491,10 +7491,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150593</v>
+        <v>129150594</v>
       </c>
       <c r="B66" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665256</v>
+        <v>665232</v>
       </c>
       <c r="R66" t="n">
-        <v>6564756</v>
+        <v>6564745</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7705,32 +7705,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150613</v>
+        <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92859</v>
+        <v>92318</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665566</v>
+        <v>665422</v>
       </c>
       <c r="R68" t="n">
-        <v>6564813</v>
+        <v>6564565</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7812,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150625</v>
+        <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92317</v>
+        <v>92860</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665422</v>
+        <v>665566</v>
       </c>
       <c r="R69" t="n">
-        <v>6564565</v>
+        <v>6564813</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B73" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R73" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150609</v>
+        <v>129150610</v>
       </c>
       <c r="B74" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665505</v>
+        <v>665640</v>
       </c>
       <c r="R74" t="n">
-        <v>6564674</v>
+        <v>6564667</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150629</v>
+        <v>129150600</v>
       </c>
       <c r="B76" t="n">
-        <v>92317</v>
+        <v>92860</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665507</v>
+        <v>665346</v>
       </c>
       <c r="R76" t="n">
-        <v>6564685</v>
+        <v>6564670</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150607</v>
+        <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665514</v>
+        <v>665424</v>
       </c>
       <c r="R77" t="n">
-        <v>6564684</v>
+        <v>6564571</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150572</v>
+        <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665424</v>
+        <v>665514</v>
       </c>
       <c r="R78" t="n">
-        <v>6564571</v>
+        <v>6564684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150581</v>
+        <v>129150597</v>
       </c>
       <c r="B79" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665366</v>
+        <v>665233</v>
       </c>
       <c r="R79" t="n">
-        <v>6564608</v>
+        <v>6564718</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150600</v>
+        <v>129150581</v>
       </c>
       <c r="B80" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665346</v>
+        <v>665366</v>
       </c>
       <c r="R80" t="n">
-        <v>6564670</v>
+        <v>6564608</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,32 +9100,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150589</v>
+        <v>129150629</v>
       </c>
       <c r="B81" t="n">
-        <v>92859</v>
+        <v>92318</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665371</v>
+        <v>665507</v>
       </c>
       <c r="R81" t="n">
-        <v>6564789</v>
+        <v>6564685</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,10 +9207,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150597</v>
+        <v>129150589</v>
       </c>
       <c r="B82" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665233</v>
+        <v>665371</v>
       </c>
       <c r="R82" t="n">
-        <v>6564718</v>
+        <v>6564789</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9314,10 +9314,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150575</v>
+        <v>129150603</v>
       </c>
       <c r="B83" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665457</v>
+        <v>665453</v>
       </c>
       <c r="R83" t="n">
-        <v>6564660</v>
+        <v>6564677</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150603</v>
+        <v>129150588</v>
       </c>
       <c r="B84" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665453</v>
+        <v>665414</v>
       </c>
       <c r="R84" t="n">
-        <v>6564677</v>
+        <v>6564728</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9528,10 +9528,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129150588</v>
+        <v>129150575</v>
       </c>
       <c r="B85" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>665414</v>
+        <v>665457</v>
       </c>
       <c r="R85" t="n">
-        <v>6564728</v>
+        <v>6564660</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128970273</v>
+        <v>128970264</v>
       </c>
       <c r="B14" t="n">
-        <v>92860</v>
+        <v>91561</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665465</v>
+        <v>665464</v>
       </c>
       <c r="R14" t="n">
-        <v>6565043</v>
+        <v>6565020</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128970264</v>
+        <v>128970273</v>
       </c>
       <c r="B15" t="n">
-        <v>91561</v>
+        <v>92860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665464</v>
+        <v>665465</v>
       </c>
       <c r="R15" t="n">
-        <v>6565020</v>
+        <v>6565043</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150620</v>
+        <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>92860</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665358</v>
+        <v>665464</v>
       </c>
       <c r="R35" t="n">
-        <v>6564768</v>
+        <v>6564686</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150604</v>
+        <v>129150567</v>
       </c>
       <c r="B36" t="n">
         <v>92860</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665464</v>
+        <v>665228</v>
       </c>
       <c r="R36" t="n">
-        <v>6564686</v>
+        <v>6564499</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150567</v>
+        <v>129150578</v>
       </c>
       <c r="B37" t="n">
         <v>92860</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665228</v>
+        <v>665443</v>
       </c>
       <c r="R37" t="n">
-        <v>6564499</v>
+        <v>6564659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B38" t="n">
         <v>92860</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R38" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150599</v>
+        <v>129150620</v>
       </c>
       <c r="B39" t="n">
-        <v>92860</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665294</v>
+        <v>665358</v>
       </c>
       <c r="R39" t="n">
-        <v>6564670</v>
+        <v>6564768</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150617</v>
+        <v>129150612</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>92860</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665376</v>
+        <v>665587</v>
       </c>
       <c r="R40" t="n">
-        <v>6564598</v>
+        <v>6564768</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150616</v>
+        <v>129150606</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92860</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665382</v>
+        <v>665503</v>
       </c>
       <c r="R41" t="n">
-        <v>6564609</v>
+        <v>6564692</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150606</v>
+        <v>129150602</v>
       </c>
       <c r="B42" t="n">
         <v>92860</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R42" t="n">
-        <v>6564692</v>
+        <v>6564663</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150602</v>
+        <v>129150590</v>
       </c>
       <c r="B43" t="n">
         <v>92860</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665388</v>
+        <v>665331</v>
       </c>
       <c r="R43" t="n">
-        <v>6564663</v>
+        <v>6564765</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150590</v>
+        <v>129150571</v>
       </c>
       <c r="B44" t="n">
         <v>92860</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665331</v>
+        <v>665408</v>
       </c>
       <c r="R44" t="n">
-        <v>6564765</v>
+        <v>6564551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150612</v>
+        <v>129150617</v>
       </c>
       <c r="B46" t="n">
-        <v>92860</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665587</v>
+        <v>665376</v>
       </c>
       <c r="R46" t="n">
-        <v>6564768</v>
+        <v>6564598</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150571</v>
+        <v>129150616</v>
       </c>
       <c r="B47" t="n">
-        <v>92860</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665408</v>
+        <v>665382</v>
       </c>
       <c r="R47" t="n">
-        <v>6564551</v>
+        <v>6564609</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150577</v>
+        <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92860</v>
+        <v>92318</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665446</v>
+        <v>665419</v>
       </c>
       <c r="R50" t="n">
-        <v>6564659</v>
+        <v>6564672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B51" t="n">
         <v>92860</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150601</v>
+        <v>129150611</v>
       </c>
       <c r="B52" t="n">
         <v>92860</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665364</v>
+        <v>665607</v>
       </c>
       <c r="R52" t="n">
-        <v>6564665</v>
+        <v>6564770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150627</v>
+        <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92318</v>
+        <v>92860</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665419</v>
+        <v>665364</v>
       </c>
       <c r="R53" t="n">
-        <v>6564672</v>
+        <v>6564665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6528,7 +6528,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150626</v>
+        <v>129150628</v>
       </c>
       <c r="B57" t="n">
         <v>92318</v>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665260</v>
+        <v>665455</v>
       </c>
       <c r="R57" t="n">
-        <v>6564773</v>
+        <v>6564681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,32 +6635,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150618</v>
+        <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>92318</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>1958</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665400</v>
+        <v>665260</v>
       </c>
       <c r="R58" t="n">
-        <v>6564742</v>
+        <v>6564773</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150628</v>
+        <v>129150618</v>
       </c>
       <c r="B59" t="n">
-        <v>92318</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1958</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665455</v>
+        <v>665400</v>
       </c>
       <c r="R59" t="n">
-        <v>6564681</v>
+        <v>6564742</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8026,10 +8026,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129150595</v>
+        <v>129150556</v>
       </c>
       <c r="B71" t="n">
-        <v>92860</v>
+        <v>57887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8037,34 +8037,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665210</v>
+        <v>665406</v>
       </c>
       <c r="R71" t="n">
-        <v>6564762</v>
+        <v>6564548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8096,7 +8100,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8106,7 +8110,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8133,10 +8137,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150556</v>
+        <v>129150595</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>92860</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8144,38 +8148,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665406</v>
+        <v>665210</v>
       </c>
       <c r="R72" t="n">
-        <v>6564548</v>
+        <v>6564762</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150600</v>
+        <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92860</v>
+        <v>92318</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665346</v>
+        <v>665507</v>
       </c>
       <c r="R76" t="n">
-        <v>6564670</v>
+        <v>6564685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150572</v>
+        <v>129150600</v>
       </c>
       <c r="B77" t="n">
         <v>92860</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665424</v>
+        <v>665346</v>
       </c>
       <c r="R77" t="n">
-        <v>6564571</v>
+        <v>6564670</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150607</v>
+        <v>129150572</v>
       </c>
       <c r="B78" t="n">
         <v>92860</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665514</v>
+        <v>665424</v>
       </c>
       <c r="R78" t="n">
-        <v>6564684</v>
+        <v>6564571</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150597</v>
+        <v>129150607</v>
       </c>
       <c r="B79" t="n">
         <v>92860</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665233</v>
+        <v>665514</v>
       </c>
       <c r="R79" t="n">
-        <v>6564718</v>
+        <v>6564684</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,7 +8993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150581</v>
+        <v>129150597</v>
       </c>
       <c r="B80" t="n">
         <v>92860</v>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665366</v>
+        <v>665233</v>
       </c>
       <c r="R80" t="n">
-        <v>6564608</v>
+        <v>6564718</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,32 +9100,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150629</v>
+        <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92318</v>
+        <v>92860</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665507</v>
+        <v>665371</v>
       </c>
       <c r="R81" t="n">
-        <v>6564685</v>
+        <v>6564789</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,7 +9207,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150589</v>
+        <v>129150581</v>
       </c>
       <c r="B82" t="n">
         <v>92860</v>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665371</v>
+        <v>665366</v>
       </c>
       <c r="R82" t="n">
-        <v>6564789</v>
+        <v>6564608</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92848</v>
+        <v>92851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128970264</v>
       </c>
       <c r="B14" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>128970273</v>
       </c>
       <c r="B15" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150596</v>
+        <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665174</v>
+        <v>665437</v>
       </c>
       <c r="R26" t="n">
-        <v>6564743</v>
+        <v>6564617</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150585</v>
+        <v>129150586</v>
       </c>
       <c r="B27" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665424</v>
+        <v>665436</v>
       </c>
       <c r="R27" t="n">
-        <v>6564786</v>
+        <v>6564778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150586</v>
+        <v>129150585</v>
       </c>
       <c r="B28" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665436</v>
+        <v>665424</v>
       </c>
       <c r="R28" t="n">
-        <v>6564778</v>
+        <v>6564786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150574</v>
+        <v>129150596</v>
       </c>
       <c r="B29" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665437</v>
+        <v>665174</v>
       </c>
       <c r="R29" t="n">
-        <v>6564617</v>
+        <v>6564743</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129150582</v>
+        <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665370</v>
+        <v>665409</v>
       </c>
       <c r="R32" t="n">
-        <v>6564621</v>
+        <v>6564786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129150584</v>
+        <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665409</v>
+        <v>665370</v>
       </c>
       <c r="R33" t="n">
-        <v>6564786</v>
+        <v>6564621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150604</v>
+        <v>129150620</v>
       </c>
       <c r="B35" t="n">
-        <v>92860</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665464</v>
+        <v>665358</v>
       </c>
       <c r="R35" t="n">
-        <v>6564686</v>
+        <v>6564768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150567</v>
+        <v>129150604</v>
       </c>
       <c r="B36" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665228</v>
+        <v>665464</v>
       </c>
       <c r="R36" t="n">
-        <v>6564499</v>
+        <v>6564686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B37" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R37" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150599</v>
+        <v>129150578</v>
       </c>
       <c r="B38" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665294</v>
+        <v>665443</v>
       </c>
       <c r="R38" t="n">
-        <v>6564670</v>
+        <v>6564659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150620</v>
+        <v>129150567</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92863</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665358</v>
+        <v>665228</v>
       </c>
       <c r="R39" t="n">
-        <v>6564768</v>
+        <v>6564499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150612</v>
+        <v>129150617</v>
       </c>
       <c r="B40" t="n">
-        <v>92860</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665587</v>
+        <v>665376</v>
       </c>
       <c r="R40" t="n">
-        <v>6564768</v>
+        <v>6564598</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150606</v>
+        <v>129150571</v>
       </c>
       <c r="B41" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665503</v>
+        <v>665408</v>
       </c>
       <c r="R41" t="n">
-        <v>6564692</v>
+        <v>6564551</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4923,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150602</v>
+        <v>129150569</v>
       </c>
       <c r="B42" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>665388</v>
       </c>
       <c r="R42" t="n">
-        <v>6564663</v>
+        <v>6564531</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5033,7 +5033,7 @@
         <v>129150590</v>
       </c>
       <c r="B43" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150571</v>
+        <v>129150602</v>
       </c>
       <c r="B44" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665408</v>
+        <v>665388</v>
       </c>
       <c r="R44" t="n">
-        <v>6564551</v>
+        <v>6564663</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150569</v>
+        <v>129150606</v>
       </c>
       <c r="B45" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665388</v>
+        <v>665503</v>
       </c>
       <c r="R45" t="n">
-        <v>6564531</v>
+        <v>6564692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150617</v>
+        <v>129150612</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>92863</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665376</v>
+        <v>665587</v>
       </c>
       <c r="R46" t="n">
-        <v>6564598</v>
+        <v>6564768</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92318</v>
+        <v>92321</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5886,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B52" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R52" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6103,7 +6103,7 @@
         <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150570</v>
+        <v>129150591</v>
       </c>
       <c r="B54" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665399</v>
+        <v>665318</v>
       </c>
       <c r="R54" t="n">
-        <v>6564537</v>
+        <v>6564762</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6317,7 +6317,7 @@
         <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6421,10 +6421,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129150591</v>
+        <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665318</v>
+        <v>665399</v>
       </c>
       <c r="R56" t="n">
-        <v>6564762</v>
+        <v>6564537</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6531,7 +6531,7 @@
         <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>92318</v>
+        <v>92321</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>92318</v>
+        <v>92321</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150618</v>
+        <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>91564</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665400</v>
+        <v>665183</v>
       </c>
       <c r="R59" t="n">
-        <v>6564742</v>
+        <v>6564505</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150557</v>
+        <v>129150618</v>
       </c>
       <c r="B60" t="n">
-        <v>91561</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665183</v>
+        <v>665400</v>
       </c>
       <c r="R60" t="n">
-        <v>6564505</v>
+        <v>6564742</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6956,10 +6956,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R61" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,10 +7063,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150583</v>
+        <v>129150566</v>
       </c>
       <c r="B62" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665372</v>
+        <v>665194</v>
       </c>
       <c r="R62" t="n">
-        <v>6564721</v>
+        <v>6564498</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7277,10 +7277,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129150593</v>
+        <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>665256</v>
+        <v>665232</v>
       </c>
       <c r="R64" t="n">
-        <v>6564756</v>
+        <v>6564745</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7491,10 +7491,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150594</v>
+        <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665232</v>
+        <v>665256</v>
       </c>
       <c r="R66" t="n">
-        <v>6564745</v>
+        <v>6564756</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92318</v>
+        <v>92321</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129150556</v>
+        <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>57887</v>
+        <v>92863</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8037,38 +8037,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665406</v>
+        <v>665210</v>
       </c>
       <c r="R71" t="n">
-        <v>6564548</v>
+        <v>6564762</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8100,7 +8096,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8110,7 +8106,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8137,10 +8133,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150595</v>
+        <v>129150556</v>
       </c>
       <c r="B72" t="n">
-        <v>92860</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8148,34 +8144,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665210</v>
+        <v>665406</v>
       </c>
       <c r="R72" t="n">
-        <v>6564762</v>
+        <v>6564548</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8244,10 +8244,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150609</v>
+        <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665505</v>
+        <v>665640</v>
       </c>
       <c r="R73" t="n">
-        <v>6564674</v>
+        <v>6564667</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R74" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8568,7 +8568,7 @@
         <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92318</v>
+        <v>92321</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8672,10 +8672,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150600</v>
+        <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665346</v>
+        <v>665424</v>
       </c>
       <c r="R77" t="n">
-        <v>6564670</v>
+        <v>6564571</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150572</v>
+        <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665424</v>
+        <v>665514</v>
       </c>
       <c r="R78" t="n">
-        <v>6564571</v>
+        <v>6564684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150607</v>
+        <v>129150581</v>
       </c>
       <c r="B79" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665514</v>
+        <v>665366</v>
       </c>
       <c r="R79" t="n">
-        <v>6564684</v>
+        <v>6564608</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150597</v>
+        <v>129150600</v>
       </c>
       <c r="B80" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665233</v>
+        <v>665346</v>
       </c>
       <c r="R80" t="n">
-        <v>6564718</v>
+        <v>6564670</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9103,7 +9103,7 @@
         <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9207,10 +9207,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150581</v>
+        <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665366</v>
+        <v>665233</v>
       </c>
       <c r="R82" t="n">
-        <v>6564608</v>
+        <v>6564718</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9314,10 +9314,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150603</v>
+        <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665453</v>
+        <v>665457</v>
       </c>
       <c r="R83" t="n">
-        <v>6564677</v>
+        <v>6564660</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150588</v>
+        <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665414</v>
+        <v>665453</v>
       </c>
       <c r="R84" t="n">
-        <v>6564728</v>
+        <v>6564677</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9528,10 +9528,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129150575</v>
+        <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>665457</v>
+        <v>665414</v>
       </c>
       <c r="R85" t="n">
-        <v>6564660</v>
+        <v>6564728</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150620</v>
+        <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>92863</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665358</v>
+        <v>665464</v>
       </c>
       <c r="R35" t="n">
-        <v>6564768</v>
+        <v>6564686</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150604</v>
+        <v>129150599</v>
       </c>
       <c r="B36" t="n">
         <v>92863</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665464</v>
+        <v>665294</v>
       </c>
       <c r="R36" t="n">
-        <v>6564686</v>
+        <v>6564670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150599</v>
+        <v>129150578</v>
       </c>
       <c r="B37" t="n">
         <v>92863</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665294</v>
+        <v>665443</v>
       </c>
       <c r="R37" t="n">
-        <v>6564670</v>
+        <v>6564659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150578</v>
+        <v>129150567</v>
       </c>
       <c r="B38" t="n">
         <v>92863</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665443</v>
+        <v>665228</v>
       </c>
       <c r="R38" t="n">
-        <v>6564659</v>
+        <v>6564499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150567</v>
+        <v>129150620</v>
       </c>
       <c r="B39" t="n">
-        <v>92863</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665228</v>
+        <v>665358</v>
       </c>
       <c r="R39" t="n">
-        <v>6564499</v>
+        <v>6564768</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150617</v>
+        <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>92863</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665376</v>
+        <v>665408</v>
       </c>
       <c r="R40" t="n">
-        <v>6564598</v>
+        <v>6564551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,7 +4816,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150571</v>
+        <v>129150569</v>
       </c>
       <c r="B41" t="n">
         <v>92863</v>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665408</v>
+        <v>665388</v>
       </c>
       <c r="R41" t="n">
-        <v>6564551</v>
+        <v>6564531</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150569</v>
+        <v>129150590</v>
       </c>
       <c r="B42" t="n">
         <v>92863</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665388</v>
+        <v>665331</v>
       </c>
       <c r="R42" t="n">
-        <v>6564531</v>
+        <v>6564765</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150590</v>
+        <v>129150602</v>
       </c>
       <c r="B43" t="n">
         <v>92863</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665331</v>
+        <v>665388</v>
       </c>
       <c r="R43" t="n">
-        <v>6564765</v>
+        <v>6564663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150602</v>
+        <v>129150606</v>
       </c>
       <c r="B44" t="n">
         <v>92863</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665388</v>
+        <v>665503</v>
       </c>
       <c r="R44" t="n">
-        <v>6564663</v>
+        <v>6564692</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5244,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150606</v>
+        <v>129150612</v>
       </c>
       <c r="B45" t="n">
         <v>92863</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665503</v>
+        <v>665587</v>
       </c>
       <c r="R45" t="n">
-        <v>6564692</v>
+        <v>6564768</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150612</v>
+        <v>129150617</v>
       </c>
       <c r="B46" t="n">
-        <v>92863</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665587</v>
+        <v>665376</v>
       </c>
       <c r="R46" t="n">
-        <v>6564768</v>
+        <v>6564598</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970265</v>
+        <v>128970274</v>
       </c>
       <c r="B5" t="n">
-        <v>92851</v>
+        <v>92865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665424</v>
+        <v>665452</v>
       </c>
       <c r="R5" t="n">
-        <v>6565096</v>
+        <v>6565050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970274</v>
+        <v>128970265</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>92853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665452</v>
+        <v>665424</v>
       </c>
       <c r="R6" t="n">
-        <v>6565050</v>
+        <v>6565096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128970264</v>
+        <v>128970273</v>
       </c>
       <c r="B14" t="n">
-        <v>91564</v>
+        <v>92865</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665464</v>
+        <v>665465</v>
       </c>
       <c r="R14" t="n">
-        <v>6565020</v>
+        <v>6565043</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128970273</v>
+        <v>128970264</v>
       </c>
       <c r="B15" t="n">
-        <v>92863</v>
+        <v>91566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665465</v>
+        <v>665464</v>
       </c>
       <c r="R15" t="n">
-        <v>6565043</v>
+        <v>6565020</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129150586</v>
       </c>
       <c r="B27" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>129150585</v>
       </c>
       <c r="B28" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>129150596</v>
       </c>
       <c r="B29" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>129150599</v>
       </c>
       <c r="B36" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>129150578</v>
       </c>
       <c r="B37" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>129150569</v>
       </c>
       <c r="B41" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>129150590</v>
       </c>
       <c r="B42" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>129150602</v>
       </c>
       <c r="B43" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>129150606</v>
       </c>
       <c r="B44" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>129150612</v>
       </c>
       <c r="B45" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92321</v>
+        <v>92323</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>129150611</v>
       </c>
       <c r="B51" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>129150577</v>
       </c>
       <c r="B52" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>129150591</v>
       </c>
       <c r="B54" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>92321</v>
+        <v>92323</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>92321</v>
+        <v>92323</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>129150566</v>
       </c>
       <c r="B62" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92321</v>
+        <v>92323</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129150595</v>
+        <v>129150556</v>
       </c>
       <c r="B71" t="n">
-        <v>92863</v>
+        <v>57887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8037,34 +8037,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665210</v>
+        <v>665406</v>
       </c>
       <c r="R71" t="n">
-        <v>6564762</v>
+        <v>6564548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8096,7 +8100,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8106,7 +8110,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8133,10 +8137,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150556</v>
+        <v>129150595</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>92865</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8144,38 +8148,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665406</v>
+        <v>665210</v>
       </c>
       <c r="R72" t="n">
-        <v>6564548</v>
+        <v>6564762</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8247,7 +8247,7 @@
         <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92321</v>
+        <v>92323</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>129150581</v>
       </c>
       <c r="B79" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>129150600</v>
       </c>
       <c r="B80" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970274</v>
+        <v>128970265</v>
       </c>
       <c r="B5" t="n">
-        <v>92865</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665452</v>
+        <v>665424</v>
       </c>
       <c r="R5" t="n">
-        <v>6565050</v>
+        <v>6565096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970265</v>
+        <v>128970274</v>
       </c>
       <c r="B6" t="n">
-        <v>92853</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665424</v>
+        <v>665452</v>
       </c>
       <c r="R6" t="n">
-        <v>6565096</v>
+        <v>6565050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>128970273</v>
       </c>
       <c r="B14" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>128970264</v>
       </c>
       <c r="B15" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150574</v>
+        <v>129150596</v>
       </c>
       <c r="B26" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665437</v>
+        <v>665174</v>
       </c>
       <c r="R26" t="n">
-        <v>6564617</v>
+        <v>6564743</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150586</v>
+        <v>129150585</v>
       </c>
       <c r="B27" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665436</v>
+        <v>665424</v>
       </c>
       <c r="R27" t="n">
-        <v>6564778</v>
+        <v>6564786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150585</v>
+        <v>129150586</v>
       </c>
       <c r="B28" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665424</v>
+        <v>665436</v>
       </c>
       <c r="R28" t="n">
-        <v>6564786</v>
+        <v>6564778</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150596</v>
+        <v>129150574</v>
       </c>
       <c r="B29" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665174</v>
+        <v>665437</v>
       </c>
       <c r="R29" t="n">
-        <v>6564743</v>
+        <v>6564617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129150584</v>
+        <v>129150582</v>
       </c>
       <c r="B32" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665409</v>
+        <v>665370</v>
       </c>
       <c r="R32" t="n">
-        <v>6564786</v>
+        <v>6564621</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129150582</v>
+        <v>129150584</v>
       </c>
       <c r="B33" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665370</v>
+        <v>665409</v>
       </c>
       <c r="R33" t="n">
-        <v>6564621</v>
+        <v>6564786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150599</v>
+        <v>129150567</v>
       </c>
       <c r="B36" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665294</v>
+        <v>665228</v>
       </c>
       <c r="R36" t="n">
-        <v>6564670</v>
+        <v>6564499</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4391,7 +4391,7 @@
         <v>129150578</v>
       </c>
       <c r="B37" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150567</v>
+        <v>129150599</v>
       </c>
       <c r="B38" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665228</v>
+        <v>665294</v>
       </c>
       <c r="R38" t="n">
-        <v>6564499</v>
+        <v>6564670</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4709,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150571</v>
+        <v>129150612</v>
       </c>
       <c r="B40" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665408</v>
+        <v>665587</v>
       </c>
       <c r="R40" t="n">
-        <v>6564551</v>
+        <v>6564768</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150569</v>
+        <v>129150606</v>
       </c>
       <c r="B41" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665388</v>
+        <v>665503</v>
       </c>
       <c r="R41" t="n">
-        <v>6564531</v>
+        <v>6564692</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4923,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150590</v>
+        <v>129150602</v>
       </c>
       <c r="B42" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665331</v>
+        <v>665388</v>
       </c>
       <c r="R42" t="n">
-        <v>6564765</v>
+        <v>6564663</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,10 +5030,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150602</v>
+        <v>129150590</v>
       </c>
       <c r="B43" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665388</v>
+        <v>665331</v>
       </c>
       <c r="R43" t="n">
-        <v>6564663</v>
+        <v>6564765</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150606</v>
+        <v>129150571</v>
       </c>
       <c r="B44" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665503</v>
+        <v>665408</v>
       </c>
       <c r="R44" t="n">
-        <v>6564692</v>
+        <v>6564551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150612</v>
+        <v>129150569</v>
       </c>
       <c r="B45" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665587</v>
+        <v>665388</v>
       </c>
       <c r="R45" t="n">
-        <v>6564768</v>
+        <v>6564531</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92323</v>
+        <v>92327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5886,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B51" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B52" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R52" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6103,7 +6103,7 @@
         <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150591</v>
+        <v>129150570</v>
       </c>
       <c r="B54" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665318</v>
+        <v>665399</v>
       </c>
       <c r="R54" t="n">
-        <v>6564762</v>
+        <v>6564537</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6317,7 +6317,7 @@
         <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6421,10 +6421,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129150570</v>
+        <v>129150591</v>
       </c>
       <c r="B56" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665399</v>
+        <v>665318</v>
       </c>
       <c r="R56" t="n">
-        <v>6564537</v>
+        <v>6564762</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6531,7 +6531,7 @@
         <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>92323</v>
+        <v>92327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>92323</v>
+        <v>92327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150583</v>
+        <v>129150566</v>
       </c>
       <c r="B61" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665372</v>
+        <v>665194</v>
       </c>
       <c r="R61" t="n">
-        <v>6564721</v>
+        <v>6564498</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,10 +7063,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B62" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R62" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7277,10 +7277,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129150594</v>
+        <v>129150593</v>
       </c>
       <c r="B64" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>665232</v>
+        <v>665256</v>
       </c>
       <c r="R64" t="n">
-        <v>6564745</v>
+        <v>6564756</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7491,10 +7491,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150593</v>
+        <v>129150594</v>
       </c>
       <c r="B66" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665256</v>
+        <v>665232</v>
       </c>
       <c r="R66" t="n">
-        <v>6564756</v>
+        <v>6564745</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7705,32 +7705,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150625</v>
+        <v>129150613</v>
       </c>
       <c r="B68" t="n">
-        <v>92323</v>
+        <v>92869</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665422</v>
+        <v>665566</v>
       </c>
       <c r="R68" t="n">
-        <v>6564565</v>
+        <v>6564813</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7812,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150613</v>
+        <v>129150625</v>
       </c>
       <c r="B69" t="n">
-        <v>92865</v>
+        <v>92327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665566</v>
+        <v>665422</v>
       </c>
       <c r="R69" t="n">
-        <v>6564813</v>
+        <v>6564565</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>129150595</v>
       </c>
       <c r="B72" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8244,32 +8244,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150610</v>
+        <v>129150622</v>
       </c>
       <c r="B73" t="n">
-        <v>92865</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665640</v>
+        <v>665194</v>
       </c>
       <c r="R73" t="n">
-        <v>6564667</v>
+        <v>6564740</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8354,7 +8354,7 @@
         <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8458,32 +8458,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150622</v>
+        <v>129150610</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>92869</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665194</v>
+        <v>665640</v>
       </c>
       <c r="R75" t="n">
-        <v>6564740</v>
+        <v>6564667</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150629</v>
+        <v>129150600</v>
       </c>
       <c r="B76" t="n">
-        <v>92323</v>
+        <v>92869</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665507</v>
+        <v>665346</v>
       </c>
       <c r="R76" t="n">
-        <v>6564685</v>
+        <v>6564670</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8675,7 +8675,7 @@
         <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8886,10 +8886,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150581</v>
+        <v>129150597</v>
       </c>
       <c r="B79" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665366</v>
+        <v>665233</v>
       </c>
       <c r="R79" t="n">
-        <v>6564608</v>
+        <v>6564718</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150600</v>
+        <v>129150589</v>
       </c>
       <c r="B80" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665346</v>
+        <v>665371</v>
       </c>
       <c r="R80" t="n">
-        <v>6564670</v>
+        <v>6564789</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,10 +9100,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150589</v>
+        <v>129150581</v>
       </c>
       <c r="B81" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665371</v>
+        <v>665366</v>
       </c>
       <c r="R81" t="n">
-        <v>6564789</v>
+        <v>6564608</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150597</v>
+        <v>129150629</v>
       </c>
       <c r="B82" t="n">
-        <v>92865</v>
+        <v>92327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665233</v>
+        <v>665507</v>
       </c>
       <c r="R82" t="n">
-        <v>6564718</v>
+        <v>6564685</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9314,10 +9314,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150575</v>
+        <v>129150603</v>
       </c>
       <c r="B83" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665457</v>
+        <v>665453</v>
       </c>
       <c r="R83" t="n">
-        <v>6564660</v>
+        <v>6564677</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150603</v>
+        <v>129150588</v>
       </c>
       <c r="B84" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665453</v>
+        <v>665414</v>
       </c>
       <c r="R84" t="n">
-        <v>6564677</v>
+        <v>6564728</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9528,10 +9528,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129150588</v>
+        <v>129150575</v>
       </c>
       <c r="B85" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>665414</v>
+        <v>665457</v>
       </c>
       <c r="R85" t="n">
-        <v>6564728</v>
+        <v>6564660</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128970268</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128970277</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970265</v>
+        <v>128970274</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665424</v>
+        <v>665452</v>
       </c>
       <c r="R5" t="n">
-        <v>6565096</v>
+        <v>6565050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970274</v>
+        <v>128970265</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665452</v>
+        <v>665424</v>
       </c>
       <c r="R6" t="n">
-        <v>6565050</v>
+        <v>6565096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>128970270</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>128970269</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>128970275</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128970267</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128970271</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128970281</v>
       </c>
       <c r="B13" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128970273</v>
+        <v>128970264</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>91571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665465</v>
+        <v>665464</v>
       </c>
       <c r="R14" t="n">
-        <v>6565043</v>
+        <v>6565020</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128970264</v>
+        <v>128970273</v>
       </c>
       <c r="B15" t="n">
-        <v>91570</v>
+        <v>92870</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665464</v>
+        <v>665465</v>
       </c>
       <c r="R15" t="n">
-        <v>6565020</v>
+        <v>6565043</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,7 +2192,7 @@
         <v>128970272</v>
       </c>
       <c r="B16" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128970278</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>128970282</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150596</v>
+        <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665174</v>
+        <v>665437</v>
       </c>
       <c r="R26" t="n">
-        <v>6564743</v>
+        <v>6564617</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150585</v>
+        <v>129150586</v>
       </c>
       <c r="B27" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665424</v>
+        <v>665436</v>
       </c>
       <c r="R27" t="n">
-        <v>6564786</v>
+        <v>6564778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150586</v>
+        <v>129150585</v>
       </c>
       <c r="B28" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665436</v>
+        <v>665424</v>
       </c>
       <c r="R28" t="n">
-        <v>6564778</v>
+        <v>6564786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150574</v>
+        <v>129150596</v>
       </c>
       <c r="B29" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665437</v>
+        <v>665174</v>
       </c>
       <c r="R29" t="n">
-        <v>6564617</v>
+        <v>6564743</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129150582</v>
+        <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665370</v>
+        <v>665409</v>
       </c>
       <c r="R32" t="n">
-        <v>6564621</v>
+        <v>6564786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129150584</v>
+        <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665409</v>
+        <v>665370</v>
       </c>
       <c r="R33" t="n">
-        <v>6564786</v>
+        <v>6564621</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150567</v>
+        <v>129150599</v>
       </c>
       <c r="B36" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665228</v>
+        <v>665294</v>
       </c>
       <c r="R36" t="n">
-        <v>6564499</v>
+        <v>6564670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4391,7 +4391,7 @@
         <v>129150578</v>
       </c>
       <c r="B37" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150599</v>
+        <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665294</v>
+        <v>665228</v>
       </c>
       <c r="R38" t="n">
-        <v>6564670</v>
+        <v>6564499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4709,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150612</v>
+        <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665587</v>
+        <v>665408</v>
       </c>
       <c r="R40" t="n">
-        <v>6564768</v>
+        <v>6564551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150606</v>
+        <v>129150569</v>
       </c>
       <c r="B41" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R41" t="n">
-        <v>6564692</v>
+        <v>6564531</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4923,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150602</v>
+        <v>129150590</v>
       </c>
       <c r="B42" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665388</v>
+        <v>665331</v>
       </c>
       <c r="R42" t="n">
-        <v>6564663</v>
+        <v>6564765</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,10 +5030,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150590</v>
+        <v>129150606</v>
       </c>
       <c r="B43" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665331</v>
+        <v>665503</v>
       </c>
       <c r="R43" t="n">
-        <v>6564765</v>
+        <v>6564692</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150571</v>
+        <v>129150612</v>
       </c>
       <c r="B44" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665408</v>
+        <v>665587</v>
       </c>
       <c r="R44" t="n">
-        <v>6564551</v>
+        <v>6564768</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,32 +5244,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150569</v>
+        <v>129150617</v>
       </c>
       <c r="B45" t="n">
-        <v>92869</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665388</v>
+        <v>665376</v>
       </c>
       <c r="R45" t="n">
-        <v>6564531</v>
+        <v>6564598</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,7 +5351,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150617</v>
+        <v>129150616</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665376</v>
+        <v>665382</v>
       </c>
       <c r="R46" t="n">
-        <v>6564598</v>
+        <v>6564609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150616</v>
+        <v>129150602</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665382</v>
+        <v>665388</v>
       </c>
       <c r="R47" t="n">
-        <v>6564609</v>
+        <v>6564663</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92327</v>
+        <v>92328</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>129150577</v>
       </c>
       <c r="B51" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>129150611</v>
       </c>
       <c r="B52" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150570</v>
+        <v>129150580</v>
       </c>
       <c r="B54" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665399</v>
+        <v>665374</v>
       </c>
       <c r="R54" t="n">
-        <v>6564537</v>
+        <v>6564595</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,10 +6314,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150580</v>
+        <v>129150570</v>
       </c>
       <c r="B55" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665374</v>
+        <v>665399</v>
       </c>
       <c r="R55" t="n">
-        <v>6564595</v>
+        <v>6564537</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6424,7 +6424,7 @@
         <v>129150591</v>
       </c>
       <c r="B56" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>92327</v>
+        <v>92328</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>92327</v>
+        <v>92328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6956,32 +6956,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150566</v>
+        <v>129150619</v>
       </c>
       <c r="B61" t="n">
-        <v>92869</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665194</v>
+        <v>665365</v>
       </c>
       <c r="R61" t="n">
-        <v>6564498</v>
+        <v>6564786</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7066,7 +7066,7 @@
         <v>129150583</v>
       </c>
       <c r="B62" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150619</v>
+        <v>129150566</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665365</v>
+        <v>665194</v>
       </c>
       <c r="R63" t="n">
-        <v>6564786</v>
+        <v>6564498</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7277,10 +7277,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129150593</v>
+        <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>665256</v>
+        <v>665232</v>
       </c>
       <c r="R64" t="n">
-        <v>6564756</v>
+        <v>6564745</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7491,10 +7491,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150594</v>
+        <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665232</v>
+        <v>665256</v>
       </c>
       <c r="R66" t="n">
-        <v>6564745</v>
+        <v>6564756</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>129150613</v>
       </c>
       <c r="B68" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>129150625</v>
       </c>
       <c r="B69" t="n">
-        <v>92327</v>
+        <v>92328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129150556</v>
+        <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>57887</v>
+        <v>92870</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8037,38 +8037,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665406</v>
+        <v>665210</v>
       </c>
       <c r="R71" t="n">
-        <v>6564548</v>
+        <v>6564762</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8100,7 +8096,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8110,7 +8106,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8137,10 +8133,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150595</v>
+        <v>129150556</v>
       </c>
       <c r="B72" t="n">
-        <v>92869</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8148,34 +8144,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665210</v>
+        <v>665406</v>
       </c>
       <c r="R72" t="n">
-        <v>6564762</v>
+        <v>6564548</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150609</v>
+        <v>129150610</v>
       </c>
       <c r="B74" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665505</v>
+        <v>665640</v>
       </c>
       <c r="R74" t="n">
-        <v>6564674</v>
+        <v>6564667</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8458,10 +8458,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B75" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R75" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150600</v>
+        <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92869</v>
+        <v>92328</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665346</v>
+        <v>665507</v>
       </c>
       <c r="R76" t="n">
-        <v>6564670</v>
+        <v>6564685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8675,7 +8675,7 @@
         <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8886,10 +8886,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150597</v>
+        <v>129150581</v>
       </c>
       <c r="B79" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665233</v>
+        <v>665366</v>
       </c>
       <c r="R79" t="n">
-        <v>6564718</v>
+        <v>6564608</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150589</v>
+        <v>129150600</v>
       </c>
       <c r="B80" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665371</v>
+        <v>665346</v>
       </c>
       <c r="R80" t="n">
-        <v>6564789</v>
+        <v>6564670</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,10 +9100,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150581</v>
+        <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665366</v>
+        <v>665371</v>
       </c>
       <c r="R81" t="n">
-        <v>6564608</v>
+        <v>6564789</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150629</v>
+        <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92327</v>
+        <v>92870</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665507</v>
+        <v>665233</v>
       </c>
       <c r="R82" t="n">
-        <v>6564685</v>
+        <v>6564718</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9314,10 +9314,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150603</v>
+        <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665453</v>
+        <v>665457</v>
       </c>
       <c r="R83" t="n">
-        <v>6564677</v>
+        <v>6564660</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9424,7 +9424,7 @@
         <v>129150588</v>
       </c>
       <c r="B84" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129150575</v>
+        <v>129150603</v>
       </c>
       <c r="B85" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>665457</v>
+        <v>665453</v>
       </c>
       <c r="R85" t="n">
-        <v>6564660</v>
+        <v>6564677</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -3211,7 +3211,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150574</v>
+        <v>129150586</v>
       </c>
       <c r="B26" t="n">
         <v>92870</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665437</v>
+        <v>665436</v>
       </c>
       <c r="R26" t="n">
-        <v>6564617</v>
+        <v>6564778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,7 +3318,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150586</v>
+        <v>129150585</v>
       </c>
       <c r="B27" t="n">
         <v>92870</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665436</v>
+        <v>665424</v>
       </c>
       <c r="R27" t="n">
-        <v>6564778</v>
+        <v>6564786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150585</v>
+        <v>129150596</v>
       </c>
       <c r="B28" t="n">
         <v>92870</v>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665424</v>
+        <v>665174</v>
       </c>
       <c r="R28" t="n">
-        <v>6564786</v>
+        <v>6564743</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150596</v>
+        <v>129150574</v>
       </c>
       <c r="B29" t="n">
         <v>92870</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665174</v>
+        <v>665437</v>
       </c>
       <c r="R29" t="n">
-        <v>6564743</v>
+        <v>6564617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,7 +3639,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129150565</v>
+        <v>129150579</v>
       </c>
       <c r="B30" t="n">
         <v>92870</v>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665143</v>
+        <v>665438</v>
       </c>
       <c r="R30" t="n">
-        <v>6564565</v>
+        <v>6564656</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,7 +3746,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129150579</v>
+        <v>129150565</v>
       </c>
       <c r="B31" t="n">
         <v>92870</v>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665438</v>
+        <v>665143</v>
       </c>
       <c r="R31" t="n">
-        <v>6564656</v>
+        <v>6564565</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150604</v>
+        <v>129150620</v>
       </c>
       <c r="B35" t="n">
-        <v>92870</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665464</v>
+        <v>665358</v>
       </c>
       <c r="R35" t="n">
-        <v>6564686</v>
+        <v>6564768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150599</v>
+        <v>129150604</v>
       </c>
       <c r="B36" t="n">
         <v>92870</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665294</v>
+        <v>665464</v>
       </c>
       <c r="R36" t="n">
-        <v>6564670</v>
+        <v>6564686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B37" t="n">
         <v>92870</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R37" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150567</v>
+        <v>129150578</v>
       </c>
       <c r="B38" t="n">
         <v>92870</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665228</v>
+        <v>665443</v>
       </c>
       <c r="R38" t="n">
-        <v>6564499</v>
+        <v>6564659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150620</v>
+        <v>129150567</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665358</v>
+        <v>665228</v>
       </c>
       <c r="R39" t="n">
-        <v>6564768</v>
+        <v>6564499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150606</v>
+        <v>129150602</v>
       </c>
       <c r="B43" t="n">
         <v>92870</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R43" t="n">
-        <v>6564692</v>
+        <v>6564663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150612</v>
+        <v>129150606</v>
       </c>
       <c r="B44" t="n">
         <v>92870</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665587</v>
+        <v>665503</v>
       </c>
       <c r="R44" t="n">
-        <v>6564768</v>
+        <v>6564692</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,32 +5244,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150617</v>
+        <v>129150612</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665376</v>
+        <v>665587</v>
       </c>
       <c r="R45" t="n">
-        <v>6564598</v>
+        <v>6564768</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,7 +5351,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150616</v>
+        <v>129150617</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665382</v>
+        <v>665376</v>
       </c>
       <c r="R46" t="n">
-        <v>6564609</v>
+        <v>6564598</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150602</v>
+        <v>129150616</v>
       </c>
       <c r="B47" t="n">
-        <v>92870</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665388</v>
+        <v>665382</v>
       </c>
       <c r="R47" t="n">
-        <v>6564663</v>
+        <v>6564609</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
         <v>92870</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B52" t="n">
         <v>92870</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R52" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6207,7 +6207,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150580</v>
+        <v>129150591</v>
       </c>
       <c r="B54" t="n">
         <v>92870</v>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665374</v>
+        <v>665318</v>
       </c>
       <c r="R54" t="n">
-        <v>6564595</v>
+        <v>6564762</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,7 +6314,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150570</v>
+        <v>129150580</v>
       </c>
       <c r="B55" t="n">
         <v>92870</v>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665399</v>
+        <v>665374</v>
       </c>
       <c r="R55" t="n">
-        <v>6564537</v>
+        <v>6564595</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6421,7 +6421,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129150591</v>
+        <v>129150570</v>
       </c>
       <c r="B56" t="n">
         <v>92870</v>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665318</v>
+        <v>665399</v>
       </c>
       <c r="R56" t="n">
-        <v>6564762</v>
+        <v>6564537</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6528,32 +6528,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150628</v>
+        <v>129150618</v>
       </c>
       <c r="B57" t="n">
-        <v>92328</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1958</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665455</v>
+        <v>665400</v>
       </c>
       <c r="R57" t="n">
-        <v>6564681</v>
+        <v>6564742</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,7 +6635,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150626</v>
+        <v>129150628</v>
       </c>
       <c r="B58" t="n">
         <v>92328</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665260</v>
+        <v>665455</v>
       </c>
       <c r="R58" t="n">
-        <v>6564773</v>
+        <v>6564681</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150557</v>
+        <v>129150626</v>
       </c>
       <c r="B59" t="n">
-        <v>91571</v>
+        <v>92328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>1958</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665183</v>
+        <v>665260</v>
       </c>
       <c r="R59" t="n">
-        <v>6564505</v>
+        <v>6564773</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150618</v>
+        <v>129150557</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>91571</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665400</v>
+        <v>665183</v>
       </c>
       <c r="R60" t="n">
-        <v>6564742</v>
+        <v>6564505</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6956,32 +6956,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150619</v>
+        <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665365</v>
+        <v>665372</v>
       </c>
       <c r="R61" t="n">
-        <v>6564786</v>
+        <v>6564721</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,7 +7063,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150583</v>
+        <v>129150566</v>
       </c>
       <c r="B62" t="n">
         <v>92870</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665372</v>
+        <v>665194</v>
       </c>
       <c r="R62" t="n">
-        <v>6564721</v>
+        <v>6564498</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150566</v>
+        <v>129150619</v>
       </c>
       <c r="B63" t="n">
-        <v>92870</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665194</v>
+        <v>665365</v>
       </c>
       <c r="R63" t="n">
-        <v>6564498</v>
+        <v>6564786</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8244,32 +8244,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150622</v>
+        <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665194</v>
+        <v>665640</v>
       </c>
       <c r="R73" t="n">
-        <v>6564740</v>
+        <v>6564667</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,7 +8351,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B74" t="n">
         <v>92870</v>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R74" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8458,32 +8458,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150609</v>
+        <v>129150622</v>
       </c>
       <c r="B75" t="n">
-        <v>92870</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665505</v>
+        <v>665194</v>
       </c>
       <c r="R75" t="n">
-        <v>6564674</v>
+        <v>6564740</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150629</v>
+        <v>129150572</v>
       </c>
       <c r="B76" t="n">
-        <v>92328</v>
+        <v>92870</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665507</v>
+        <v>665424</v>
       </c>
       <c r="R76" t="n">
-        <v>6564685</v>
+        <v>6564571</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150572</v>
+        <v>129150581</v>
       </c>
       <c r="B77" t="n">
         <v>92870</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665424</v>
+        <v>665366</v>
       </c>
       <c r="R77" t="n">
-        <v>6564571</v>
+        <v>6564608</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150607</v>
+        <v>129150589</v>
       </c>
       <c r="B78" t="n">
         <v>92870</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665514</v>
+        <v>665371</v>
       </c>
       <c r="R78" t="n">
-        <v>6564684</v>
+        <v>6564789</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150581</v>
+        <v>129150597</v>
       </c>
       <c r="B79" t="n">
         <v>92870</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665366</v>
+        <v>665233</v>
       </c>
       <c r="R79" t="n">
-        <v>6564608</v>
+        <v>6564718</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,7 +8993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150600</v>
+        <v>129150607</v>
       </c>
       <c r="B80" t="n">
         <v>92870</v>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665346</v>
+        <v>665514</v>
       </c>
       <c r="R80" t="n">
-        <v>6564670</v>
+        <v>6564684</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150589</v>
+        <v>129150600</v>
       </c>
       <c r="B81" t="n">
         <v>92870</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665371</v>
+        <v>665346</v>
       </c>
       <c r="R81" t="n">
-        <v>6564789</v>
+        <v>6564670</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150597</v>
+        <v>129150629</v>
       </c>
       <c r="B82" t="n">
-        <v>92870</v>
+        <v>92328</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665233</v>
+        <v>665507</v>
       </c>
       <c r="R82" t="n">
-        <v>6564718</v>
+        <v>6564685</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9314,7 +9314,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150575</v>
+        <v>129150588</v>
       </c>
       <c r="B83" t="n">
         <v>92870</v>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665457</v>
+        <v>665414</v>
       </c>
       <c r="R83" t="n">
-        <v>6564660</v>
+        <v>6564728</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,7 +9421,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150588</v>
+        <v>129150575</v>
       </c>
       <c r="B84" t="n">
         <v>92870</v>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665414</v>
+        <v>665457</v>
       </c>
       <c r="R84" t="n">
-        <v>6564728</v>
+        <v>6564660</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -3211,7 +3211,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150586</v>
+        <v>129150574</v>
       </c>
       <c r="B26" t="n">
         <v>92870</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665436</v>
+        <v>665437</v>
       </c>
       <c r="R26" t="n">
-        <v>6564778</v>
+        <v>6564617</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,7 +3318,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150585</v>
+        <v>129150586</v>
       </c>
       <c r="B27" t="n">
         <v>92870</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665424</v>
+        <v>665436</v>
       </c>
       <c r="R27" t="n">
-        <v>6564786</v>
+        <v>6564778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150596</v>
+        <v>129150585</v>
       </c>
       <c r="B28" t="n">
         <v>92870</v>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665174</v>
+        <v>665424</v>
       </c>
       <c r="R28" t="n">
-        <v>6564743</v>
+        <v>6564786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150574</v>
+        <v>129150596</v>
       </c>
       <c r="B29" t="n">
         <v>92870</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665437</v>
+        <v>665174</v>
       </c>
       <c r="R29" t="n">
-        <v>6564617</v>
+        <v>6564743</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150620</v>
+        <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665358</v>
+        <v>665464</v>
       </c>
       <c r="R35" t="n">
-        <v>6564768</v>
+        <v>6564686</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150604</v>
+        <v>129150599</v>
       </c>
       <c r="B36" t="n">
         <v>92870</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665464</v>
+        <v>665294</v>
       </c>
       <c r="R36" t="n">
-        <v>6564686</v>
+        <v>6564670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150599</v>
+        <v>129150578</v>
       </c>
       <c r="B37" t="n">
         <v>92870</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665294</v>
+        <v>665443</v>
       </c>
       <c r="R37" t="n">
-        <v>6564670</v>
+        <v>6564659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150578</v>
+        <v>129150567</v>
       </c>
       <c r="B38" t="n">
         <v>92870</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665443</v>
+        <v>665228</v>
       </c>
       <c r="R38" t="n">
-        <v>6564659</v>
+        <v>6564499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150567</v>
+        <v>129150620</v>
       </c>
       <c r="B39" t="n">
-        <v>92870</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665228</v>
+        <v>665358</v>
       </c>
       <c r="R39" t="n">
-        <v>6564499</v>
+        <v>6564768</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6528,32 +6528,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150618</v>
+        <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>92328</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>1958</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665400</v>
+        <v>665455</v>
       </c>
       <c r="R57" t="n">
-        <v>6564742</v>
+        <v>6564681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,7 +6635,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150628</v>
+        <v>129150626</v>
       </c>
       <c r="B58" t="n">
         <v>92328</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665455</v>
+        <v>665260</v>
       </c>
       <c r="R58" t="n">
-        <v>6564681</v>
+        <v>6564773</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150626</v>
+        <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>92328</v>
+        <v>91571</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1958</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665260</v>
+        <v>665183</v>
       </c>
       <c r="R59" t="n">
-        <v>6564773</v>
+        <v>6564505</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150557</v>
+        <v>129150618</v>
       </c>
       <c r="B60" t="n">
-        <v>91571</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665183</v>
+        <v>665400</v>
       </c>
       <c r="R60" t="n">
-        <v>6564505</v>
+        <v>6564742</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7705,32 +7705,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150613</v>
+        <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92870</v>
+        <v>92328</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665566</v>
+        <v>665422</v>
       </c>
       <c r="R68" t="n">
-        <v>6564813</v>
+        <v>6564565</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7812,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150625</v>
+        <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92328</v>
+        <v>92870</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665422</v>
+        <v>665566</v>
       </c>
       <c r="R69" t="n">
-        <v>6564565</v>
+        <v>6564813</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150572</v>
+        <v>129150607</v>
       </c>
       <c r="B76" t="n">
         <v>92870</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665424</v>
+        <v>665514</v>
       </c>
       <c r="R76" t="n">
-        <v>6564571</v>
+        <v>6564684</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150581</v>
+        <v>129150600</v>
       </c>
       <c r="B77" t="n">
         <v>92870</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665366</v>
+        <v>665346</v>
       </c>
       <c r="R77" t="n">
-        <v>6564608</v>
+        <v>6564670</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,32 +8779,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150589</v>
+        <v>129150629</v>
       </c>
       <c r="B78" t="n">
-        <v>92870</v>
+        <v>92328</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665371</v>
+        <v>665507</v>
       </c>
       <c r="R78" t="n">
-        <v>6564789</v>
+        <v>6564685</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150597</v>
+        <v>129150572</v>
       </c>
       <c r="B79" t="n">
         <v>92870</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665233</v>
+        <v>665424</v>
       </c>
       <c r="R79" t="n">
-        <v>6564718</v>
+        <v>6564571</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,7 +8993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150607</v>
+        <v>129150581</v>
       </c>
       <c r="B80" t="n">
         <v>92870</v>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665514</v>
+        <v>665366</v>
       </c>
       <c r="R80" t="n">
-        <v>6564684</v>
+        <v>6564608</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150600</v>
+        <v>129150589</v>
       </c>
       <c r="B81" t="n">
         <v>92870</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665346</v>
+        <v>665371</v>
       </c>
       <c r="R81" t="n">
-        <v>6564670</v>
+        <v>6564789</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150629</v>
+        <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92328</v>
+        <v>92870</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665507</v>
+        <v>665233</v>
       </c>
       <c r="R82" t="n">
-        <v>6564685</v>
+        <v>6564718</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9635,7 +9635,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129150623</v>
+        <v>129150615</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>665233</v>
+        <v>665164</v>
       </c>
       <c r="R86" t="n">
-        <v>6564720</v>
+        <v>6564505</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9742,7 +9742,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129150615</v>
+        <v>129150623</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>665164</v>
+        <v>665233</v>
       </c>
       <c r="R87" t="n">
-        <v>6564505</v>
+        <v>6564720</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -2632,7 +2632,7 @@
         <v>129107656</v>
       </c>
       <c r="B20" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129107654</v>
       </c>
       <c r="B21" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>129107653</v>
       </c>
       <c r="B22" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129107651</v>
       </c>
       <c r="B23" t="n">
-        <v>92844</v>
+        <v>92847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129107655</v>
       </c>
       <c r="B24" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129150586</v>
       </c>
       <c r="B27" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>129150585</v>
       </c>
       <c r="B28" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>129150596</v>
       </c>
       <c r="B29" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129150579</v>
+        <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665438</v>
+        <v>665143</v>
       </c>
       <c r="R30" t="n">
-        <v>6564656</v>
+        <v>6564565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129150565</v>
+        <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665143</v>
+        <v>665438</v>
       </c>
       <c r="R31" t="n">
-        <v>6564565</v>
+        <v>6564656</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,7 +3856,7 @@
         <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>129150599</v>
       </c>
       <c r="B36" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>129150578</v>
       </c>
       <c r="B37" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>129150569</v>
       </c>
       <c r="B41" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>129150590</v>
       </c>
       <c r="B42" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>129150602</v>
       </c>
       <c r="B43" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>129150606</v>
       </c>
       <c r="B44" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>129150612</v>
       </c>
       <c r="B45" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150627</v>
+        <v>129150611</v>
       </c>
       <c r="B50" t="n">
-        <v>92328</v>
+        <v>92873</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665419</v>
+        <v>665607</v>
       </c>
       <c r="R50" t="n">
-        <v>6564672</v>
+        <v>6564770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B51" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150577</v>
+        <v>129150601</v>
       </c>
       <c r="B52" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665446</v>
+        <v>665364</v>
       </c>
       <c r="R52" t="n">
-        <v>6564659</v>
+        <v>6564665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150601</v>
+        <v>129150627</v>
       </c>
       <c r="B53" t="n">
-        <v>92870</v>
+        <v>92331</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665364</v>
+        <v>665419</v>
       </c>
       <c r="R53" t="n">
-        <v>6564665</v>
+        <v>6564672</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6210,7 +6210,7 @@
         <v>129150591</v>
       </c>
       <c r="B54" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>92328</v>
+        <v>92331</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>92328</v>
+        <v>92331</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>129150566</v>
       </c>
       <c r="B62" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>129150625</v>
       </c>
       <c r="B68" t="n">
-        <v>92328</v>
+        <v>92331</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>129150613</v>
       </c>
       <c r="B69" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150607</v>
+        <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92870</v>
+        <v>92331</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665514</v>
+        <v>665507</v>
       </c>
       <c r="R76" t="n">
-        <v>6564684</v>
+        <v>6564685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150600</v>
+        <v>129150572</v>
       </c>
       <c r="B77" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665346</v>
+        <v>665424</v>
       </c>
       <c r="R77" t="n">
-        <v>6564670</v>
+        <v>6564571</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,32 +8779,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150629</v>
+        <v>129150607</v>
       </c>
       <c r="B78" t="n">
-        <v>92328</v>
+        <v>92873</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665507</v>
+        <v>665514</v>
       </c>
       <c r="R78" t="n">
-        <v>6564685</v>
+        <v>6564684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150572</v>
+        <v>129150581</v>
       </c>
       <c r="B79" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665424</v>
+        <v>665366</v>
       </c>
       <c r="R79" t="n">
-        <v>6564571</v>
+        <v>6564608</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150581</v>
+        <v>129150600</v>
       </c>
       <c r="B80" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665366</v>
+        <v>665346</v>
       </c>
       <c r="R80" t="n">
-        <v>6564608</v>
+        <v>6564670</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9103,7 +9103,7 @@
         <v>129150589</v>
       </c>
       <c r="B81" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9314,10 +9314,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150588</v>
+        <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665414</v>
+        <v>665457</v>
       </c>
       <c r="R83" t="n">
-        <v>6564728</v>
+        <v>6564660</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150575</v>
+        <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665457</v>
+        <v>665453</v>
       </c>
       <c r="R84" t="n">
-        <v>6564660</v>
+        <v>6564677</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9528,10 +9528,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129150603</v>
+        <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>665453</v>
+        <v>665414</v>
       </c>
       <c r="R85" t="n">
-        <v>6564677</v>
+        <v>6564728</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9635,7 +9635,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129150615</v>
+        <v>129150623</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>665164</v>
+        <v>665233</v>
       </c>
       <c r="R86" t="n">
-        <v>6564505</v>
+        <v>6564720</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9742,7 +9742,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129150623</v>
+        <v>129150615</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>665233</v>
+        <v>665164</v>
       </c>
       <c r="R87" t="n">
-        <v>6564720</v>
+        <v>6564505</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150604</v>
+        <v>129150620</v>
       </c>
       <c r="B35" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665464</v>
+        <v>665358</v>
       </c>
       <c r="R35" t="n">
-        <v>6564686</v>
+        <v>6564768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150599</v>
+        <v>129150604</v>
       </c>
       <c r="B36" t="n">
         <v>92873</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665294</v>
+        <v>665464</v>
       </c>
       <c r="R36" t="n">
-        <v>6564670</v>
+        <v>6564686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B37" t="n">
         <v>92873</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R37" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150620</v>
+        <v>129150578</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665358</v>
+        <v>665443</v>
       </c>
       <c r="R39" t="n">
-        <v>6564768</v>
+        <v>6564659</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,7 +4709,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150571</v>
+        <v>129150590</v>
       </c>
       <c r="B40" t="n">
         <v>92873</v>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665408</v>
+        <v>665331</v>
       </c>
       <c r="R40" t="n">
-        <v>6564551</v>
+        <v>6564765</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,7 +4816,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150569</v>
+        <v>129150606</v>
       </c>
       <c r="B41" t="n">
         <v>92873</v>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665388</v>
+        <v>665503</v>
       </c>
       <c r="R41" t="n">
-        <v>6564531</v>
+        <v>6564692</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150590</v>
+        <v>129150612</v>
       </c>
       <c r="B42" t="n">
         <v>92873</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665331</v>
+        <v>665587</v>
       </c>
       <c r="R42" t="n">
-        <v>6564765</v>
+        <v>6564768</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150602</v>
+        <v>129150571</v>
       </c>
       <c r="B43" t="n">
         <v>92873</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665388</v>
+        <v>665408</v>
       </c>
       <c r="R43" t="n">
-        <v>6564663</v>
+        <v>6564551</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150606</v>
+        <v>129150569</v>
       </c>
       <c r="B44" t="n">
         <v>92873</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R44" t="n">
-        <v>6564692</v>
+        <v>6564531</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5244,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150612</v>
+        <v>129150602</v>
       </c>
       <c r="B45" t="n">
         <v>92873</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665587</v>
+        <v>665388</v>
       </c>
       <c r="R45" t="n">
-        <v>6564768</v>
+        <v>6564663</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150611</v>
+        <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92873</v>
+        <v>92331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665607</v>
+        <v>665419</v>
       </c>
       <c r="R50" t="n">
-        <v>6564770</v>
+        <v>6564672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
         <v>92873</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150601</v>
+        <v>129150577</v>
       </c>
       <c r="B52" t="n">
         <v>92873</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665364</v>
+        <v>665446</v>
       </c>
       <c r="R52" t="n">
-        <v>6564665</v>
+        <v>6564659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150627</v>
+        <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92331</v>
+        <v>92873</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665419</v>
+        <v>665364</v>
       </c>
       <c r="R53" t="n">
-        <v>6564672</v>
+        <v>6564665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6528,7 +6528,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150628</v>
+        <v>129150626</v>
       </c>
       <c r="B57" t="n">
         <v>92331</v>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665455</v>
+        <v>665260</v>
       </c>
       <c r="R57" t="n">
-        <v>6564681</v>
+        <v>6564773</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,32 +6635,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150626</v>
+        <v>129150618</v>
       </c>
       <c r="B58" t="n">
-        <v>92331</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1958</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665260</v>
+        <v>665400</v>
       </c>
       <c r="R58" t="n">
-        <v>6564773</v>
+        <v>6564742</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150557</v>
+        <v>129150628</v>
       </c>
       <c r="B59" t="n">
-        <v>91574</v>
+        <v>92331</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>1958</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665183</v>
+        <v>665455</v>
       </c>
       <c r="R59" t="n">
-        <v>6564505</v>
+        <v>6564681</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150618</v>
+        <v>129150557</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>91574</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665400</v>
+        <v>665183</v>
       </c>
       <c r="R60" t="n">
-        <v>6564742</v>
+        <v>6564505</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7384,7 +7384,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129150598</v>
+        <v>129150605</v>
       </c>
       <c r="B65" t="n">
         <v>92873</v>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>665283</v>
+        <v>665484</v>
       </c>
       <c r="R65" t="n">
-        <v>6564685</v>
+        <v>6564691</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,7 +7491,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150593</v>
+        <v>129150598</v>
       </c>
       <c r="B66" t="n">
         <v>92873</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665256</v>
+        <v>665283</v>
       </c>
       <c r="R66" t="n">
-        <v>6564756</v>
+        <v>6564685</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7598,7 +7598,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129150605</v>
+        <v>129150593</v>
       </c>
       <c r="B67" t="n">
         <v>92873</v>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>665484</v>
+        <v>665256</v>
       </c>
       <c r="R67" t="n">
-        <v>6564691</v>
+        <v>6564756</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150629</v>
+        <v>129150607</v>
       </c>
       <c r="B76" t="n">
-        <v>92331</v>
+        <v>92873</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665507</v>
+        <v>665514</v>
       </c>
       <c r="R76" t="n">
-        <v>6564685</v>
+        <v>6564684</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150572</v>
+        <v>129150581</v>
       </c>
       <c r="B77" t="n">
         <v>92873</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665424</v>
+        <v>665366</v>
       </c>
       <c r="R77" t="n">
-        <v>6564571</v>
+        <v>6564608</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150607</v>
+        <v>129150589</v>
       </c>
       <c r="B78" t="n">
         <v>92873</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665514</v>
+        <v>665371</v>
       </c>
       <c r="R78" t="n">
-        <v>6564684</v>
+        <v>6564789</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150581</v>
+        <v>129150597</v>
       </c>
       <c r="B79" t="n">
         <v>92873</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665366</v>
+        <v>665233</v>
       </c>
       <c r="R79" t="n">
-        <v>6564608</v>
+        <v>6564718</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,32 +8993,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150600</v>
+        <v>129150629</v>
       </c>
       <c r="B80" t="n">
-        <v>92873</v>
+        <v>92331</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665346</v>
+        <v>665507</v>
       </c>
       <c r="R80" t="n">
-        <v>6564670</v>
+        <v>6564685</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150589</v>
+        <v>129150572</v>
       </c>
       <c r="B81" t="n">
         <v>92873</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665371</v>
+        <v>665424</v>
       </c>
       <c r="R81" t="n">
-        <v>6564789</v>
+        <v>6564571</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,7 +9207,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150597</v>
+        <v>129150600</v>
       </c>
       <c r="B82" t="n">
         <v>92873</v>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665233</v>
+        <v>665346</v>
       </c>
       <c r="R82" t="n">
-        <v>6564718</v>
+        <v>6564670</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9314,7 +9314,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150575</v>
+        <v>129150603</v>
       </c>
       <c r="B83" t="n">
         <v>92873</v>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665457</v>
+        <v>665453</v>
       </c>
       <c r="R83" t="n">
-        <v>6564660</v>
+        <v>6564677</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,7 +9421,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150603</v>
+        <v>129150575</v>
       </c>
       <c r="B84" t="n">
         <v>92873</v>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665453</v>
+        <v>665457</v>
       </c>
       <c r="R84" t="n">
-        <v>6564677</v>
+        <v>6564660</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9635,7 +9635,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129150623</v>
+        <v>129150615</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>665233</v>
+        <v>665164</v>
       </c>
       <c r="R86" t="n">
-        <v>6564720</v>
+        <v>6564505</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9742,7 +9742,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129150615</v>
+        <v>129150623</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>665164</v>
+        <v>665233</v>
       </c>
       <c r="R87" t="n">
-        <v>6564505</v>
+        <v>6564720</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -4495,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150567</v>
+        <v>129150578</v>
       </c>
       <c r="B38" t="n">
         <v>92873</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665228</v>
+        <v>665443</v>
       </c>
       <c r="R38" t="n">
-        <v>6564499</v>
+        <v>6564659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,7 +4602,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150578</v>
+        <v>129150567</v>
       </c>
       <c r="B39" t="n">
         <v>92873</v>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665443</v>
+        <v>665228</v>
       </c>
       <c r="R39" t="n">
-        <v>6564659</v>
+        <v>6564499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150590</v>
+        <v>129150617</v>
       </c>
       <c r="B40" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665331</v>
+        <v>665376</v>
       </c>
       <c r="R40" t="n">
-        <v>6564765</v>
+        <v>6564598</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150606</v>
+        <v>129150616</v>
       </c>
       <c r="B41" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665503</v>
+        <v>665382</v>
       </c>
       <c r="R41" t="n">
-        <v>6564692</v>
+        <v>6564609</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150612</v>
+        <v>129150571</v>
       </c>
       <c r="B42" t="n">
         <v>92873</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665587</v>
+        <v>665408</v>
       </c>
       <c r="R42" t="n">
-        <v>6564768</v>
+        <v>6564551</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150571</v>
+        <v>129150569</v>
       </c>
       <c r="B43" t="n">
         <v>92873</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665408</v>
+        <v>665388</v>
       </c>
       <c r="R43" t="n">
-        <v>6564551</v>
+        <v>6564531</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150569</v>
+        <v>129150590</v>
       </c>
       <c r="B44" t="n">
         <v>92873</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665388</v>
+        <v>665331</v>
       </c>
       <c r="R44" t="n">
-        <v>6564531</v>
+        <v>6564765</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150617</v>
+        <v>129150606</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665376</v>
+        <v>665503</v>
       </c>
       <c r="R46" t="n">
-        <v>6564598</v>
+        <v>6564692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150616</v>
+        <v>129150612</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665382</v>
+        <v>665587</v>
       </c>
       <c r="R47" t="n">
-        <v>6564609</v>
+        <v>6564768</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150627</v>
+        <v>129150611</v>
       </c>
       <c r="B50" t="n">
-        <v>92331</v>
+        <v>92873</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665419</v>
+        <v>665607</v>
       </c>
       <c r="R50" t="n">
-        <v>6564672</v>
+        <v>6564770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B51" t="n">
         <v>92873</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150577</v>
+        <v>129150601</v>
       </c>
       <c r="B52" t="n">
         <v>92873</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665446</v>
+        <v>665364</v>
       </c>
       <c r="R52" t="n">
-        <v>6564659</v>
+        <v>6564665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150601</v>
+        <v>129150627</v>
       </c>
       <c r="B53" t="n">
-        <v>92873</v>
+        <v>92331</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665364</v>
+        <v>665419</v>
       </c>
       <c r="R53" t="n">
-        <v>6564665</v>
+        <v>6564672</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6528,7 +6528,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150626</v>
+        <v>129150628</v>
       </c>
       <c r="B57" t="n">
         <v>92331</v>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665260</v>
+        <v>665455</v>
       </c>
       <c r="R57" t="n">
-        <v>6564773</v>
+        <v>6564681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,32 +6635,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150618</v>
+        <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>92331</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>1958</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665400</v>
+        <v>665260</v>
       </c>
       <c r="R58" t="n">
-        <v>6564742</v>
+        <v>6564773</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150628</v>
+        <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>92331</v>
+        <v>91574</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1958</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665455</v>
+        <v>665183</v>
       </c>
       <c r="R59" t="n">
-        <v>6564681</v>
+        <v>6564505</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150557</v>
+        <v>129150618</v>
       </c>
       <c r="B60" t="n">
-        <v>91574</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665183</v>
+        <v>665400</v>
       </c>
       <c r="R60" t="n">
-        <v>6564505</v>
+        <v>6564742</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6956,32 +6956,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150583</v>
+        <v>129150619</v>
       </c>
       <c r="B61" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665372</v>
+        <v>665365</v>
       </c>
       <c r="R61" t="n">
-        <v>6564721</v>
+        <v>6564786</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,7 +7063,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B62" t="n">
         <v>92873</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R62" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150619</v>
+        <v>129150566</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665365</v>
+        <v>665194</v>
       </c>
       <c r="R63" t="n">
-        <v>6564786</v>
+        <v>6564498</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7384,7 +7384,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129150605</v>
+        <v>129150598</v>
       </c>
       <c r="B65" t="n">
         <v>92873</v>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>665484</v>
+        <v>665283</v>
       </c>
       <c r="R65" t="n">
-        <v>6564691</v>
+        <v>6564685</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,7 +7491,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150598</v>
+        <v>129150593</v>
       </c>
       <c r="B66" t="n">
         <v>92873</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665283</v>
+        <v>665256</v>
       </c>
       <c r="R66" t="n">
-        <v>6564685</v>
+        <v>6564756</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7598,7 +7598,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129150593</v>
+        <v>129150605</v>
       </c>
       <c r="B67" t="n">
         <v>92873</v>
@@ -7633,10 +7633,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>665256</v>
+        <v>665484</v>
       </c>
       <c r="R67" t="n">
-        <v>6564756</v>
+        <v>6564691</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8026,10 +8026,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129150595</v>
+        <v>129150556</v>
       </c>
       <c r="B71" t="n">
-        <v>92873</v>
+        <v>57887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8037,34 +8037,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665210</v>
+        <v>665406</v>
       </c>
       <c r="R71" t="n">
-        <v>6564762</v>
+        <v>6564548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8096,7 +8100,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8106,7 +8110,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8133,10 +8137,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150556</v>
+        <v>129150595</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>92873</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8144,38 +8148,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665406</v>
+        <v>665210</v>
       </c>
       <c r="R72" t="n">
-        <v>6564548</v>
+        <v>6564762</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150607</v>
+        <v>129150572</v>
       </c>
       <c r="B76" t="n">
         <v>92873</v>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665514</v>
+        <v>665424</v>
       </c>
       <c r="R76" t="n">
-        <v>6564684</v>
+        <v>6564571</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150581</v>
+        <v>129150607</v>
       </c>
       <c r="B77" t="n">
         <v>92873</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665366</v>
+        <v>665514</v>
       </c>
       <c r="R77" t="n">
-        <v>6564608</v>
+        <v>6564684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150589</v>
+        <v>129150581</v>
       </c>
       <c r="B78" t="n">
         <v>92873</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665371</v>
+        <v>665366</v>
       </c>
       <c r="R78" t="n">
-        <v>6564789</v>
+        <v>6564608</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150597</v>
+        <v>129150600</v>
       </c>
       <c r="B79" t="n">
         <v>92873</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665233</v>
+        <v>665346</v>
       </c>
       <c r="R79" t="n">
-        <v>6564718</v>
+        <v>6564670</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,32 +8993,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150629</v>
+        <v>129150589</v>
       </c>
       <c r="B80" t="n">
-        <v>92331</v>
+        <v>92873</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665507</v>
+        <v>665371</v>
       </c>
       <c r="R80" t="n">
-        <v>6564685</v>
+        <v>6564789</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150572</v>
+        <v>129150597</v>
       </c>
       <c r="B81" t="n">
         <v>92873</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665424</v>
+        <v>665233</v>
       </c>
       <c r="R81" t="n">
-        <v>6564571</v>
+        <v>6564718</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150600</v>
+        <v>129150629</v>
       </c>
       <c r="B82" t="n">
-        <v>92873</v>
+        <v>92331</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665346</v>
+        <v>665507</v>
       </c>
       <c r="R82" t="n">
-        <v>6564670</v>
+        <v>6564685</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9314,7 +9314,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150603</v>
+        <v>129150575</v>
       </c>
       <c r="B83" t="n">
         <v>92873</v>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665453</v>
+        <v>665457</v>
       </c>
       <c r="R83" t="n">
-        <v>6564677</v>
+        <v>6564660</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,7 +9421,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150575</v>
+        <v>129150603</v>
       </c>
       <c r="B84" t="n">
         <v>92873</v>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665457</v>
+        <v>665453</v>
       </c>
       <c r="R84" t="n">
-        <v>6564660</v>
+        <v>6564677</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9635,7 +9635,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129150615</v>
+        <v>129150623</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>665164</v>
+        <v>665233</v>
       </c>
       <c r="R86" t="n">
-        <v>6564505</v>
+        <v>6564720</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9742,7 +9742,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129150623</v>
+        <v>129150615</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>665233</v>
+        <v>665164</v>
       </c>
       <c r="R87" t="n">
-        <v>6564720</v>
+        <v>6564505</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -4174,32 +4174,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150620</v>
+        <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665358</v>
+        <v>665464</v>
       </c>
       <c r="R35" t="n">
-        <v>6564768</v>
+        <v>6564686</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150604</v>
+        <v>129150599</v>
       </c>
       <c r="B36" t="n">
         <v>92873</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665464</v>
+        <v>665294</v>
       </c>
       <c r="R36" t="n">
-        <v>6564686</v>
+        <v>6564670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150599</v>
+        <v>129150578</v>
       </c>
       <c r="B37" t="n">
         <v>92873</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665294</v>
+        <v>665443</v>
       </c>
       <c r="R37" t="n">
-        <v>6564670</v>
+        <v>6564659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150578</v>
+        <v>129150567</v>
       </c>
       <c r="B38" t="n">
         <v>92873</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665443</v>
+        <v>665228</v>
       </c>
       <c r="R38" t="n">
-        <v>6564659</v>
+        <v>6564499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4602,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150567</v>
+        <v>129150620</v>
       </c>
       <c r="B39" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665228</v>
+        <v>665358</v>
       </c>
       <c r="R39" t="n">
-        <v>6564499</v>
+        <v>6564768</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150617</v>
+        <v>129150571</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665376</v>
+        <v>665408</v>
       </c>
       <c r="R40" t="n">
-        <v>6564598</v>
+        <v>6564551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150616</v>
+        <v>129150569</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665382</v>
+        <v>665388</v>
       </c>
       <c r="R41" t="n">
-        <v>6564609</v>
+        <v>6564531</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150571</v>
+        <v>129150590</v>
       </c>
       <c r="B42" t="n">
         <v>92873</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665408</v>
+        <v>665331</v>
       </c>
       <c r="R42" t="n">
-        <v>6564551</v>
+        <v>6564765</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150569</v>
+        <v>129150602</v>
       </c>
       <c r="B43" t="n">
         <v>92873</v>
@@ -5068,7 +5068,7 @@
         <v>665388</v>
       </c>
       <c r="R43" t="n">
-        <v>6564531</v>
+        <v>6564663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150590</v>
+        <v>129150606</v>
       </c>
       <c r="B44" t="n">
         <v>92873</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665331</v>
+        <v>665503</v>
       </c>
       <c r="R44" t="n">
-        <v>6564765</v>
+        <v>6564692</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5244,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150602</v>
+        <v>129150612</v>
       </c>
       <c r="B45" t="n">
         <v>92873</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665388</v>
+        <v>665587</v>
       </c>
       <c r="R45" t="n">
-        <v>6564663</v>
+        <v>6564768</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150606</v>
+        <v>129150617</v>
       </c>
       <c r="B46" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665503</v>
+        <v>665376</v>
       </c>
       <c r="R46" t="n">
-        <v>6564692</v>
+        <v>6564598</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150612</v>
+        <v>129150616</v>
       </c>
       <c r="B47" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665587</v>
+        <v>665382</v>
       </c>
       <c r="R47" t="n">
-        <v>6564768</v>
+        <v>6564609</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5779,32 +5779,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150611</v>
+        <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92873</v>
+        <v>92331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665607</v>
+        <v>665419</v>
       </c>
       <c r="R50" t="n">
-        <v>6564770</v>
+        <v>6564672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
         <v>92873</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150601</v>
+        <v>129150577</v>
       </c>
       <c r="B52" t="n">
         <v>92873</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665364</v>
+        <v>665446</v>
       </c>
       <c r="R52" t="n">
-        <v>6564665</v>
+        <v>6564659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,32 +6100,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150627</v>
+        <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92331</v>
+        <v>92873</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665419</v>
+        <v>665364</v>
       </c>
       <c r="R53" t="n">
-        <v>6564672</v>
+        <v>6564665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6956,32 +6956,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150619</v>
+        <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665365</v>
+        <v>665372</v>
       </c>
       <c r="R61" t="n">
-        <v>6564786</v>
+        <v>6564721</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,7 +7063,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150583</v>
+        <v>129150566</v>
       </c>
       <c r="B62" t="n">
         <v>92873</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665372</v>
+        <v>665194</v>
       </c>
       <c r="R62" t="n">
-        <v>6564721</v>
+        <v>6564498</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150566</v>
+        <v>129150619</v>
       </c>
       <c r="B63" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665194</v>
+        <v>665365</v>
       </c>
       <c r="R63" t="n">
-        <v>6564498</v>
+        <v>6564786</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -3318,7 +3318,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150586</v>
+        <v>129150596</v>
       </c>
       <c r="B27" t="n">
         <v>92873</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665436</v>
+        <v>665174</v>
       </c>
       <c r="R27" t="n">
-        <v>6564778</v>
+        <v>6564743</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150585</v>
+        <v>129150586</v>
       </c>
       <c r="B28" t="n">
         <v>92873</v>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665424</v>
+        <v>665436</v>
       </c>
       <c r="R28" t="n">
-        <v>6564786</v>
+        <v>6564778</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150596</v>
+        <v>129150585</v>
       </c>
       <c r="B29" t="n">
         <v>92873</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665174</v>
+        <v>665424</v>
       </c>
       <c r="R29" t="n">
-        <v>6564743</v>
+        <v>6564786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150599</v>
+        <v>129150578</v>
       </c>
       <c r="B36" t="n">
         <v>92873</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665294</v>
+        <v>665443</v>
       </c>
       <c r="R36" t="n">
-        <v>6564670</v>
+        <v>6564659</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B37" t="n">
         <v>92873</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R37" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4709,7 +4709,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150571</v>
+        <v>129150602</v>
       </c>
       <c r="B40" t="n">
         <v>92873</v>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665408</v>
+        <v>665388</v>
       </c>
       <c r="R40" t="n">
-        <v>6564551</v>
+        <v>6564663</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,7 +4816,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150569</v>
+        <v>129150606</v>
       </c>
       <c r="B41" t="n">
         <v>92873</v>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665388</v>
+        <v>665503</v>
       </c>
       <c r="R41" t="n">
-        <v>6564531</v>
+        <v>6564692</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150590</v>
+        <v>129150612</v>
       </c>
       <c r="B42" t="n">
         <v>92873</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665331</v>
+        <v>665587</v>
       </c>
       <c r="R42" t="n">
-        <v>6564765</v>
+        <v>6564768</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150602</v>
+        <v>129150571</v>
       </c>
       <c r="B43" t="n">
         <v>92873</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665388</v>
+        <v>665408</v>
       </c>
       <c r="R43" t="n">
-        <v>6564663</v>
+        <v>6564551</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150606</v>
+        <v>129150569</v>
       </c>
       <c r="B44" t="n">
         <v>92873</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R44" t="n">
-        <v>6564692</v>
+        <v>6564531</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5244,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150612</v>
+        <v>129150590</v>
       </c>
       <c r="B45" t="n">
         <v>92873</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665587</v>
+        <v>665331</v>
       </c>
       <c r="R45" t="n">
-        <v>6564768</v>
+        <v>6564765</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5565,32 +5565,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129150568</v>
+        <v>129150621</v>
       </c>
       <c r="B48" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665276</v>
+        <v>665321</v>
       </c>
       <c r="R48" t="n">
-        <v>6564529</v>
+        <v>6564753</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,32 +5672,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129150621</v>
+        <v>129150568</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665321</v>
+        <v>665276</v>
       </c>
       <c r="R49" t="n">
-        <v>6564753</v>
+        <v>6564529</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150577</v>
       </c>
       <c r="B51" t="n">
         <v>92873</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665446</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564659</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150577</v>
+        <v>129150601</v>
       </c>
       <c r="B52" t="n">
         <v>92873</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665446</v>
+        <v>665364</v>
       </c>
       <c r="R52" t="n">
-        <v>6564659</v>
+        <v>6564665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,7 +6100,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150601</v>
+        <v>129150611</v>
       </c>
       <c r="B53" t="n">
         <v>92873</v>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665364</v>
+        <v>665607</v>
       </c>
       <c r="R53" t="n">
-        <v>6564665</v>
+        <v>6564770</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6314,7 +6314,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150580</v>
+        <v>129150570</v>
       </c>
       <c r="B55" t="n">
         <v>92873</v>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665374</v>
+        <v>665399</v>
       </c>
       <c r="R55" t="n">
-        <v>6564595</v>
+        <v>6564537</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6421,7 +6421,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129150570</v>
+        <v>129150580</v>
       </c>
       <c r="B56" t="n">
         <v>92873</v>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665399</v>
+        <v>665374</v>
       </c>
       <c r="R56" t="n">
-        <v>6564537</v>
+        <v>6564595</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6956,32 +6956,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150583</v>
+        <v>129150619</v>
       </c>
       <c r="B61" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665372</v>
+        <v>665365</v>
       </c>
       <c r="R61" t="n">
-        <v>6564721</v>
+        <v>6564786</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,7 +7063,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B62" t="n">
         <v>92873</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R62" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150619</v>
+        <v>129150566</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665365</v>
+        <v>665194</v>
       </c>
       <c r="R63" t="n">
-        <v>6564786</v>
+        <v>6564498</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7384,7 +7384,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129150598</v>
+        <v>129150593</v>
       </c>
       <c r="B65" t="n">
         <v>92873</v>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>665283</v>
+        <v>665256</v>
       </c>
       <c r="R65" t="n">
-        <v>6564685</v>
+        <v>6564756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,7 +7491,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150593</v>
+        <v>129150598</v>
       </c>
       <c r="B66" t="n">
         <v>92873</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665256</v>
+        <v>665283</v>
       </c>
       <c r="R66" t="n">
-        <v>6564756</v>
+        <v>6564685</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8244,32 +8244,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150610</v>
+        <v>129150622</v>
       </c>
       <c r="B73" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665640</v>
+        <v>665194</v>
       </c>
       <c r="R73" t="n">
-        <v>6564667</v>
+        <v>6564740</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8458,32 +8458,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150622</v>
+        <v>129150610</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665194</v>
+        <v>665640</v>
       </c>
       <c r="R75" t="n">
-        <v>6564740</v>
+        <v>6564667</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150572</v>
+        <v>129150629</v>
       </c>
       <c r="B76" t="n">
-        <v>92873</v>
+        <v>92331</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665424</v>
+        <v>665507</v>
       </c>
       <c r="R76" t="n">
-        <v>6564571</v>
+        <v>6564685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,7 +8672,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150607</v>
+        <v>129150572</v>
       </c>
       <c r="B77" t="n">
         <v>92873</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665514</v>
+        <v>665424</v>
       </c>
       <c r="R77" t="n">
-        <v>6564684</v>
+        <v>6564571</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150581</v>
+        <v>129150600</v>
       </c>
       <c r="B78" t="n">
         <v>92873</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665366</v>
+        <v>665346</v>
       </c>
       <c r="R78" t="n">
-        <v>6564608</v>
+        <v>6564670</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150600</v>
+        <v>129150589</v>
       </c>
       <c r="B79" t="n">
         <v>92873</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665346</v>
+        <v>665371</v>
       </c>
       <c r="R79" t="n">
-        <v>6564670</v>
+        <v>6564789</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,7 +8993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150589</v>
+        <v>129150607</v>
       </c>
       <c r="B80" t="n">
         <v>92873</v>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665371</v>
+        <v>665514</v>
       </c>
       <c r="R80" t="n">
-        <v>6564789</v>
+        <v>6564684</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150597</v>
+        <v>129150581</v>
       </c>
       <c r="B81" t="n">
         <v>92873</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665233</v>
+        <v>665366</v>
       </c>
       <c r="R81" t="n">
-        <v>6564718</v>
+        <v>6564608</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150629</v>
+        <v>129150597</v>
       </c>
       <c r="B82" t="n">
-        <v>92331</v>
+        <v>92873</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665507</v>
+        <v>665233</v>
       </c>
       <c r="R82" t="n">
-        <v>6564685</v>
+        <v>6564718</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9421,7 +9421,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150603</v>
+        <v>129150588</v>
       </c>
       <c r="B84" t="n">
         <v>92873</v>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665453</v>
+        <v>665414</v>
       </c>
       <c r="R84" t="n">
-        <v>6564677</v>
+        <v>6564728</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9528,7 +9528,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129150588</v>
+        <v>129150603</v>
       </c>
       <c r="B85" t="n">
         <v>92873</v>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>665414</v>
+        <v>665453</v>
       </c>
       <c r="R85" t="n">
-        <v>6564728</v>
+        <v>6564677</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -3318,7 +3318,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150596</v>
+        <v>129150586</v>
       </c>
       <c r="B27" t="n">
         <v>92873</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665174</v>
+        <v>665436</v>
       </c>
       <c r="R27" t="n">
-        <v>6564743</v>
+        <v>6564778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150586</v>
+        <v>129150585</v>
       </c>
       <c r="B28" t="n">
         <v>92873</v>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665436</v>
+        <v>665424</v>
       </c>
       <c r="R28" t="n">
-        <v>6564778</v>
+        <v>6564786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150585</v>
+        <v>129150596</v>
       </c>
       <c r="B29" t="n">
         <v>92873</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665424</v>
+        <v>665174</v>
       </c>
       <c r="R29" t="n">
-        <v>6564786</v>
+        <v>6564743</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4281,7 +4281,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150578</v>
+        <v>129150599</v>
       </c>
       <c r="B36" t="n">
         <v>92873</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665443</v>
+        <v>665294</v>
       </c>
       <c r="R36" t="n">
-        <v>6564659</v>
+        <v>6564670</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150599</v>
+        <v>129150578</v>
       </c>
       <c r="B37" t="n">
         <v>92873</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665294</v>
+        <v>665443</v>
       </c>
       <c r="R37" t="n">
-        <v>6564670</v>
+        <v>6564659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4709,7 +4709,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150602</v>
+        <v>129150571</v>
       </c>
       <c r="B40" t="n">
         <v>92873</v>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665388</v>
+        <v>665408</v>
       </c>
       <c r="R40" t="n">
-        <v>6564663</v>
+        <v>6564551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,7 +4816,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150606</v>
+        <v>129150590</v>
       </c>
       <c r="B41" t="n">
         <v>92873</v>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665503</v>
+        <v>665331</v>
       </c>
       <c r="R41" t="n">
-        <v>6564692</v>
+        <v>6564765</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150612</v>
+        <v>129150602</v>
       </c>
       <c r="B42" t="n">
         <v>92873</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665587</v>
+        <v>665388</v>
       </c>
       <c r="R42" t="n">
-        <v>6564768</v>
+        <v>6564663</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150571</v>
+        <v>129150606</v>
       </c>
       <c r="B43" t="n">
         <v>92873</v>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665408</v>
+        <v>665503</v>
       </c>
       <c r="R43" t="n">
-        <v>6564551</v>
+        <v>6564692</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150569</v>
+        <v>129150612</v>
       </c>
       <c r="B44" t="n">
         <v>92873</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665388</v>
+        <v>665587</v>
       </c>
       <c r="R44" t="n">
-        <v>6564531</v>
+        <v>6564768</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,32 +5244,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150590</v>
+        <v>129150617</v>
       </c>
       <c r="B45" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665331</v>
+        <v>665376</v>
       </c>
       <c r="R45" t="n">
-        <v>6564765</v>
+        <v>6564598</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,7 +5351,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150617</v>
+        <v>129150616</v>
       </c>
       <c r="B46" t="n">
         <v>8450</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665376</v>
+        <v>665382</v>
       </c>
       <c r="R46" t="n">
-        <v>6564598</v>
+        <v>6564609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,32 +5458,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150616</v>
+        <v>129150569</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665382</v>
+        <v>665388</v>
       </c>
       <c r="R47" t="n">
-        <v>6564609</v>
+        <v>6564531</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5565,32 +5565,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129150621</v>
+        <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665321</v>
+        <v>665276</v>
       </c>
       <c r="R48" t="n">
-        <v>6564753</v>
+        <v>6564529</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,32 +5672,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129150568</v>
+        <v>129150621</v>
       </c>
       <c r="B49" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665276</v>
+        <v>665321</v>
       </c>
       <c r="R49" t="n">
-        <v>6564529</v>
+        <v>6564753</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150577</v>
+        <v>129150611</v>
       </c>
       <c r="B51" t="n">
         <v>92873</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665446</v>
+        <v>665607</v>
       </c>
       <c r="R51" t="n">
-        <v>6564659</v>
+        <v>6564770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150601</v>
+        <v>129150577</v>
       </c>
       <c r="B52" t="n">
         <v>92873</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665364</v>
+        <v>665446</v>
       </c>
       <c r="R52" t="n">
-        <v>6564665</v>
+        <v>6564659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,7 +6100,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150611</v>
+        <v>129150601</v>
       </c>
       <c r="B53" t="n">
         <v>92873</v>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665607</v>
+        <v>665364</v>
       </c>
       <c r="R53" t="n">
-        <v>6564770</v>
+        <v>6564665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6207,7 +6207,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150591</v>
+        <v>129150580</v>
       </c>
       <c r="B54" t="n">
         <v>92873</v>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665318</v>
+        <v>665374</v>
       </c>
       <c r="R54" t="n">
-        <v>6564762</v>
+        <v>6564595</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,7 +6314,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150570</v>
+        <v>129150591</v>
       </c>
       <c r="B55" t="n">
         <v>92873</v>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665399</v>
+        <v>665318</v>
       </c>
       <c r="R55" t="n">
-        <v>6564537</v>
+        <v>6564762</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6421,7 +6421,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129150580</v>
+        <v>129150570</v>
       </c>
       <c r="B56" t="n">
         <v>92873</v>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665374</v>
+        <v>665399</v>
       </c>
       <c r="R56" t="n">
-        <v>6564595</v>
+        <v>6564537</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6528,32 +6528,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150628</v>
+        <v>129150557</v>
       </c>
       <c r="B57" t="n">
-        <v>92331</v>
+        <v>91574</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1958</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665455</v>
+        <v>665183</v>
       </c>
       <c r="R57" t="n">
-        <v>6564681</v>
+        <v>6564505</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,7 +6635,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150626</v>
+        <v>129150628</v>
       </c>
       <c r="B58" t="n">
         <v>92331</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665260</v>
+        <v>665455</v>
       </c>
       <c r="R58" t="n">
-        <v>6564773</v>
+        <v>6564681</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150557</v>
+        <v>129150626</v>
       </c>
       <c r="B59" t="n">
-        <v>91574</v>
+        <v>92331</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>1958</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665183</v>
+        <v>665260</v>
       </c>
       <c r="R59" t="n">
-        <v>6564505</v>
+        <v>6564773</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6956,32 +6956,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150619</v>
+        <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665365</v>
+        <v>665372</v>
       </c>
       <c r="R61" t="n">
-        <v>6564786</v>
+        <v>6564721</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,7 +7063,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150583</v>
+        <v>129150566</v>
       </c>
       <c r="B62" t="n">
         <v>92873</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665372</v>
+        <v>665194</v>
       </c>
       <c r="R62" t="n">
-        <v>6564721</v>
+        <v>6564498</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150566</v>
+        <v>129150619</v>
       </c>
       <c r="B63" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665194</v>
+        <v>665365</v>
       </c>
       <c r="R63" t="n">
-        <v>6564498</v>
+        <v>6564786</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7384,7 +7384,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129150593</v>
+        <v>129150598</v>
       </c>
       <c r="B65" t="n">
         <v>92873</v>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>665256</v>
+        <v>665283</v>
       </c>
       <c r="R65" t="n">
-        <v>6564756</v>
+        <v>6564685</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,7 +7491,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150598</v>
+        <v>129150593</v>
       </c>
       <c r="B66" t="n">
         <v>92873</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665283</v>
+        <v>665256</v>
       </c>
       <c r="R66" t="n">
-        <v>6564685</v>
+        <v>6564756</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8026,10 +8026,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129150556</v>
+        <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>57887</v>
+        <v>92873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8037,38 +8037,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665406</v>
+        <v>665210</v>
       </c>
       <c r="R71" t="n">
-        <v>6564548</v>
+        <v>6564762</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8100,7 +8096,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8110,7 +8106,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8137,10 +8133,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150595</v>
+        <v>129150556</v>
       </c>
       <c r="B72" t="n">
-        <v>92873</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8148,34 +8144,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665210</v>
+        <v>665406</v>
       </c>
       <c r="R72" t="n">
-        <v>6564762</v>
+        <v>6564548</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8351,7 +8351,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150609</v>
+        <v>129150610</v>
       </c>
       <c r="B74" t="n">
         <v>92873</v>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665505</v>
+        <v>665640</v>
       </c>
       <c r="R74" t="n">
-        <v>6564674</v>
+        <v>6564667</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8458,7 +8458,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B75" t="n">
         <v>92873</v>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R75" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150600</v>
+        <v>129150607</v>
       </c>
       <c r="B78" t="n">
         <v>92873</v>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665346</v>
+        <v>665514</v>
       </c>
       <c r="R78" t="n">
-        <v>6564670</v>
+        <v>6564684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150589</v>
+        <v>129150581</v>
       </c>
       <c r="B79" t="n">
         <v>92873</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665371</v>
+        <v>665366</v>
       </c>
       <c r="R79" t="n">
-        <v>6564789</v>
+        <v>6564608</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,7 +8993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150607</v>
+        <v>129150600</v>
       </c>
       <c r="B80" t="n">
         <v>92873</v>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665514</v>
+        <v>665346</v>
       </c>
       <c r="R80" t="n">
-        <v>6564684</v>
+        <v>6564670</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,7 +9100,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150581</v>
+        <v>129150589</v>
       </c>
       <c r="B81" t="n">
         <v>92873</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665366</v>
+        <v>665371</v>
       </c>
       <c r="R81" t="n">
-        <v>6564608</v>
+        <v>6564789</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9421,7 +9421,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150588</v>
+        <v>129150603</v>
       </c>
       <c r="B84" t="n">
         <v>92873</v>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665414</v>
+        <v>665453</v>
       </c>
       <c r="R84" t="n">
-        <v>6564728</v>
+        <v>6564677</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9528,7 +9528,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129150603</v>
+        <v>129150588</v>
       </c>
       <c r="B85" t="n">
         <v>92873</v>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>665453</v>
+        <v>665414</v>
       </c>
       <c r="R85" t="n">
-        <v>6564677</v>
+        <v>6564728</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>129150574</v>
       </c>
       <c r="B26" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129150586</v>
       </c>
       <c r="B27" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>129150585</v>
       </c>
       <c r="B28" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>129150596</v>
       </c>
       <c r="B29" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>129150565</v>
       </c>
       <c r="B30" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129150579</v>
       </c>
       <c r="B31" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>129150584</v>
       </c>
       <c r="B32" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>129150582</v>
       </c>
       <c r="B33" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129150576</v>
       </c>
       <c r="B34" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>129150604</v>
       </c>
       <c r="B35" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>129150599</v>
       </c>
       <c r="B36" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>129150578</v>
       </c>
       <c r="B37" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>129150567</v>
       </c>
       <c r="B38" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4709,32 +4709,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150571</v>
+        <v>129150616</v>
       </c>
       <c r="B40" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665408</v>
+        <v>665382</v>
       </c>
       <c r="R40" t="n">
-        <v>6564551</v>
+        <v>6564609</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4816,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150590</v>
+        <v>129150617</v>
       </c>
       <c r="B41" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665331</v>
+        <v>665376</v>
       </c>
       <c r="R41" t="n">
-        <v>6564765</v>
+        <v>6564598</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4923,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150602</v>
+        <v>129150571</v>
       </c>
       <c r="B42" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665388</v>
+        <v>665408</v>
       </c>
       <c r="R42" t="n">
-        <v>6564663</v>
+        <v>6564551</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,10 +5030,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150606</v>
+        <v>129150569</v>
       </c>
       <c r="B43" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665503</v>
+        <v>665388</v>
       </c>
       <c r="R43" t="n">
-        <v>6564692</v>
+        <v>6564531</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150612</v>
+        <v>129150590</v>
       </c>
       <c r="B44" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665587</v>
+        <v>665331</v>
       </c>
       <c r="R44" t="n">
-        <v>6564768</v>
+        <v>6564765</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,32 +5244,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150617</v>
+        <v>129150602</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>92901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665376</v>
+        <v>665388</v>
       </c>
       <c r="R45" t="n">
-        <v>6564598</v>
+        <v>6564663</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,32 +5351,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150616</v>
+        <v>129150606</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>92901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665382</v>
+        <v>665503</v>
       </c>
       <c r="R46" t="n">
-        <v>6564609</v>
+        <v>6564692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,10 +5458,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150569</v>
+        <v>129150612</v>
       </c>
       <c r="B47" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665388</v>
+        <v>665587</v>
       </c>
       <c r="R47" t="n">
-        <v>6564531</v>
+        <v>6564768</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5568,7 +5568,7 @@
         <v>129150568</v>
       </c>
       <c r="B48" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>129150627</v>
       </c>
       <c r="B50" t="n">
-        <v>92331</v>
+        <v>92359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>129150611</v>
       </c>
       <c r="B51" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>129150577</v>
       </c>
       <c r="B52" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>129150601</v>
       </c>
       <c r="B53" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150580</v>
+        <v>129150591</v>
       </c>
       <c r="B54" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665374</v>
+        <v>665318</v>
       </c>
       <c r="R54" t="n">
-        <v>6564595</v>
+        <v>6564762</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,10 +6314,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150591</v>
+        <v>129150580</v>
       </c>
       <c r="B55" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665318</v>
+        <v>665374</v>
       </c>
       <c r="R55" t="n">
-        <v>6564762</v>
+        <v>6564595</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6424,7 +6424,7 @@
         <v>129150570</v>
       </c>
       <c r="B56" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6528,32 +6528,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150557</v>
+        <v>129150628</v>
       </c>
       <c r="B57" t="n">
-        <v>91574</v>
+        <v>92359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>1958</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665183</v>
+        <v>665455</v>
       </c>
       <c r="R57" t="n">
-        <v>6564505</v>
+        <v>6564681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,10 +6635,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150628</v>
+        <v>129150626</v>
       </c>
       <c r="B58" t="n">
-        <v>92331</v>
+        <v>92359</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665455</v>
+        <v>665260</v>
       </c>
       <c r="R58" t="n">
-        <v>6564681</v>
+        <v>6564773</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150626</v>
+        <v>129150557</v>
       </c>
       <c r="B59" t="n">
-        <v>92331</v>
+        <v>91602</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1958</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665260</v>
+        <v>665183</v>
       </c>
       <c r="R59" t="n">
-        <v>6564773</v>
+        <v>6564505</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6959,7 +6959,7 @@
         <v>129150583</v>
       </c>
       <c r="B61" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>129150566</v>
       </c>
       <c r="B62" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>129150594</v>
       </c>
       <c r="B64" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129150598</v>
       </c>
       <c r="B65" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>129150593</v>
       </c>
       <c r="B66" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>129150605</v>
       </c>
       <c r="B67" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7705,32 +7705,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150625</v>
+        <v>129150613</v>
       </c>
       <c r="B68" t="n">
-        <v>92331</v>
+        <v>92901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665422</v>
+        <v>665566</v>
       </c>
       <c r="R68" t="n">
-        <v>6564565</v>
+        <v>6564813</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7812,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150613</v>
+        <v>129150625</v>
       </c>
       <c r="B69" t="n">
-        <v>92873</v>
+        <v>92359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7847,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665566</v>
+        <v>665422</v>
       </c>
       <c r="R69" t="n">
-        <v>6564813</v>
+        <v>6564565</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7922,7 +7922,7 @@
         <v>129150587</v>
       </c>
       <c r="B70" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>129150595</v>
       </c>
       <c r="B71" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>129150556</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8244,32 +8244,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150622</v>
+        <v>129150610</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>92901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665194</v>
+        <v>665640</v>
       </c>
       <c r="R73" t="n">
-        <v>6564740</v>
+        <v>6564667</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B74" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R74" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8458,32 +8458,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150609</v>
+        <v>129150622</v>
       </c>
       <c r="B75" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665505</v>
+        <v>665194</v>
       </c>
       <c r="R75" t="n">
-        <v>6564674</v>
+        <v>6564740</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8565,32 +8565,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150629</v>
+        <v>129150572</v>
       </c>
       <c r="B76" t="n">
-        <v>92331</v>
+        <v>92901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665507</v>
+        <v>665424</v>
       </c>
       <c r="R76" t="n">
-        <v>6564685</v>
+        <v>6564571</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,10 +8672,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150572</v>
+        <v>129150607</v>
       </c>
       <c r="B77" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665424</v>
+        <v>665514</v>
       </c>
       <c r="R77" t="n">
-        <v>6564571</v>
+        <v>6564684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150607</v>
+        <v>129150581</v>
       </c>
       <c r="B78" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665514</v>
+        <v>665366</v>
       </c>
       <c r="R78" t="n">
-        <v>6564684</v>
+        <v>6564608</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8886,10 +8886,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150581</v>
+        <v>129150600</v>
       </c>
       <c r="B79" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665366</v>
+        <v>665346</v>
       </c>
       <c r="R79" t="n">
-        <v>6564608</v>
+        <v>6564670</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,10 +8993,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150600</v>
+        <v>129150589</v>
       </c>
       <c r="B80" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665346</v>
+        <v>665371</v>
       </c>
       <c r="R80" t="n">
-        <v>6564670</v>
+        <v>6564789</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9100,10 +9100,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150589</v>
+        <v>129150597</v>
       </c>
       <c r="B81" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665371</v>
+        <v>665233</v>
       </c>
       <c r="R81" t="n">
-        <v>6564789</v>
+        <v>6564718</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9207,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150597</v>
+        <v>129150629</v>
       </c>
       <c r="B82" t="n">
-        <v>92873</v>
+        <v>92359</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9242,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665233</v>
+        <v>665507</v>
       </c>
       <c r="R82" t="n">
-        <v>6564718</v>
+        <v>6564685</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9317,7 +9317,7 @@
         <v>129150575</v>
       </c>
       <c r="B83" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>129150603</v>
       </c>
       <c r="B84" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>129150588</v>
       </c>
       <c r="B85" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -6528,32 +6528,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150628</v>
+        <v>129150618</v>
       </c>
       <c r="B57" t="n">
-        <v>92359</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1958</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665455</v>
+        <v>665400</v>
       </c>
       <c r="R57" t="n">
-        <v>6564681</v>
+        <v>6564742</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,32 +6635,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150626</v>
+        <v>129150557</v>
       </c>
       <c r="B58" t="n">
-        <v>92359</v>
+        <v>91602</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1958</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665260</v>
+        <v>665183</v>
       </c>
       <c r="R58" t="n">
-        <v>6564773</v>
+        <v>6564505</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6742,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150557</v>
+        <v>129150628</v>
       </c>
       <c r="B59" t="n">
-        <v>91602</v>
+        <v>92359</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>1958</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665183</v>
+        <v>665455</v>
       </c>
       <c r="R59" t="n">
-        <v>6564505</v>
+        <v>6564681</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,32 +6849,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150618</v>
+        <v>129150626</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>92359</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>1958</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665400</v>
+        <v>665260</v>
       </c>
       <c r="R60" t="n">
-        <v>6564742</v>
+        <v>6564773</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6956,32 +6956,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150583</v>
+        <v>129150619</v>
       </c>
       <c r="B61" t="n">
-        <v>92901</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665372</v>
+        <v>665365</v>
       </c>
       <c r="R61" t="n">
-        <v>6564721</v>
+        <v>6564786</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,7 +7063,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150566</v>
+        <v>129150583</v>
       </c>
       <c r="B62" t="n">
         <v>92901</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665194</v>
+        <v>665372</v>
       </c>
       <c r="R62" t="n">
-        <v>6564498</v>
+        <v>6564721</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150619</v>
+        <v>129150566</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>92901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665365</v>
+        <v>665194</v>
       </c>
       <c r="R63" t="n">
-        <v>6564786</v>
+        <v>6564498</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128536275</v>
+        <v>129150625</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665586</v>
+        <v>665422</v>
       </c>
       <c r="R2" t="n">
-        <v>6564841</v>
+        <v>6564565</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Talldominerad torr-frisk mark</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Bökmark</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Bökmark</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128970268</v>
+        <v>129150626</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
+        <v>92692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665540</v>
+        <v>665260</v>
       </c>
       <c r="R3" t="n">
-        <v>6564865</v>
+        <v>6564773</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128970277</v>
+        <v>129150627</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665424</v>
+        <v>665419</v>
       </c>
       <c r="R4" t="n">
-        <v>6565079</v>
+        <v>6564672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128970274</v>
+        <v>129150628</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665452</v>
+        <v>665455</v>
       </c>
       <c r="R5" t="n">
-        <v>6565050</v>
+        <v>6564681</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128970265</v>
+        <v>129150629</v>
       </c>
       <c r="B6" t="n">
-        <v>92858</v>
+        <v>92692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>1958</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665424</v>
+        <v>665507</v>
       </c>
       <c r="R6" t="n">
-        <v>6565096</v>
+        <v>6564685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128970270</v>
+        <v>129107651</v>
       </c>
       <c r="B7" t="n">
-        <v>92870</v>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665540</v>
+        <v>665357</v>
       </c>
       <c r="R7" t="n">
-        <v>6564894</v>
+        <v>6564680</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,22 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:24</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:24</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128970269</v>
+        <v>128970264</v>
       </c>
       <c r="B8" t="n">
-        <v>92870</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665528</v>
+        <v>665464</v>
       </c>
       <c r="R8" t="n">
-        <v>6564890</v>
+        <v>6565020</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1413,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,32 +1414,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128970284</v>
+        <v>129150557</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665545</v>
+        <v>665183</v>
       </c>
       <c r="R9" t="n">
-        <v>6564914</v>
+        <v>6564505</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,22 +1479,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128970275</v>
+        <v>128970265</v>
       </c>
       <c r="B10" t="n">
-        <v>92870</v>
+        <v>93223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1582,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665443</v>
+        <v>665424</v>
       </c>
       <c r="R10" t="n">
-        <v>6565057</v>
+        <v>6565096</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1627,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128970267</v>
+        <v>128536275</v>
       </c>
       <c r="B11" t="n">
-        <v>92870</v>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,20 +1656,31 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665571</v>
+        <v>665586</v>
       </c>
       <c r="R11" t="n">
-        <v>6564879</v>
+        <v>6564841</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1719,22 +1704,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Talldominerad torr-frisk mark</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1739,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Sara Bökmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Sara Bökmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128970271</v>
+        <v>128970267</v>
       </c>
       <c r="B12" t="n">
-        <v>92870</v>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,10 +1786,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665506</v>
+        <v>665571</v>
       </c>
       <c r="R12" t="n">
-        <v>6564967</v>
+        <v>6564879</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1821,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1841,7 +1831,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128970281</v>
+        <v>128970268</v>
       </c>
       <c r="B13" t="n">
-        <v>92870</v>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665505</v>
+        <v>665540</v>
       </c>
       <c r="R13" t="n">
-        <v>6565027</v>
+        <v>6564865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,7 +1928,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1948,7 +1938,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128970264</v>
+        <v>128970269</v>
       </c>
       <c r="B14" t="n">
-        <v>91571</v>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1976,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665464</v>
+        <v>665528</v>
       </c>
       <c r="R14" t="n">
-        <v>6565020</v>
+        <v>6564890</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2035,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2055,7 +2045,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128970273</v>
+        <v>128970270</v>
       </c>
       <c r="B15" t="n">
-        <v>92870</v>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665465</v>
+        <v>665540</v>
       </c>
       <c r="R15" t="n">
-        <v>6565043</v>
+        <v>6564894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2142,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2162,7 +2152,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128970272</v>
+        <v>128970271</v>
       </c>
       <c r="B16" t="n">
-        <v>92870</v>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665504</v>
+        <v>665506</v>
       </c>
       <c r="R16" t="n">
-        <v>6564970</v>
+        <v>6564967</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128970278</v>
+        <v>128970272</v>
       </c>
       <c r="B17" t="n">
-        <v>92870</v>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665427</v>
+        <v>665504</v>
       </c>
       <c r="R17" t="n">
-        <v>6565093</v>
+        <v>6564970</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,7 +2356,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2376,7 +2366,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128970282</v>
+        <v>128970273</v>
       </c>
       <c r="B18" t="n">
-        <v>92870</v>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,10 +2428,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665516</v>
+        <v>665465</v>
       </c>
       <c r="R18" t="n">
-        <v>6565017</v>
+        <v>6565043</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,7 +2463,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2483,7 +2473,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2510,10 +2500,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129052185</v>
+        <v>128970274</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>93235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,49 +2511,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brantbrink, Brantbrink, Srm</t>
+          <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665290</v>
+        <v>665452</v>
       </c>
       <c r="R19" t="n">
-        <v>6564770</v>
+        <v>6565050</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,22 +2565,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2617,22 +2595,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129107656</v>
+        <v>128970275</v>
       </c>
       <c r="B20" t="n">
-        <v>92873</v>
+        <v>93235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2664,10 +2642,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665526</v>
+        <v>665443</v>
       </c>
       <c r="R20" t="n">
-        <v>6564766</v>
+        <v>6565057</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,12 +2672,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,22 +2702,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129107654</v>
+        <v>128970277</v>
       </c>
       <c r="B21" t="n">
-        <v>92873</v>
+        <v>93235</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2761,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665344</v>
+        <v>665424</v>
       </c>
       <c r="R21" t="n">
-        <v>6564658</v>
+        <v>6565079</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,12 +2779,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2811,22 +2809,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129107653</v>
+        <v>128970278</v>
       </c>
       <c r="B22" t="n">
-        <v>92873</v>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2858,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665292</v>
+        <v>665427</v>
       </c>
       <c r="R22" t="n">
-        <v>6564679</v>
+        <v>6565093</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2888,12 +2886,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2908,44 +2916,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129107651</v>
+        <v>128970279</v>
       </c>
       <c r="B23" t="n">
-        <v>92847</v>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2955,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665357</v>
+        <v>665487</v>
       </c>
       <c r="R23" t="n">
-        <v>6564680</v>
+        <v>6565071</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,12 +2993,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3005,22 +3023,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129107655</v>
+        <v>128970280</v>
       </c>
       <c r="B24" t="n">
-        <v>92873</v>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3052,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665397</v>
+        <v>665491</v>
       </c>
       <c r="R24" t="n">
-        <v>6564688</v>
+        <v>6565068</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,12 +3100,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3102,22 +3130,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129107649</v>
+        <v>128970281</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,21 +3153,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3149,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665272</v>
+        <v>665505</v>
       </c>
       <c r="R25" t="n">
-        <v>6564714</v>
+        <v>6565027</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,12 +3207,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3199,22 +3237,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129150574</v>
+        <v>128970282</v>
       </c>
       <c r="B26" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665437</v>
+        <v>665516</v>
       </c>
       <c r="R26" t="n">
-        <v>6564617</v>
+        <v>6565017</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3276,22 +3314,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129150586</v>
+        <v>129107653</v>
       </c>
       <c r="B27" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665436</v>
+        <v>665292</v>
       </c>
       <c r="R27" t="n">
-        <v>6564778</v>
+        <v>6564679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3383,22 +3421,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3413,22 +3441,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129150585</v>
+        <v>129107654</v>
       </c>
       <c r="B28" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,10 +3488,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665424</v>
+        <v>665344</v>
       </c>
       <c r="R28" t="n">
-        <v>6564786</v>
+        <v>6564658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3490,22 +3518,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3520,22 +3538,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129150596</v>
+        <v>129107655</v>
       </c>
       <c r="B29" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3567,10 +3585,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665174</v>
+        <v>665397</v>
       </c>
       <c r="R29" t="n">
-        <v>6564743</v>
+        <v>6564688</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3597,22 +3615,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3627,22 +3635,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129150565</v>
+        <v>129107656</v>
       </c>
       <c r="B30" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665143</v>
+        <v>665526</v>
       </c>
       <c r="R30" t="n">
-        <v>6564565</v>
+        <v>6564766</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3704,22 +3712,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3734,22 +3732,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129150579</v>
+        <v>129150565</v>
       </c>
       <c r="B31" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665438</v>
+        <v>665143</v>
       </c>
       <c r="R31" t="n">
-        <v>6564656</v>
+        <v>6564565</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3814,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3826,7 +3824,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,10 +3851,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129150584</v>
+        <v>129150566</v>
       </c>
       <c r="B32" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665409</v>
+        <v>665194</v>
       </c>
       <c r="R32" t="n">
-        <v>6564786</v>
+        <v>6564498</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3921,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3931,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3958,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129150582</v>
+        <v>129150567</v>
       </c>
       <c r="B33" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,10 +3993,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665370</v>
+        <v>665228</v>
       </c>
       <c r="R33" t="n">
-        <v>6564621</v>
+        <v>6564499</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4028,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4038,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129150576</v>
+        <v>129150568</v>
       </c>
       <c r="B34" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4102,10 +4100,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665452</v>
+        <v>665276</v>
       </c>
       <c r="R34" t="n">
-        <v>6564659</v>
+        <v>6564529</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4137,7 +4135,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4147,7 +4145,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4174,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129150604</v>
+        <v>129150569</v>
       </c>
       <c r="B35" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4209,10 +4207,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665464</v>
+        <v>665388</v>
       </c>
       <c r="R35" t="n">
-        <v>6564686</v>
+        <v>6564531</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4242,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4252,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,10 +4279,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129150599</v>
+        <v>129150570</v>
       </c>
       <c r="B36" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665294</v>
+        <v>665399</v>
       </c>
       <c r="R36" t="n">
-        <v>6564670</v>
+        <v>6564537</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,7 +4349,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4361,7 +4359,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4388,10 +4386,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129150578</v>
+        <v>129150571</v>
       </c>
       <c r="B37" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4423,10 +4421,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665443</v>
+        <v>665408</v>
       </c>
       <c r="R37" t="n">
-        <v>6564659</v>
+        <v>6564551</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,7 +4456,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4468,7 +4466,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4495,10 +4493,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129150567</v>
+        <v>129150572</v>
       </c>
       <c r="B38" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,10 +4528,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665228</v>
+        <v>665424</v>
       </c>
       <c r="R38" t="n">
-        <v>6564499</v>
+        <v>6564571</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,7 +4563,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4575,7 +4573,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,32 +4600,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129150620</v>
+        <v>129150573</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>93235</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4635,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665358</v>
+        <v>665455</v>
       </c>
       <c r="R39" t="n">
-        <v>6564768</v>
+        <v>6564594</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,7 +4670,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4682,7 +4680,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,32 +4707,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129150616</v>
+        <v>129150574</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>93235</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4744,10 +4742,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665382</v>
+        <v>665437</v>
       </c>
       <c r="R40" t="n">
-        <v>6564609</v>
+        <v>6564617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,7 +4777,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4789,7 +4787,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,32 +4814,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129150617</v>
+        <v>129150575</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>93235</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4851,10 +4849,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665376</v>
+        <v>665457</v>
       </c>
       <c r="R41" t="n">
-        <v>6564598</v>
+        <v>6564660</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,7 +4884,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4896,7 +4894,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4921,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129150571</v>
+        <v>129150576</v>
       </c>
       <c r="B42" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4958,10 +4956,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665408</v>
+        <v>665452</v>
       </c>
       <c r="R42" t="n">
-        <v>6564551</v>
+        <v>6564659</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4991,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5003,7 +5001,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,10 +5028,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129150569</v>
+        <v>129150577</v>
       </c>
       <c r="B43" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5065,10 +5063,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665388</v>
+        <v>665446</v>
       </c>
       <c r="R43" t="n">
-        <v>6564531</v>
+        <v>6564659</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,7 +5098,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5110,7 +5108,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,10 +5135,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129150590</v>
+        <v>129150578</v>
       </c>
       <c r="B44" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,10 +5170,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665331</v>
+        <v>665443</v>
       </c>
       <c r="R44" t="n">
-        <v>6564765</v>
+        <v>6564659</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5207,7 +5205,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5217,7 +5215,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,10 +5242,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129150602</v>
+        <v>129150579</v>
       </c>
       <c r="B45" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5279,10 +5277,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665388</v>
+        <v>665438</v>
       </c>
       <c r="R45" t="n">
-        <v>6564663</v>
+        <v>6564656</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5314,7 +5312,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5324,7 +5322,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,10 +5349,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129150606</v>
+        <v>129150580</v>
       </c>
       <c r="B46" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5386,10 +5384,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665503</v>
+        <v>665374</v>
       </c>
       <c r="R46" t="n">
-        <v>6564692</v>
+        <v>6564595</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5421,7 +5419,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5431,7 +5429,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,10 +5456,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129150612</v>
+        <v>129150581</v>
       </c>
       <c r="B47" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5493,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665587</v>
+        <v>665366</v>
       </c>
       <c r="R47" t="n">
-        <v>6564768</v>
+        <v>6564608</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5526,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5536,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5565,10 +5563,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129150568</v>
+        <v>129150582</v>
       </c>
       <c r="B48" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5600,10 +5598,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665276</v>
+        <v>665370</v>
       </c>
       <c r="R48" t="n">
-        <v>6564529</v>
+        <v>6564621</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,7 +5633,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5645,7 +5643,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5672,32 +5670,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129150621</v>
+        <v>129150583</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>93235</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5705,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665321</v>
+        <v>665372</v>
       </c>
       <c r="R49" t="n">
-        <v>6564753</v>
+        <v>6564721</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5742,7 +5740,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5752,7 +5750,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5779,32 +5777,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129150627</v>
+        <v>129150584</v>
       </c>
       <c r="B50" t="n">
-        <v>92359</v>
+        <v>93235</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5814,10 +5812,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665419</v>
+        <v>665409</v>
       </c>
       <c r="R50" t="n">
-        <v>6564672</v>
+        <v>6564786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5849,7 +5847,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5859,7 +5857,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,10 +5884,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129150611</v>
+        <v>129150585</v>
       </c>
       <c r="B51" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5921,10 +5919,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665607</v>
+        <v>665424</v>
       </c>
       <c r="R51" t="n">
-        <v>6564770</v>
+        <v>6564786</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,7 +5954,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5966,7 +5964,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,10 +5991,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129150577</v>
+        <v>129150586</v>
       </c>
       <c r="B52" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6028,10 +6026,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665446</v>
+        <v>665436</v>
       </c>
       <c r="R52" t="n">
-        <v>6564659</v>
+        <v>6564778</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,7 +6061,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6073,7 +6071,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6100,10 +6098,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129150601</v>
+        <v>129150587</v>
       </c>
       <c r="B53" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6135,10 +6133,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665364</v>
+        <v>665424</v>
       </c>
       <c r="R53" t="n">
-        <v>6564665</v>
+        <v>6564762</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6170,7 +6168,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6180,7 +6178,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6207,10 +6205,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129150591</v>
+        <v>129150588</v>
       </c>
       <c r="B54" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6242,10 +6240,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665318</v>
+        <v>665414</v>
       </c>
       <c r="R54" t="n">
-        <v>6564762</v>
+        <v>6564728</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6275,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6287,7 +6285,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,10 +6312,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129150580</v>
+        <v>129150589</v>
       </c>
       <c r="B55" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6349,10 +6347,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665374</v>
+        <v>665371</v>
       </c>
       <c r="R55" t="n">
-        <v>6564595</v>
+        <v>6564789</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6384,7 +6382,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6394,7 +6392,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6421,10 +6419,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129150570</v>
+        <v>129150590</v>
       </c>
       <c r="B56" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6456,10 +6454,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665399</v>
+        <v>665331</v>
       </c>
       <c r="R56" t="n">
-        <v>6564537</v>
+        <v>6564765</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6491,7 +6489,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6501,7 +6499,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6528,32 +6526,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129150618</v>
+        <v>129150591</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>93235</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6563,10 +6561,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665400</v>
+        <v>665318</v>
       </c>
       <c r="R57" t="n">
-        <v>6564742</v>
+        <v>6564762</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6598,7 +6596,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6608,7 +6606,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6635,10 +6633,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129150557</v>
+        <v>129150593</v>
       </c>
       <c r="B58" t="n">
-        <v>91602</v>
+        <v>93235</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6646,21 +6644,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6670,10 +6668,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>665183</v>
+        <v>665256</v>
       </c>
       <c r="R58" t="n">
-        <v>6564505</v>
+        <v>6564756</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,7 +6703,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6715,7 +6713,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6742,32 +6740,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129150628</v>
+        <v>129150594</v>
       </c>
       <c r="B59" t="n">
-        <v>92359</v>
+        <v>93235</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6777,10 +6775,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>665455</v>
+        <v>665232</v>
       </c>
       <c r="R59" t="n">
-        <v>6564681</v>
+        <v>6564745</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6812,7 +6810,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6822,7 +6820,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6849,32 +6847,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129150626</v>
+        <v>129150595</v>
       </c>
       <c r="B60" t="n">
-        <v>92359</v>
+        <v>93235</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6884,10 +6882,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>665260</v>
+        <v>665210</v>
       </c>
       <c r="R60" t="n">
-        <v>6564773</v>
+        <v>6564762</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,7 +6917,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6929,7 +6927,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6956,32 +6954,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129150619</v>
+        <v>129150596</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>93235</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6991,10 +6989,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>665365</v>
+        <v>665174</v>
       </c>
       <c r="R61" t="n">
-        <v>6564786</v>
+        <v>6564743</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,7 +7024,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7036,7 +7034,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7063,10 +7061,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129150583</v>
+        <v>129150597</v>
       </c>
       <c r="B62" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7098,10 +7096,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>665372</v>
+        <v>665233</v>
       </c>
       <c r="R62" t="n">
-        <v>6564721</v>
+        <v>6564718</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7133,7 +7131,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7143,7 +7141,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7170,10 +7168,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129150566</v>
+        <v>129150598</v>
       </c>
       <c r="B63" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7205,10 +7203,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>665194</v>
+        <v>665283</v>
       </c>
       <c r="R63" t="n">
-        <v>6564498</v>
+        <v>6564685</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7240,7 +7238,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7250,7 +7248,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7277,10 +7275,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129150594</v>
+        <v>129150599</v>
       </c>
       <c r="B64" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7312,10 +7310,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>665232</v>
+        <v>665294</v>
       </c>
       <c r="R64" t="n">
-        <v>6564745</v>
+        <v>6564670</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7347,7 +7345,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7357,7 +7355,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7384,10 +7382,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129150598</v>
+        <v>129150600</v>
       </c>
       <c r="B65" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7419,10 +7417,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>665283</v>
+        <v>665346</v>
       </c>
       <c r="R65" t="n">
-        <v>6564685</v>
+        <v>6564670</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7454,7 +7452,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7464,7 +7462,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7491,10 +7489,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129150593</v>
+        <v>129150601</v>
       </c>
       <c r="B66" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7526,10 +7524,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>665256</v>
+        <v>665364</v>
       </c>
       <c r="R66" t="n">
-        <v>6564756</v>
+        <v>6564665</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7561,7 +7559,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7571,7 +7569,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7598,10 +7596,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129150605</v>
+        <v>129150602</v>
       </c>
       <c r="B67" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7633,10 +7631,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>665484</v>
+        <v>665388</v>
       </c>
       <c r="R67" t="n">
-        <v>6564691</v>
+        <v>6564663</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7668,7 +7666,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7678,7 +7676,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7705,10 +7703,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129150613</v>
+        <v>129150603</v>
       </c>
       <c r="B68" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7740,10 +7738,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665566</v>
+        <v>665453</v>
       </c>
       <c r="R68" t="n">
-        <v>6564813</v>
+        <v>6564677</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7775,7 +7773,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7785,7 +7783,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,32 +7810,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129150625</v>
+        <v>129150604</v>
       </c>
       <c r="B69" t="n">
-        <v>92359</v>
+        <v>93235</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7847,10 +7845,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665422</v>
+        <v>665464</v>
       </c>
       <c r="R69" t="n">
-        <v>6564565</v>
+        <v>6564686</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7882,7 +7880,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7892,7 +7890,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7919,10 +7917,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129150587</v>
+        <v>129150605</v>
       </c>
       <c r="B70" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7954,10 +7952,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>665424</v>
+        <v>665484</v>
       </c>
       <c r="R70" t="n">
-        <v>6564762</v>
+        <v>6564691</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7989,7 +7987,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7999,7 +7997,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8026,10 +8024,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129150595</v>
+        <v>129150606</v>
       </c>
       <c r="B71" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8061,10 +8059,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665210</v>
+        <v>665503</v>
       </c>
       <c r="R71" t="n">
-        <v>6564762</v>
+        <v>6564692</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8096,7 +8094,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8106,7 +8104,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8133,10 +8131,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150556</v>
+        <v>129150607</v>
       </c>
       <c r="B72" t="n">
-        <v>57890</v>
+        <v>93235</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8144,38 +8142,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665406</v>
+        <v>665514</v>
       </c>
       <c r="R72" t="n">
-        <v>6564548</v>
+        <v>6564684</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8207,7 +8201,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8217,7 +8211,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8244,10 +8238,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150610</v>
+        <v>129150609</v>
       </c>
       <c r="B73" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8279,10 +8273,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665640</v>
+        <v>665505</v>
       </c>
       <c r="R73" t="n">
-        <v>6564667</v>
+        <v>6564674</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8314,7 +8308,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8324,7 +8318,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8351,10 +8345,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150609</v>
+        <v>129150610</v>
       </c>
       <c r="B74" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,10 +8380,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665505</v>
+        <v>665640</v>
       </c>
       <c r="R74" t="n">
-        <v>6564674</v>
+        <v>6564667</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,7 +8415,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8431,7 +8425,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8458,32 +8452,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150622</v>
+        <v>129150611</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>93235</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8493,10 +8487,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665194</v>
+        <v>665607</v>
       </c>
       <c r="R75" t="n">
-        <v>6564740</v>
+        <v>6564770</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,7 +8522,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8538,7 +8532,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8565,10 +8559,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150572</v>
+        <v>129150612</v>
       </c>
       <c r="B76" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8600,10 +8594,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665424</v>
+        <v>665587</v>
       </c>
       <c r="R76" t="n">
-        <v>6564571</v>
+        <v>6564768</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8635,7 +8629,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8645,7 +8639,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8672,10 +8666,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150607</v>
+        <v>129150613</v>
       </c>
       <c r="B77" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8707,10 +8701,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665514</v>
+        <v>665566</v>
       </c>
       <c r="R77" t="n">
-        <v>6564684</v>
+        <v>6564813</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8742,7 +8736,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8752,7 +8746,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,48 +8773,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150581</v>
+        <v>127898594</v>
       </c>
       <c r="B78" t="n">
-        <v>92901</v>
+        <v>56845</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>100053</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Brantbrink, Srm</t>
+          <t>Elljusspår, 146 38 Botkyrka kommun, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665366</v>
+        <v>665529</v>
       </c>
       <c r="R78" t="n">
-        <v>6564608</v>
+        <v>6564827</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8844,22 +8847,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8874,22 +8877,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150600</v>
+        <v>129052185</v>
       </c>
       <c r="B79" t="n">
-        <v>92901</v>
+        <v>58114</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8897,37 +8904,49 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Brantbrink, Srm</t>
+          <t>Brantbrink, Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665346</v>
+        <v>665290</v>
       </c>
       <c r="R79" t="n">
-        <v>6564670</v>
+        <v>6564770</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8951,22 +8970,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8981,22 +9000,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150589</v>
+        <v>129107649</v>
       </c>
       <c r="B80" t="n">
-        <v>92901</v>
+        <v>58114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9004,21 +9023,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9028,10 +9047,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665371</v>
+        <v>665272</v>
       </c>
       <c r="R80" t="n">
-        <v>6564789</v>
+        <v>6564714</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9058,22 +9077,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9088,22 +9097,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129150597</v>
+        <v>129150556</v>
       </c>
       <c r="B81" t="n">
-        <v>92901</v>
+        <v>58114</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9111,34 +9120,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665233</v>
+        <v>665406</v>
       </c>
       <c r="R81" t="n">
-        <v>6564718</v>
+        <v>6564548</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,7 +9183,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9180,7 +9193,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9207,32 +9220,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129150629</v>
+        <v>128970284</v>
       </c>
       <c r="B82" t="n">
-        <v>92359</v>
+        <v>8455</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9242,10 +9255,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665507</v>
+        <v>665545</v>
       </c>
       <c r="R82" t="n">
-        <v>6564685</v>
+        <v>6564914</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9272,22 +9285,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9314,32 +9327,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129150575</v>
+        <v>129150615</v>
       </c>
       <c r="B83" t="n">
-        <v>92901</v>
+        <v>8455</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9349,10 +9362,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665457</v>
+        <v>665164</v>
       </c>
       <c r="R83" t="n">
-        <v>6564660</v>
+        <v>6564505</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9384,7 +9397,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9394,7 +9407,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,32 +9434,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129150603</v>
+        <v>129150616</v>
       </c>
       <c r="B84" t="n">
-        <v>92901</v>
+        <v>8455</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9456,10 +9469,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665453</v>
+        <v>665382</v>
       </c>
       <c r="R84" t="n">
-        <v>6564677</v>
+        <v>6564609</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9491,7 +9504,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9501,7 +9514,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9528,32 +9541,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129150588</v>
+        <v>129150617</v>
       </c>
       <c r="B85" t="n">
-        <v>92901</v>
+        <v>8455</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9563,10 +9576,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>665414</v>
+        <v>665376</v>
       </c>
       <c r="R85" t="n">
-        <v>6564728</v>
+        <v>6564598</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9598,7 +9611,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9608,7 +9621,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9635,10 +9648,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129150623</v>
+        <v>129150618</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9670,10 +9683,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>665233</v>
+        <v>665400</v>
       </c>
       <c r="R86" t="n">
-        <v>6564720</v>
+        <v>6564742</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9705,7 +9718,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9715,7 +9728,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9742,10 +9755,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129150615</v>
+        <v>129150619</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9777,10 +9790,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>665164</v>
+        <v>665365</v>
       </c>
       <c r="R87" t="n">
-        <v>6564505</v>
+        <v>6564786</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9812,7 +9825,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9822,7 +9835,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9846,6 +9859,434 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129150620</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>665358</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6564768</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129150621</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>665321</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6564753</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129150622</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>665194</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6564740</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129150623</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>665233</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6564720</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150625</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150626</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150627</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150628</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150629</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107651</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150557</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536275</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970267</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1748,6 +1798,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970268</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1855,6 +1910,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970269</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1962,6 +2022,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970270</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2069,6 +2134,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970271</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2176,6 +2246,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970272</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2273,6 +2348,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107653</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2370,6 +2450,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107654</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107655</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2564,6 +2654,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107656</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2671,6 +2766,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150565</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2778,6 +2878,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150566</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2885,6 +2990,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150567</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2992,6 +3102,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150568</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3099,6 +3214,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150569</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3206,6 +3326,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150570</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3313,6 +3438,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150571</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3420,6 +3550,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150572</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3527,6 +3662,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150573</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3634,6 +3774,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150574</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3741,6 +3886,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150575</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3848,6 +3998,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150576</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3955,6 +4110,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150577</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4062,6 +4222,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150578</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4169,6 +4334,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150579</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4276,6 +4446,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150580</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4383,6 +4558,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150581</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4490,6 +4670,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150582</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4597,6 +4782,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150583</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4704,6 +4894,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150584</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4811,6 +5006,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150585</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4918,6 +5118,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150586</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5025,6 +5230,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150587</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5132,6 +5342,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150588</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5239,6 +5454,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150589</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5346,6 +5566,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150590</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5453,6 +5678,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150591</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5560,6 +5790,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150593</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5667,6 +5902,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150594</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5774,6 +6014,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150595</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5881,6 +6126,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150596</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5988,6 +6238,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150597</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6095,6 +6350,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150598</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6202,6 +6462,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150599</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6309,6 +6574,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150600</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6416,6 +6686,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150601</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6523,6 +6798,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150602</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6630,6 +6910,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150603</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6737,6 +7022,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150604</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6844,6 +7134,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150605</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6951,6 +7246,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150606</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7058,6 +7358,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150607</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7165,6 +7470,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150609</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7272,6 +7582,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150610</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7379,6 +7694,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150611</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7486,6 +7806,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150612</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7593,6 +7918,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150613</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7713,6 +8043,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127898594</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7832,6 +8167,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129052185</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7929,6 +8269,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107649</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8040,6 +8385,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150556</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8147,6 +8497,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970284</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8254,6 +8609,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150615</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8361,6 +8721,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150616</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8468,6 +8833,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150617</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8575,6 +8945,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150618</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8682,6 +9057,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150619</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8789,6 +9169,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150620</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8896,6 +9281,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150621</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9003,6 +9393,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150622</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9110,6 +9505,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129150623</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9217,6 +9617,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970264</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9324,6 +9729,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970265</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9431,6 +9841,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970273</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9538,6 +9953,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970274</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9645,6 +10065,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970275</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9752,6 +10177,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970277</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9859,6 +10289,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970278</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9966,6 +10401,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970279</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10073,6 +10513,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970280</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10180,6 +10625,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970281</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10287,8 +10737,105 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970282</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>